--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>107243</v>
+        <v>98458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R2" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>98383</v>
+        <v>107318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R3" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174187</v>
+        <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>98397</v>
+        <v>96039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,46 +908,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223621</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725669</v>
+        <v>725732</v>
       </c>
       <c r="R4" t="n">
-        <v>6385120</v>
+        <v>6385256</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +988,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,7 +1015,7 @@
         <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1126,7 @@
         <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B7" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R7" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174604</v>
+        <v>127174195</v>
       </c>
       <c r="B8" t="n">
-        <v>95964</v>
+        <v>98472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,49 +1356,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>223621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725732</v>
+        <v>725722</v>
       </c>
       <c r="R8" t="n">
-        <v>6385256</v>
+        <v>6385158</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,13 +1433,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174209</v>
+        <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>98383</v>
+        <v>107318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725832</v>
+        <v>725647</v>
       </c>
       <c r="R9" t="n">
-        <v>6385251</v>
+        <v>6385302</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174172</v>
+        <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>107243</v>
+        <v>98458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725473</v>
+        <v>725832</v>
       </c>
       <c r="R10" t="n">
-        <v>6385147</v>
+        <v>6385251</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174224</v>
+        <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725647</v>
+        <v>725473</v>
       </c>
       <c r="R11" t="n">
-        <v>6385302</v>
+        <v>6385147</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>109185</v>
+        <v>5492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,46 +1911,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R13" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,6 +1973,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1986,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2011,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>109260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2013,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R14" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,11 +2084,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2097,6 +2092,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2116,7 +2116,7 @@
         <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>107243</v>
+        <v>98328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R16" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         <v>127174178</v>
       </c>
       <c r="B17" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174220</v>
+        <v>127174217</v>
       </c>
       <c r="B18" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725734</v>
+        <v>725732</v>
       </c>
       <c r="R18" t="n">
-        <v>6385261</v>
+        <v>6385256</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,11 +2526,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,37 +2557,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174203</v>
+        <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>98253</v>
+        <v>107318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725843</v>
+        <v>725734</v>
       </c>
       <c r="R19" t="n">
-        <v>6385204</v>
+        <v>6385261</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,6 +2639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
         <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98383</v>
+        <v>98458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98398</v>
+        <v>98473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98389</v>
+        <v>98464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R25" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>127174173</v>
       </c>
       <c r="B27" t="n">
-        <v>98383</v>
+        <v>98458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>127174166</v>
       </c>
       <c r="B28" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,37 +3677,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174145</v>
+        <v>127174193</v>
       </c>
       <c r="B29" t="n">
-        <v>107243</v>
+        <v>105471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725591</v>
+        <v>725758</v>
       </c>
       <c r="R29" t="n">
-        <v>6385252</v>
+        <v>6385124</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3775,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174168</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>98389</v>
+        <v>98411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,21 +3799,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3837,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725457</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385181</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3904,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174193</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>105396</v>
+        <v>107318</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725758</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385124</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3986,6 +3981,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174207</v>
+        <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>98336</v>
+        <v>98464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219797</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725831</v>
+        <v>725457</v>
       </c>
       <c r="R32" t="n">
-        <v>6385246</v>
+        <v>6385181</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
         <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98397</v>
+        <v>109260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109185</v>
+        <v>98472</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,42 +4682,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>98336</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R38" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,6 +4760,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4772,11 +4773,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4793,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107243</v>
+        <v>98411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4904,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174757</v>
+        <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>107318</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,27 +4911,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725778</v>
+        <v>725722</v>
       </c>
       <c r="R40" t="n">
-        <v>6385123</v>
+        <v>6385158</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4982,11 +4982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4995,6 +4990,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkblandskog av blandad ålder.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98383</v>
+        <v>98458</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5344,42 +5344,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B44" t="n">
-        <v>98397</v>
+        <v>109260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R44" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B45" t="n">
-        <v>98398</v>
+        <v>98472</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R45" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>127174177</v>
       </c>
       <c r="B46" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,42 +5677,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B47" t="n">
-        <v>109185</v>
+        <v>98473</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R47" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127174160</v>
       </c>
       <c r="B48" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>127174151</v>
       </c>
       <c r="B49" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>127174163</v>
       </c>
       <c r="B51" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>127174184</v>
       </c>
       <c r="B52" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98397</v>
+        <v>109260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109185</v>
+        <v>98472</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174174</v>
+        <v>127174218</v>
       </c>
       <c r="B55" t="n">
-        <v>98383</v>
+        <v>98472</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,26 +6568,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725478</v>
+        <v>725732</v>
       </c>
       <c r="R55" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6639,11 +6639,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6655,7 +6650,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6676,7 +6671,7 @@
         <v>127174157</v>
       </c>
       <c r="B56" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6787,7 +6782,7 @@
         <v>127174204</v>
       </c>
       <c r="B57" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6900,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174218</v>
+        <v>127174174</v>
       </c>
       <c r="B58" t="n">
-        <v>98397</v>
+        <v>98458</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,26 +6906,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6944,13 +6939,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725732</v>
+        <v>725478</v>
       </c>
       <c r="R58" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6982,6 +6977,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B2" t="n">
-        <v>98458</v>
+        <v>107324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R2" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B3" t="n">
-        <v>107318</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R3" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174187</v>
+        <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725669</v>
+        <v>725722</v>
       </c>
       <c r="R7" t="n">
-        <v>6385120</v>
+        <v>6385158</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B8" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R8" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B9" t="n">
-        <v>107318</v>
+        <v>98464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R9" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174209</v>
+        <v>127174172</v>
       </c>
       <c r="B10" t="n">
-        <v>98458</v>
+        <v>107324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725832</v>
+        <v>725473</v>
       </c>
       <c r="R10" t="n">
-        <v>6385251</v>
+        <v>6385147</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174172</v>
+        <v>127174224</v>
       </c>
       <c r="B11" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725473</v>
+        <v>725647</v>
       </c>
       <c r="R11" t="n">
-        <v>6385147</v>
+        <v>6385302</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174194</v>
+        <v>127174178</v>
       </c>
       <c r="B15" t="n">
-        <v>98472</v>
+        <v>107324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725758</v>
+        <v>725542</v>
       </c>
       <c r="R15" t="n">
-        <v>6385124</v>
+        <v>6385111</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174203</v>
+        <v>127174217</v>
       </c>
       <c r="B16" t="n">
-        <v>98328</v>
+        <v>107324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R16" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174178</v>
+        <v>127174220</v>
       </c>
       <c r="B17" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725542</v>
+        <v>725734</v>
       </c>
       <c r="R17" t="n">
-        <v>6385111</v>
+        <v>6385261</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,6 +2417,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2433,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,37 +2451,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B18" t="n">
-        <v>107318</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R18" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2539,7 +2544,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2557,37 +2562,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174220</v>
+        <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>107318</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2601,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725734</v>
+        <v>725758</v>
       </c>
       <c r="R19" t="n">
-        <v>6385261</v>
+        <v>6385124</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,11 +2644,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
         <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98458</v>
+        <v>98464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B22" t="n">
-        <v>98473</v>
+        <v>107324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R22" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B23" t="n">
-        <v>107318</v>
+        <v>98479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R23" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174152</v>
+        <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98472</v>
+        <v>98464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725532</v>
+        <v>725473</v>
       </c>
       <c r="R25" t="n">
-        <v>6385259</v>
+        <v>6385147</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3339,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3374,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R26" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3450,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174173</v>
+        <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98458</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,26 +3466,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3494,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725473</v>
+        <v>725549</v>
       </c>
       <c r="R27" t="n">
-        <v>6385147</v>
+        <v>6385258</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3532,11 +3537,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,42 +3566,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174166</v>
+        <v>127174193</v>
       </c>
       <c r="B28" t="n">
-        <v>109260</v>
+        <v>105477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725442</v>
+        <v>725758</v>
       </c>
       <c r="R28" t="n">
-        <v>6385186</v>
+        <v>6385124</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174193</v>
+        <v>127174168</v>
       </c>
       <c r="B29" t="n">
-        <v>105471</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,26 +3688,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725758</v>
+        <v>725457</v>
       </c>
       <c r="R29" t="n">
-        <v>6385124</v>
+        <v>6385181</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3788,42 +3788,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174166</v>
       </c>
       <c r="B30" t="n">
-        <v>98411</v>
+        <v>109266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725442</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385186</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174207</v>
       </c>
       <c r="B31" t="n">
-        <v>107318</v>
+        <v>98417</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725831</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385246</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3981,11 +3981,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3997,7 +3992,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,37 +4010,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174168</v>
+        <v>127174145</v>
       </c>
       <c r="B32" t="n">
-        <v>98464</v>
+        <v>107324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,13 +4054,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725457</v>
+        <v>725591</v>
       </c>
       <c r="R32" t="n">
-        <v>6385181</v>
+        <v>6385252</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,6 +4090,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B33" t="n">
-        <v>109260</v>
+        <v>107324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R33" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,11 +4208,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4224,7 +4219,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B34" t="n">
-        <v>107318</v>
+        <v>109266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,31 +4248,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4286,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R34" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,6 +4319,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
         <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B39" t="n">
-        <v>98411</v>
+        <v>107324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R39" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B40" t="n">
-        <v>107318</v>
+        <v>98417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R40" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B41" t="n">
-        <v>107318</v>
+        <v>98417</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R41" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98458</v>
+        <v>98464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B43" t="n">
-        <v>98411</v>
+        <v>107324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R43" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,42 +5344,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B44" t="n">
-        <v>109260</v>
+        <v>98479</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R44" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,42 +5455,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>98472</v>
+        <v>109266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R45" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5569,7 +5569,7 @@
         <v>127174177</v>
       </c>
       <c r="B46" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127174160</v>
       </c>
       <c r="B48" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>127174151</v>
       </c>
       <c r="B49" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>109260</v>
+        <v>107324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,34 +6128,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R51" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,11 +6199,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6224,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>107318</v>
+        <v>109266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,43 +6239,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R52" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,6 +6301,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
         <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>127174218</v>
       </c>
       <c r="B55" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>127174157</v>
       </c>
       <c r="B56" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>127174204</v>
       </c>
       <c r="B57" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>127174174</v>
       </c>
       <c r="B58" t="n">
-        <v>98458</v>
+        <v>98464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>107324</v>
+        <v>98464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R2" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>107324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R3" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174604</v>
+        <v>127174179</v>
       </c>
       <c r="B4" t="n">
-        <v>96045</v>
+        <v>107324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725732</v>
+        <v>725566</v>
       </c>
       <c r="R4" t="n">
-        <v>6385256</v>
+        <v>6385110</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,13 +985,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1012,37 +1008,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174179</v>
+        <v>127174150</v>
       </c>
       <c r="B5" t="n">
-        <v>107324</v>
+        <v>98465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725566</v>
+        <v>725532</v>
       </c>
       <c r="R5" t="n">
-        <v>6385110</v>
+        <v>6385259</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174150</v>
+        <v>127174195</v>
       </c>
       <c r="B6" t="n">
-        <v>98465</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1130,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725532</v>
+        <v>725722</v>
       </c>
       <c r="R6" t="n">
-        <v>6385259</v>
+        <v>6385158</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B7" t="n">
         <v>98478</v>
@@ -1264,7 +1260,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R7" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174187</v>
+        <v>127174604</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>96045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,46 +1352,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223621</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725669</v>
+        <v>725732</v>
       </c>
       <c r="R8" t="n">
-        <v>6385120</v>
+        <v>6385256</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1432,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174209</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>98464</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725832</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385251</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174172</v>
+        <v>127174224</v>
       </c>
       <c r="B10" t="n">
         <v>107324</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725473</v>
+        <v>725647</v>
       </c>
       <c r="R10" t="n">
-        <v>6385147</v>
+        <v>6385302</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B11" t="n">
-        <v>107324</v>
+        <v>98464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R11" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>107324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R12" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B13" t="n">
-        <v>5492</v>
+        <v>109266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,37 +1911,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R13" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,11 +1982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1986,6 +1990,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2002,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B14" t="n">
-        <v>109266</v>
+        <v>5492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,46 +2022,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R14" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,6 +2084,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2092,11 +2097,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174178</v>
+        <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>107324</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725542</v>
+        <v>725758</v>
       </c>
       <c r="R15" t="n">
-        <v>6385111</v>
+        <v>6385124</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>107324</v>
+        <v>98334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R16" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174220</v>
+        <v>127174178</v>
       </c>
       <c r="B17" t="n">
         <v>107324</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725734</v>
+        <v>725542</v>
       </c>
       <c r="R17" t="n">
-        <v>6385261</v>
+        <v>6385111</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,11 +2417,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2451,37 +2446,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174203</v>
+        <v>127174217</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>107324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R18" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2544,7 +2539,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2562,37 +2557,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174194</v>
+        <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>107324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725758</v>
+        <v>725734</v>
       </c>
       <c r="R19" t="n">
-        <v>6385124</v>
+        <v>6385261</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,6 +2639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>107324</v>
+        <v>98479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R22" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>98479</v>
+        <v>107324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R23" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174173</v>
+        <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98464</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725473</v>
+        <v>725532</v>
       </c>
       <c r="R25" t="n">
-        <v>6385147</v>
+        <v>6385259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3326,7 +3321,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3344,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
         <v>98478</v>
@@ -3374,7 +3369,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3388,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174147</v>
+        <v>127174173</v>
       </c>
       <c r="B27" t="n">
-        <v>98478</v>
+        <v>98464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,26 +3461,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725549</v>
+        <v>725473</v>
       </c>
       <c r="R27" t="n">
-        <v>6385258</v>
+        <v>6385147</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3532,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3677,27 +3677,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174168</v>
+        <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>109266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725457</v>
+        <v>725442</v>
       </c>
       <c r="R29" t="n">
-        <v>6385181</v>
+        <v>6385186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3788,42 +3788,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174166</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>109266</v>
+        <v>98417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725442</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385186</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174207</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>98417</v>
+        <v>107324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725831</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385246</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3981,6 +3981,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3992,7 +3997,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4010,37 +4015,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174145</v>
+        <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>107324</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4054,13 +4059,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725591</v>
+        <v>725457</v>
       </c>
       <c r="R32" t="n">
-        <v>6385252</v>
+        <v>6385181</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4090,11 +4095,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>107324</v>
+        <v>109266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R33" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,6 +4208,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4237,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>109266</v>
+        <v>107324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,31 +4253,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4281,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R34" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,11 +4324,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,48 +4353,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>109266</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R35" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4424,11 +4433,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,57 +4464,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>109266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R36" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4789,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107324</v>
+        <v>98417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>98417</v>
+        <v>107324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R40" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>98417</v>
+        <v>107324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R41" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>107324</v>
+        <v>98417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R43" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B44" t="n">
-        <v>98479</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R44" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B45" t="n">
-        <v>109266</v>
+        <v>107324</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,31 +5466,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R45" t="n">
         <v>6385121</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174177</v>
+        <v>127174182</v>
       </c>
       <c r="B46" t="n">
-        <v>107324</v>
+        <v>109266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,31 +5577,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725520</v>
+        <v>725616</v>
       </c>
       <c r="R46" t="n">
         <v>6385121</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174186</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>219875</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725669</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>109266</v>
+        <v>107324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,37 +5799,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,11 +5870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5895,10 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>107324</v>
+        <v>109266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,46 +5910,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,6 +5972,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109266</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>109266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -897,57 +897,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174179</v>
+        <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>107324</v>
+        <v>96045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725566</v>
+        <v>725732</v>
       </c>
       <c r="R4" t="n">
-        <v>6385110</v>
+        <v>6385256</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +988,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174150</v>
+        <v>127174195</v>
       </c>
       <c r="B5" t="n">
-        <v>98465</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,26 +1023,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725532</v>
+        <v>725722</v>
       </c>
       <c r="R5" t="n">
-        <v>6385259</v>
+        <v>6385158</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B6" t="n">
         <v>98478</v>
@@ -1149,7 +1153,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R6" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174187</v>
+        <v>127174179</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>107324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725669</v>
+        <v>725566</v>
       </c>
       <c r="R7" t="n">
-        <v>6385120</v>
+        <v>6385110</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174604</v>
+        <v>127174150</v>
       </c>
       <c r="B8" t="n">
-        <v>96045</v>
+        <v>98465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,49 +1356,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725732</v>
+        <v>725532</v>
       </c>
       <c r="R8" t="n">
-        <v>6385256</v>
+        <v>6385259</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,13 +1433,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174194</v>
+        <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,26 +2124,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>219769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725758</v>
+        <v>725843</v>
       </c>
       <c r="R15" t="n">
-        <v>6385124</v>
+        <v>6385204</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174203</v>
+        <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>98334</v>
+        <v>107324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725843</v>
+        <v>725542</v>
       </c>
       <c r="R16" t="n">
-        <v>6385204</v>
+        <v>6385111</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174178</v>
+        <v>127174217</v>
       </c>
       <c r="B17" t="n">
         <v>107324</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725542</v>
+        <v>725732</v>
       </c>
       <c r="R17" t="n">
-        <v>6385111</v>
+        <v>6385256</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174217</v>
+        <v>127174220</v>
       </c>
       <c r="B18" t="n">
         <v>107324</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725732</v>
+        <v>725734</v>
       </c>
       <c r="R18" t="n">
-        <v>6385256</v>
+        <v>6385261</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,6 +2526,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,37 +2562,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174220</v>
+        <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>107324</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2601,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725734</v>
+        <v>725758</v>
       </c>
       <c r="R19" t="n">
-        <v>6385261</v>
+        <v>6385124</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,11 +2644,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>109266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109266</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5344,37 +5344,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174183</v>
+        <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>107324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725652</v>
+        <v>725520</v>
       </c>
       <c r="R44" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174177</v>
+        <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>107324</v>
+        <v>109266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,31 +5466,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725520</v>
+        <v>725616</v>
       </c>
       <c r="R45" t="n">
         <v>6385121</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>109266</v>
+        <v>98479</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R46" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>98479</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>107324</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R55" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,6 +6639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6650,7 +6655,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6668,10 +6673,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98478</v>
+        <v>98464</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,26 +6684,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6712,13 +6717,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R56" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6750,6 +6755,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6761,7 +6771,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6779,37 +6789,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>107324</v>
+        <v>98478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6823,10 +6833,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R57" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6861,11 +6871,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6895,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98464</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6906,26 +6911,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6939,13 +6944,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R58" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6977,11 +6982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98464</v>
+        <v>98465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174195</v>
+        <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>107325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725722</v>
+        <v>725566</v>
       </c>
       <c r="R5" t="n">
-        <v>6385158</v>
+        <v>6385110</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174187</v>
+        <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725669</v>
+        <v>725532</v>
       </c>
       <c r="R6" t="n">
-        <v>6385120</v>
+        <v>6385259</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174179</v>
+        <v>127174187</v>
       </c>
       <c r="B7" t="n">
-        <v>107324</v>
+        <v>98479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725566</v>
+        <v>725669</v>
       </c>
       <c r="R7" t="n">
-        <v>6385110</v>
+        <v>6385120</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174150</v>
+        <v>127174195</v>
       </c>
       <c r="B8" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725532</v>
+        <v>725722</v>
       </c>
       <c r="R8" t="n">
-        <v>6385259</v>
+        <v>6385158</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174155</v>
+        <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>107325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725522</v>
+        <v>725647</v>
       </c>
       <c r="R9" t="n">
-        <v>6385261</v>
+        <v>6385302</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>107324</v>
+        <v>98465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R10" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174209</v>
+        <v>127174155</v>
       </c>
       <c r="B11" t="n">
-        <v>98464</v>
+        <v>98479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725832</v>
+        <v>725522</v>
       </c>
       <c r="R11" t="n">
-        <v>6385251</v>
+        <v>6385261</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127174172</v>
       </c>
       <c r="B12" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>109266</v>
+        <v>5492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,46 +1911,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R13" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,6 +1973,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1986,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2011,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>109267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2013,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R14" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,11 +2084,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2097,6 +2092,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2116,7 +2116,7 @@
         <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>98335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127174217</v>
       </c>
       <c r="B17" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>127174220</v>
       </c>
       <c r="B18" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98464</v>
+        <v>98465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98479</v>
+        <v>98480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174152</v>
+        <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98465</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725532</v>
+        <v>725473</v>
       </c>
       <c r="R25" t="n">
-        <v>6385259</v>
+        <v>6385147</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3339,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3374,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R26" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3450,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174173</v>
+        <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98464</v>
+        <v>98479</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,26 +3466,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3494,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725473</v>
+        <v>725549</v>
       </c>
       <c r="R27" t="n">
-        <v>6385147</v>
+        <v>6385258</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3532,11 +3537,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174193</v>
+        <v>127174207</v>
       </c>
       <c r="B28" t="n">
-        <v>105477</v>
+        <v>98418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,26 +3577,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725758</v>
+        <v>725831</v>
       </c>
       <c r="R28" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174166</v>
+        <v>127174145</v>
       </c>
       <c r="B29" t="n">
-        <v>109266</v>
+        <v>107325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,31 +3688,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725442</v>
+        <v>725591</v>
       </c>
       <c r="R29" t="n">
-        <v>6385186</v>
+        <v>6385252</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,6 +3757,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174168</v>
       </c>
       <c r="B30" t="n">
-        <v>98417</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,21 +3804,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3832,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725457</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385181</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,10 +3904,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174166</v>
       </c>
       <c r="B31" t="n">
-        <v>107324</v>
+        <v>109267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,31 +3915,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3943,13 +3948,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725442</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385186</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,11 +3984,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174168</v>
+        <v>127174193</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>105478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,26 +4026,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725457</v>
+        <v>725758</v>
       </c>
       <c r="R32" t="n">
-        <v>6385181</v>
+        <v>6385124</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B33" t="n">
-        <v>109266</v>
+        <v>107325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R33" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,11 +4208,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4224,7 +4219,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B34" t="n">
-        <v>107324</v>
+        <v>109267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,31 +4248,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4286,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R34" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,6 +4319,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,48 +4353,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>109266</v>
+        <v>98479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R35" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4424,11 +4433,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,57 +4464,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>109267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R36" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B39" t="n">
-        <v>98417</v>
+        <v>107325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R39" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B40" t="n">
-        <v>107324</v>
+        <v>98418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R40" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98464</v>
+        <v>98465</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98417</v>
+        <v>98418</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,42 +5455,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B45" t="n">
-        <v>109266</v>
+        <v>98480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R45" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B46" t="n">
         <v>98479</v>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R46" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,42 +5677,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>109267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B51" t="n">
-        <v>107324</v>
+        <v>109267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,43 +6128,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R51" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,6 +6190,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6210,7 +6206,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6228,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B52" t="n">
-        <v>109266</v>
+        <v>107325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6239,34 +6235,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R52" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6301,11 +6306,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>109267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109266</v>
+        <v>98479</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B55" t="n">
-        <v>107324</v>
+        <v>98479</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R55" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,11 +6639,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6655,7 +6650,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6673,10 +6668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B56" t="n">
-        <v>98464</v>
+        <v>98479</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,26 +6679,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6717,13 +6712,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R56" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,11 +6750,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6771,7 +6761,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6789,37 +6779,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B57" t="n">
-        <v>98478</v>
+        <v>107325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6833,10 +6823,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R57" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6871,6 +6861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6900,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>98465</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,26 +6906,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6944,13 +6939,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R58" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6982,6 +6977,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -1012,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174179</v>
+        <v>127174195</v>
       </c>
       <c r="B5" t="n">
-        <v>107325</v>
+        <v>98479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725566</v>
+        <v>725722</v>
       </c>
       <c r="R5" t="n">
-        <v>6385110</v>
+        <v>6385158</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174150</v>
+        <v>127174187</v>
       </c>
       <c r="B6" t="n">
-        <v>98466</v>
+        <v>98479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725532</v>
+        <v>725669</v>
       </c>
       <c r="R6" t="n">
-        <v>6385259</v>
+        <v>6385120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174187</v>
+        <v>127174179</v>
       </c>
       <c r="B7" t="n">
-        <v>98479</v>
+        <v>107325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725669</v>
+        <v>725566</v>
       </c>
       <c r="R7" t="n">
-        <v>6385120</v>
+        <v>6385110</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174195</v>
+        <v>127174150</v>
       </c>
       <c r="B8" t="n">
-        <v>98479</v>
+        <v>98466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725722</v>
+        <v>725532</v>
       </c>
       <c r="R8" t="n">
-        <v>6385158</v>
+        <v>6385259</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>98479</v>
+        <v>107325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R11" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174172</v>
+        <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>107325</v>
+        <v>98479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725473</v>
+        <v>725522</v>
       </c>
       <c r="R12" t="n">
-        <v>6385147</v>
+        <v>6385261</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B13" t="n">
-        <v>5492</v>
+        <v>109267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,37 +1911,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R13" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,11 +1982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1986,6 +1990,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2002,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B14" t="n">
-        <v>109267</v>
+        <v>5492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,46 +2022,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R14" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,6 +2084,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2092,11 +2097,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127174192</v>
+        <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98479</v>
+        <v>98465</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725752</v>
+        <v>725840</v>
       </c>
       <c r="R20" t="n">
-        <v>6385124</v>
+        <v>6385253</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127174206</v>
+        <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725840</v>
+        <v>725752</v>
       </c>
       <c r="R21" t="n">
-        <v>6385253</v>
+        <v>6385124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109267</v>
+        <v>98479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B46" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R46" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,42 +5677,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174182</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>109267</v>
+        <v>98479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725616</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385121</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>109267</v>
+        <v>107325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,34 +6128,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R51" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,11 +6199,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6224,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>107325</v>
+        <v>109267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,43 +6239,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R52" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,6 +6301,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>98479</v>
+        <v>107325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R55" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,6 +6639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6650,7 +6655,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6668,10 +6673,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98479</v>
+        <v>98465</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,26 +6684,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6712,13 +6717,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R56" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6750,6 +6755,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6761,7 +6771,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6779,37 +6789,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>107325</v>
+        <v>98479</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6823,10 +6833,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R57" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6861,11 +6871,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6895,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6906,26 +6911,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6939,13 +6944,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R58" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6977,11 +6982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -1012,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174195</v>
+        <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>98479</v>
+        <v>107325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725722</v>
+        <v>725566</v>
       </c>
       <c r="R5" t="n">
-        <v>6385158</v>
+        <v>6385110</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174187</v>
+        <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98479</v>
+        <v>98466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725669</v>
+        <v>725532</v>
       </c>
       <c r="R6" t="n">
-        <v>6385120</v>
+        <v>6385259</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174179</v>
+        <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>107325</v>
+        <v>98479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725566</v>
+        <v>725722</v>
       </c>
       <c r="R7" t="n">
-        <v>6385110</v>
+        <v>6385158</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174150</v>
+        <v>127174187</v>
       </c>
       <c r="B8" t="n">
-        <v>98466</v>
+        <v>98479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725532</v>
+        <v>725669</v>
       </c>
       <c r="R8" t="n">
-        <v>6385259</v>
+        <v>6385120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>109267</v>
+        <v>5492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,46 +1911,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R13" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,6 +1973,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1986,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2011,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>109267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2013,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R14" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,11 +2084,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2097,6 +2092,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -3566,42 +3566,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174207</v>
+        <v>127174166</v>
       </c>
       <c r="B28" t="n">
-        <v>98418</v>
+        <v>109267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725831</v>
+        <v>725442</v>
       </c>
       <c r="R28" t="n">
-        <v>6385246</v>
+        <v>6385186</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,37 +3677,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174145</v>
+        <v>127174207</v>
       </c>
       <c r="B29" t="n">
-        <v>107325</v>
+        <v>98418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725591</v>
+        <v>725831</v>
       </c>
       <c r="R29" t="n">
-        <v>6385252</v>
+        <v>6385246</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3775,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3793,37 +3788,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174168</v>
+        <v>127174145</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>107325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3837,13 +3832,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725457</v>
+        <v>725591</v>
       </c>
       <c r="R30" t="n">
-        <v>6385181</v>
+        <v>6385252</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3873,6 +3868,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,27 +3904,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174166</v>
+        <v>127174168</v>
       </c>
       <c r="B31" t="n">
-        <v>109267</v>
+        <v>98471</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725442</v>
+        <v>725457</v>
       </c>
       <c r="R31" t="n">
-        <v>6385186</v>
+        <v>6385181</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>107325</v>
+        <v>109267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R33" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,6 +4208,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4237,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>109267</v>
+        <v>107325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,31 +4253,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4281,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R34" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,11 +4324,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4682,38 +4682,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174757</v>
+        <v>127174162</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>98418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>219797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725778</v>
+        <v>725433</v>
       </c>
       <c r="R38" t="n">
-        <v>6385123</v>
+        <v>6385211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,11 +4764,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4773,6 +4772,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4900,42 +4904,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B40" t="n">
-        <v>98418</v>
+        <v>57654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R40" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4982,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4990,11 +4995,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5455,42 +5455,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174186</v>
+        <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>98480</v>
+        <v>109267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725669</v>
+        <v>725616</v>
       </c>
       <c r="R45" t="n">
-        <v>6385120</v>
+        <v>6385121</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>109267</v>
+        <v>98480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R46" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109267</v>
+        <v>98479</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127174206</v>
+        <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725840</v>
+        <v>725752</v>
       </c>
       <c r="R20" t="n">
-        <v>6385253</v>
+        <v>6385124</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127174192</v>
+        <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98479</v>
+        <v>98465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725752</v>
+        <v>725840</v>
       </c>
       <c r="R21" t="n">
-        <v>6385124</v>
+        <v>6385253</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -4682,42 +4682,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>98418</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R38" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,6 +4760,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4772,11 +4773,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4793,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107325</v>
+        <v>98418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4904,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174757</v>
+        <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>107325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,27 +4911,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725778</v>
+        <v>725722</v>
       </c>
       <c r="R40" t="n">
-        <v>6385123</v>
+        <v>6385158</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4982,11 +4982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4995,6 +4990,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkblandskog av blandad ålder.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109267</v>
+        <v>98479</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174203</v>
+        <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>98335</v>
+        <v>98479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,26 +2124,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725843</v>
+        <v>725758</v>
       </c>
       <c r="R15" t="n">
-        <v>6385204</v>
+        <v>6385124</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174178</v>
+        <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>107325</v>
+        <v>98335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725542</v>
+        <v>725843</v>
       </c>
       <c r="R16" t="n">
-        <v>6385111</v>
+        <v>6385204</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174217</v>
+        <v>127174178</v>
       </c>
       <c r="B17" t="n">
         <v>107325</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725732</v>
+        <v>725542</v>
       </c>
       <c r="R17" t="n">
-        <v>6385256</v>
+        <v>6385111</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174220</v>
+        <v>127174217</v>
       </c>
       <c r="B18" t="n">
         <v>107325</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725734</v>
+        <v>725732</v>
       </c>
       <c r="R18" t="n">
-        <v>6385261</v>
+        <v>6385256</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,11 +2526,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,37 +2557,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174194</v>
+        <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>98479</v>
+        <v>107325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725758</v>
+        <v>725734</v>
       </c>
       <c r="R19" t="n">
-        <v>6385124</v>
+        <v>6385261</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,6 +2639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3566,42 +3566,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174166</v>
+        <v>127174193</v>
       </c>
       <c r="B28" t="n">
-        <v>109267</v>
+        <v>105478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725442</v>
+        <v>725758</v>
       </c>
       <c r="R28" t="n">
-        <v>6385186</v>
+        <v>6385124</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,42 +3677,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174207</v>
+        <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>98418</v>
+        <v>109267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725831</v>
+        <v>725442</v>
       </c>
       <c r="R29" t="n">
-        <v>6385246</v>
+        <v>6385186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3788,37 +3788,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174145</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>107325</v>
+        <v>98418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725591</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385252</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3870,11 +3870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3904,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174168</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>98471</v>
+        <v>107325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725457</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385181</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3984,6 +3979,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174193</v>
+        <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>105478</v>
+        <v>98471</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,26 +4026,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725758</v>
+        <v>725457</v>
       </c>
       <c r="R32" t="n">
-        <v>6385124</v>
+        <v>6385181</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109267</v>
+        <v>98479</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98479</v>
+        <v>109267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127174187</v>
       </c>
       <c r="B8" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>98335</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127174178</v>
       </c>
       <c r="B17" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>127174217</v>
       </c>
       <c r="B18" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98480</v>
+        <v>98484</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98471</v>
+        <v>98475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174193</v>
+        <v>127174207</v>
       </c>
       <c r="B28" t="n">
-        <v>105478</v>
+        <v>98422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,26 +3577,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725758</v>
+        <v>725831</v>
       </c>
       <c r="R28" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174166</v>
+        <v>127174145</v>
       </c>
       <c r="B29" t="n">
-        <v>109267</v>
+        <v>107331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,31 +3688,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725442</v>
+        <v>725591</v>
       </c>
       <c r="R29" t="n">
-        <v>6385186</v>
+        <v>6385252</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,6 +3757,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174168</v>
       </c>
       <c r="B30" t="n">
-        <v>98418</v>
+        <v>98475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,21 +3804,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3832,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725457</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385181</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,10 +3904,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174166</v>
       </c>
       <c r="B31" t="n">
-        <v>107325</v>
+        <v>109273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,31 +3915,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3943,13 +3948,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725442</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385186</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,11 +3984,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174168</v>
+        <v>127174193</v>
       </c>
       <c r="B32" t="n">
-        <v>98471</v>
+        <v>105484</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,26 +4026,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725457</v>
+        <v>725758</v>
       </c>
       <c r="R32" t="n">
-        <v>6385181</v>
+        <v>6385124</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B33" t="n">
-        <v>109267</v>
+        <v>107331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R33" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,11 +4208,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4224,7 +4219,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B34" t="n">
-        <v>107325</v>
+        <v>109273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,31 +4248,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4286,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R34" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,6 +4319,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
         <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,38 +4682,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174757</v>
+        <v>127174162</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>98422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>219797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725778</v>
+        <v>725433</v>
       </c>
       <c r="R38" t="n">
-        <v>6385123</v>
+        <v>6385211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,11 +4764,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4773,6 +4772,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4789,37 +4793,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B39" t="n">
-        <v>98418</v>
+        <v>107331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4833,13 +4837,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R39" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4886,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4900,10 +4904,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174196</v>
+        <v>127174757</v>
       </c>
       <c r="B40" t="n">
-        <v>107325</v>
+        <v>57658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4911,31 +4915,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725722</v>
+        <v>725778</v>
       </c>
       <c r="R40" t="n">
-        <v>6385158</v>
+        <v>6385123</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4982,6 +4982,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4990,11 +4995,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkblandskog av blandad ålder.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98418</v>
+        <v>98422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5344,37 +5344,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174177</v>
+        <v>127174183</v>
       </c>
       <c r="B44" t="n">
-        <v>107325</v>
+        <v>98483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725520</v>
+        <v>725652</v>
       </c>
       <c r="R44" t="n">
-        <v>6385121</v>
+        <v>6385115</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B45" t="n">
-        <v>109267</v>
+        <v>107331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,31 +5466,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R45" t="n">
         <v>6385121</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5569,7 +5569,7 @@
         <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>98480</v>
+        <v>98484</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,42 +5677,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B47" t="n">
-        <v>98479</v>
+        <v>109273</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98479</v>
+        <v>109273</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109267</v>
+        <v>98483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98465</v>
+        <v>98469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R2" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B3" t="n">
-        <v>107331</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R3" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1012,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174179</v>
+        <v>127174195</v>
       </c>
       <c r="B5" t="n">
-        <v>107331</v>
+        <v>98483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725566</v>
+        <v>725722</v>
       </c>
       <c r="R5" t="n">
-        <v>6385110</v>
+        <v>6385158</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174150</v>
+        <v>127174187</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725532</v>
+        <v>725669</v>
       </c>
       <c r="R6" t="n">
-        <v>6385259</v>
+        <v>6385120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174195</v>
+        <v>127174179</v>
       </c>
       <c r="B7" t="n">
-        <v>98483</v>
+        <v>107331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725722</v>
+        <v>725566</v>
       </c>
       <c r="R7" t="n">
-        <v>6385158</v>
+        <v>6385110</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174187</v>
+        <v>127174150</v>
       </c>
       <c r="B8" t="n">
-        <v>98483</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,26 +1356,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725669</v>
+        <v>725532</v>
       </c>
       <c r="R8" t="n">
-        <v>6385120</v>
+        <v>6385259</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174224</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>107331</v>
+        <v>98483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725647</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385302</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174155</v>
+        <v>127174224</v>
       </c>
       <c r="B12" t="n">
-        <v>98483</v>
+        <v>107331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725522</v>
+        <v>725647</v>
       </c>
       <c r="R12" t="n">
-        <v>6385261</v>
+        <v>6385302</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>109273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,37 +1911,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R13" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,11 +1982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1986,6 +1990,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2002,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B14" t="n">
-        <v>109273</v>
+        <v>5493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,46 +2022,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R14" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,6 +2084,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2092,11 +2097,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174194</v>
+        <v>127174178</v>
       </c>
       <c r="B15" t="n">
-        <v>98483</v>
+        <v>107331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725758</v>
+        <v>725542</v>
       </c>
       <c r="R15" t="n">
-        <v>6385124</v>
+        <v>6385111</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174203</v>
+        <v>127174217</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>107331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R16" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174178</v>
+        <v>127174220</v>
       </c>
       <c r="B17" t="n">
         <v>107331</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725542</v>
+        <v>725734</v>
       </c>
       <c r="R17" t="n">
-        <v>6385111</v>
+        <v>6385261</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,6 +2417,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2433,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,37 +2451,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B18" t="n">
-        <v>107331</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R18" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2539,7 +2544,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2557,37 +2562,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174220</v>
+        <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>107331</v>
+        <v>98483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2601,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725734</v>
+        <v>725758</v>
       </c>
       <c r="R19" t="n">
-        <v>6385261</v>
+        <v>6385124</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,11 +2644,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127174192</v>
+        <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98483</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725752</v>
+        <v>725840</v>
       </c>
       <c r="R20" t="n">
-        <v>6385124</v>
+        <v>6385253</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127174206</v>
+        <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725840</v>
+        <v>725752</v>
       </c>
       <c r="R21" t="n">
-        <v>6385253</v>
+        <v>6385124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B22" t="n">
-        <v>98484</v>
+        <v>107331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R22" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B23" t="n">
-        <v>107331</v>
+        <v>98484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R23" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
         <v>98483</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B27" t="n">
         <v>98483</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R27" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174207</v>
+        <v>127174168</v>
       </c>
       <c r="B28" t="n">
-        <v>98422</v>
+        <v>98475</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725831</v>
+        <v>725457</v>
       </c>
       <c r="R28" t="n">
-        <v>6385246</v>
+        <v>6385181</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174145</v>
+        <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>107331</v>
+        <v>109273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,31 +3688,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725591</v>
+        <v>725442</v>
       </c>
       <c r="R29" t="n">
-        <v>6385252</v>
+        <v>6385186</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,11 +3757,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3793,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174168</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>98475</v>
+        <v>98422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,21 +3799,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3837,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725457</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385181</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3904,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174166</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>109273</v>
+        <v>107331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,31 +3910,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725442</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385186</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3984,6 +3979,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4353,48 +4353,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>109273</v>
+        <v>98483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R35" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4424,11 +4433,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,57 +4464,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>98483</v>
+        <v>109273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R36" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,37 +4682,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B38" t="n">
-        <v>98422</v>
+        <v>107331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R38" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4793,37 +4793,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107331</v>
+        <v>98422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B41" t="n">
-        <v>107331</v>
+        <v>98422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R41" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B43" t="n">
-        <v>98422</v>
+        <v>107331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R43" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5455,37 +5455,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174177</v>
+        <v>127174186</v>
       </c>
       <c r="B45" t="n">
-        <v>107331</v>
+        <v>98484</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725520</v>
+        <v>725669</v>
       </c>
       <c r="R45" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174186</v>
+        <v>127174182</v>
       </c>
       <c r="B46" t="n">
-        <v>98484</v>
+        <v>109273</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725669</v>
+        <v>725616</v>
       </c>
       <c r="R46" t="n">
-        <v>6385120</v>
+        <v>6385121</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B47" t="n">
-        <v>109273</v>
+        <v>107331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R47" t="n">
         <v>6385121</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B48" t="n">
-        <v>107331</v>
+        <v>109273</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,46 +5799,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5870,6 +5861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5881,7 +5877,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5899,10 +5895,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B49" t="n">
-        <v>109273</v>
+        <v>107331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,37 +5906,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5972,11 +5977,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174173</v>
+        <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>98483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725473</v>
+        <v>725532</v>
       </c>
       <c r="R25" t="n">
-        <v>6385147</v>
+        <v>6385259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3326,7 +3321,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3344,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174147</v>
+        <v>127174173</v>
       </c>
       <c r="B26" t="n">
-        <v>98483</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,26 +3350,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3388,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725549</v>
+        <v>725473</v>
       </c>
       <c r="R26" t="n">
-        <v>6385258</v>
+        <v>6385147</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3426,6 +3421,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B27" t="n">
         <v>98483</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R27" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174155</v>
+        <v>127174209</v>
       </c>
       <c r="B9" t="n">
-        <v>98483</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725522</v>
+        <v>725832</v>
       </c>
       <c r="R9" t="n">
-        <v>6385261</v>
+        <v>6385251</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174209</v>
+        <v>127174172</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>107331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725832</v>
+        <v>725473</v>
       </c>
       <c r="R10" t="n">
-        <v>6385251</v>
+        <v>6385147</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174172</v>
+        <v>127174224</v>
       </c>
       <c r="B11" t="n">
         <v>107331</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725473</v>
+        <v>725647</v>
       </c>
       <c r="R11" t="n">
-        <v>6385147</v>
+        <v>6385302</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174224</v>
+        <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>107331</v>
+        <v>98483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725647</v>
+        <v>725522</v>
       </c>
       <c r="R12" t="n">
-        <v>6385302</v>
+        <v>6385261</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174178</v>
+        <v>127174217</v>
       </c>
       <c r="B15" t="n">
         <v>107331</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725542</v>
+        <v>725732</v>
       </c>
       <c r="R15" t="n">
-        <v>6385111</v>
+        <v>6385256</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174217</v>
+        <v>127174220</v>
       </c>
       <c r="B16" t="n">
         <v>107331</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725732</v>
+        <v>725734</v>
       </c>
       <c r="R16" t="n">
-        <v>6385256</v>
+        <v>6385261</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2304,6 +2304,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,37 +2340,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174220</v>
+        <v>127174203</v>
       </c>
       <c r="B17" t="n">
-        <v>107331</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2384,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725734</v>
+        <v>725843</v>
       </c>
       <c r="R17" t="n">
-        <v>6385261</v>
+        <v>6385204</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,11 +2422,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2451,37 +2451,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174203</v>
+        <v>127174178</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>107331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725843</v>
+        <v>725542</v>
       </c>
       <c r="R18" t="n">
-        <v>6385204</v>
+        <v>6385111</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>107331</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R2" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>107333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R3" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127174195</v>
       </c>
       <c r="B5" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127174187</v>
       </c>
       <c r="B6" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>127174179</v>
       </c>
       <c r="B7" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127174150</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174209</v>
+        <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>107333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725832</v>
+        <v>725647</v>
       </c>
       <c r="R9" t="n">
-        <v>6385251</v>
+        <v>6385302</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174172</v>
+        <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>107331</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725473</v>
+        <v>725832</v>
       </c>
       <c r="R10" t="n">
-        <v>6385147</v>
+        <v>6385251</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174224</v>
+        <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725647</v>
+        <v>725473</v>
       </c>
       <c r="R11" t="n">
-        <v>6385302</v>
+        <v>6385147</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>109273</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,46 +1911,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R13" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,6 +1973,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1986,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2011,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>5493</v>
+        <v>109275</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2013,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R14" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,11 +2084,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2097,6 +2092,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>107331</v>
+        <v>98340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R15" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174220</v>
+        <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725734</v>
+        <v>725542</v>
       </c>
       <c r="R16" t="n">
-        <v>6385261</v>
+        <v>6385111</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,11 +2306,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2322,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2340,37 +2335,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174203</v>
+        <v>127174217</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>107333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2384,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R17" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2433,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174178</v>
+        <v>127174220</v>
       </c>
       <c r="B18" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725542</v>
+        <v>725734</v>
       </c>
       <c r="R18" t="n">
-        <v>6385111</v>
+        <v>6385261</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,6 +2528,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
         <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>107331</v>
+        <v>98485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R22" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>98484</v>
+        <v>107333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R23" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98475</v>
+        <v>98476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174173</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3350,26 +3350,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725473</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385147</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3421,11 +3421,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3437,7 +3432,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3455,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174147</v>
+        <v>127174173</v>
       </c>
       <c r="B27" t="n">
-        <v>98483</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,26 +3461,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725549</v>
+        <v>725473</v>
       </c>
       <c r="R27" t="n">
-        <v>6385258</v>
+        <v>6385147</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3532,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,27 +3566,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174168</v>
+        <v>127174166</v>
       </c>
       <c r="B28" t="n">
-        <v>98475</v>
+        <v>109275</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725457</v>
+        <v>725442</v>
       </c>
       <c r="R28" t="n">
-        <v>6385181</v>
+        <v>6385186</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3677,42 +3677,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174166</v>
+        <v>127174207</v>
       </c>
       <c r="B29" t="n">
-        <v>109273</v>
+        <v>98423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725442</v>
+        <v>725831</v>
       </c>
       <c r="R29" t="n">
-        <v>6385186</v>
+        <v>6385246</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3788,37 +3788,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174145</v>
       </c>
       <c r="B30" t="n">
-        <v>98422</v>
+        <v>107333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725591</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385252</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3870,6 +3870,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,37 +3904,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174168</v>
       </c>
       <c r="B31" t="n">
-        <v>107331</v>
+        <v>98476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3943,13 +3948,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725457</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385181</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,11 +3984,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4018,7 +4018,7 @@
         <v>127174193</v>
       </c>
       <c r="B32" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>107331</v>
+        <v>109275</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R33" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,6 +4208,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4237,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>109273</v>
+        <v>107333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,31 +4253,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4281,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R34" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,11 +4324,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98483</v>
+        <v>109275</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109273</v>
+        <v>98484</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,37 +4682,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B38" t="n">
-        <v>107331</v>
+        <v>98423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R38" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4793,37 +4793,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B39" t="n">
-        <v>98422</v>
+        <v>107333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R39" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>98422</v>
+        <v>107333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R41" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>107331</v>
+        <v>98423</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R43" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,37 +5344,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174183</v>
+        <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>98483</v>
+        <v>107333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725652</v>
+        <v>725520</v>
       </c>
       <c r="R44" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5455,42 +5455,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174186</v>
+        <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>98484</v>
+        <v>109275</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725669</v>
+        <v>725616</v>
       </c>
       <c r="R45" t="n">
-        <v>6385120</v>
+        <v>6385121</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174182</v>
+        <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>109273</v>
+        <v>98485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725616</v>
+        <v>725669</v>
       </c>
       <c r="R46" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,37 +5677,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174177</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>107331</v>
+        <v>98484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725520</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385121</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>109273</v>
+        <v>107333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,37 +5799,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,11 +5870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5895,10 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>107331</v>
+        <v>109275</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,46 +5910,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,6 +5972,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109273</v>
+        <v>98484</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98483</v>
+        <v>109275</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174224</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>107333</v>
+        <v>98484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725647</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385302</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174209</v>
+        <v>127174224</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>107333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725832</v>
+        <v>725647</v>
       </c>
       <c r="R10" t="n">
-        <v>6385251</v>
+        <v>6385302</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174172</v>
+        <v>127174209</v>
       </c>
       <c r="B11" t="n">
-        <v>107333</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725473</v>
+        <v>725832</v>
       </c>
       <c r="R11" t="n">
-        <v>6385147</v>
+        <v>6385251</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B12" t="n">
-        <v>98484</v>
+        <v>107333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R12" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4682,42 +4682,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>98423</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R38" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,6 +4760,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4772,11 +4773,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4793,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107333</v>
+        <v>98423</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4904,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174757</v>
+        <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>57658</v>
+        <v>107333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,27 +4911,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725778</v>
+        <v>725722</v>
       </c>
       <c r="R40" t="n">
-        <v>6385123</v>
+        <v>6385158</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4982,11 +4982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4995,6 +4990,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkblandskog av blandad ålder.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B51" t="n">
-        <v>107333</v>
+        <v>109275</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,43 +6128,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R51" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,6 +6190,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6210,7 +6206,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6228,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B52" t="n">
-        <v>109275</v>
+        <v>107333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6239,34 +6235,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R52" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6301,11 +6306,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98484</v>
+        <v>109275</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109275</v>
+        <v>98484</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>107335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R2" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B3" t="n">
-        <v>107333</v>
+        <v>98472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R3" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174604</v>
+        <v>127174179</v>
       </c>
       <c r="B4" t="n">
-        <v>96050</v>
+        <v>107335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725732</v>
+        <v>725566</v>
       </c>
       <c r="R4" t="n">
-        <v>6385256</v>
+        <v>6385110</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,13 +985,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1012,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174195</v>
+        <v>127174150</v>
       </c>
       <c r="B5" t="n">
-        <v>98484</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,26 +1019,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725722</v>
+        <v>725532</v>
       </c>
       <c r="R5" t="n">
-        <v>6385158</v>
+        <v>6385259</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1126,7 +1122,7 @@
         <v>127174187</v>
       </c>
       <c r="B6" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,37 +1230,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174179</v>
+        <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>107333</v>
+        <v>98486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725566</v>
+        <v>725722</v>
       </c>
       <c r="R7" t="n">
-        <v>6385110</v>
+        <v>6385158</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174150</v>
+        <v>127174604</v>
       </c>
       <c r="B8" t="n">
-        <v>98471</v>
+        <v>96052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,46 +1352,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725532</v>
+        <v>725732</v>
       </c>
       <c r="R8" t="n">
-        <v>6385259</v>
+        <v>6385256</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1432,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174155</v>
+        <v>127174209</v>
       </c>
       <c r="B9" t="n">
-        <v>98484</v>
+        <v>98472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725522</v>
+        <v>725832</v>
       </c>
       <c r="R9" t="n">
-        <v>6385261</v>
+        <v>6385251</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174224</v>
+        <v>127174172</v>
       </c>
       <c r="B10" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725647</v>
+        <v>725473</v>
       </c>
       <c r="R10" t="n">
-        <v>6385302</v>
+        <v>6385147</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174209</v>
+        <v>127174155</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725832</v>
+        <v>725522</v>
       </c>
       <c r="R11" t="n">
-        <v>6385251</v>
+        <v>6385261</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174172</v>
+        <v>127174224</v>
       </c>
       <c r="B12" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725473</v>
+        <v>725647</v>
       </c>
       <c r="R12" t="n">
-        <v>6385147</v>
+        <v>6385302</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174203</v>
+        <v>127174178</v>
       </c>
       <c r="B15" t="n">
-        <v>98340</v>
+        <v>107335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725843</v>
+        <v>725542</v>
       </c>
       <c r="R15" t="n">
-        <v>6385204</v>
+        <v>6385111</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174178</v>
+        <v>127174217</v>
       </c>
       <c r="B16" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725542</v>
+        <v>725732</v>
       </c>
       <c r="R16" t="n">
-        <v>6385111</v>
+        <v>6385256</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174217</v>
+        <v>127174220</v>
       </c>
       <c r="B17" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725732</v>
+        <v>725734</v>
       </c>
       <c r="R17" t="n">
-        <v>6385256</v>
+        <v>6385261</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,6 +2415,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,37 +2451,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174220</v>
+        <v>127174203</v>
       </c>
       <c r="B18" t="n">
-        <v>107333</v>
+        <v>98342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2495,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725734</v>
+        <v>725843</v>
       </c>
       <c r="R18" t="n">
-        <v>6385261</v>
+        <v>6385204</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2528,11 +2533,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
         <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127174206</v>
+        <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725840</v>
+        <v>725752</v>
       </c>
       <c r="R20" t="n">
-        <v>6385253</v>
+        <v>6385124</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127174192</v>
+        <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98484</v>
+        <v>98472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725752</v>
+        <v>725840</v>
       </c>
       <c r="R21" t="n">
-        <v>6385124</v>
+        <v>6385253</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B22" t="n">
-        <v>98485</v>
+        <v>107335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R22" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B23" t="n">
-        <v>107333</v>
+        <v>98487</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R23" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174152</v>
+        <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98484</v>
+        <v>98472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725532</v>
+        <v>725473</v>
       </c>
       <c r="R25" t="n">
-        <v>6385259</v>
+        <v>6385147</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3339,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3374,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R26" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3450,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174173</v>
+        <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,26 +3466,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3494,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725473</v>
+        <v>725549</v>
       </c>
       <c r="R27" t="n">
-        <v>6385147</v>
+        <v>6385258</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3532,11 +3537,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,27 +3566,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174166</v>
+        <v>127174168</v>
       </c>
       <c r="B28" t="n">
-        <v>109275</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725442</v>
+        <v>725457</v>
       </c>
       <c r="R28" t="n">
-        <v>6385186</v>
+        <v>6385181</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3677,42 +3677,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174207</v>
+        <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>98423</v>
+        <v>109277</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725831</v>
+        <v>725442</v>
       </c>
       <c r="R29" t="n">
-        <v>6385246</v>
+        <v>6385186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3788,37 +3788,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174145</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>107333</v>
+        <v>98425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725591</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385252</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3870,11 +3870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3904,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174168</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>98476</v>
+        <v>107335</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725457</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385181</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3984,6 +3979,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4018,7 +4018,7 @@
         <v>127174193</v>
       </c>
       <c r="B32" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B33" t="n">
-        <v>109275</v>
+        <v>107335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R33" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,11 +4208,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4224,7 +4219,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B34" t="n">
-        <v>107333</v>
+        <v>109277</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,31 +4248,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4286,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R34" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,6 +4319,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,48 +4353,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>109275</v>
+        <v>98486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R35" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4424,11 +4433,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,57 +4464,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>98484</v>
+        <v>109277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R36" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174162</v>
+        <v>127174196</v>
       </c>
       <c r="B39" t="n">
-        <v>98423</v>
+        <v>107335</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725433</v>
+        <v>725722</v>
       </c>
       <c r="R39" t="n">
-        <v>6385211</v>
+        <v>6385158</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4900,37 +4900,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B40" t="n">
-        <v>107333</v>
+        <v>98425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R40" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B41" t="n">
-        <v>107333</v>
+        <v>98425</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R41" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>98472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B43" t="n">
-        <v>98423</v>
+        <v>107335</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R43" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,37 +5344,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174177</v>
+        <v>127174186</v>
       </c>
       <c r="B44" t="n">
-        <v>107333</v>
+        <v>98487</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725520</v>
+        <v>725669</v>
       </c>
       <c r="R44" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5458,7 +5458,7 @@
         <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5566,37 +5566,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174186</v>
+        <v>127174177</v>
       </c>
       <c r="B46" t="n">
-        <v>98485</v>
+        <v>107335</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725669</v>
+        <v>725520</v>
       </c>
       <c r="R46" t="n">
-        <v>6385120</v>
+        <v>6385121</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
         <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B48" t="n">
-        <v>107333</v>
+        <v>109277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,46 +5799,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5870,6 +5861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5881,7 +5877,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5899,10 +5895,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B49" t="n">
-        <v>109275</v>
+        <v>107335</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,37 +5906,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5972,11 +5977,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>109275</v>
+        <v>107335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,34 +6128,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R51" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,11 +6199,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6224,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>107333</v>
+        <v>109277</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,43 +6239,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R52" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,6 +6301,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
         <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B55" t="n">
-        <v>107333</v>
+        <v>98486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R55" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,11 +6639,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6655,7 +6650,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6673,10 +6668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>98486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,26 +6679,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6717,13 +6712,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R56" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,11 +6750,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6771,7 +6761,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6789,37 +6779,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B57" t="n">
-        <v>98484</v>
+        <v>107335</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6833,10 +6823,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R57" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6871,6 +6861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6900,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B58" t="n">
-        <v>98484</v>
+        <v>98472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,26 +6906,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6944,13 +6939,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R58" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6982,6 +6977,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -897,57 +897,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174179</v>
+        <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>107335</v>
+        <v>96052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725566</v>
+        <v>725732</v>
       </c>
       <c r="R4" t="n">
-        <v>6385110</v>
+        <v>6385256</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +988,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174150</v>
+        <v>127174195</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,26 +1023,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725532</v>
+        <v>725722</v>
       </c>
       <c r="R5" t="n">
-        <v>6385259</v>
+        <v>6385158</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1230,37 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174195</v>
+        <v>127174179</v>
       </c>
       <c r="B7" t="n">
-        <v>98486</v>
+        <v>107335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725722</v>
+        <v>725566</v>
       </c>
       <c r="R7" t="n">
-        <v>6385158</v>
+        <v>6385110</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174604</v>
+        <v>127174150</v>
       </c>
       <c r="B8" t="n">
-        <v>96052</v>
+        <v>98473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,49 +1356,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725732</v>
+        <v>725532</v>
       </c>
       <c r="R8" t="n">
-        <v>6385256</v>
+        <v>6385259</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,13 +1433,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174209</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>98472</v>
+        <v>98486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725832</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385251</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174172</v>
+        <v>127174224</v>
       </c>
       <c r="B10" t="n">
         <v>107335</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725473</v>
+        <v>725647</v>
       </c>
       <c r="R10" t="n">
-        <v>6385147</v>
+        <v>6385302</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>98486</v>
+        <v>107335</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R11" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B12" t="n">
-        <v>107335</v>
+        <v>98472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R12" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>109277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,37 +1911,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R13" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,11 +1982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1986,6 +1990,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2002,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B14" t="n">
-        <v>109277</v>
+        <v>5493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,46 +2022,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R14" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,6 +2084,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2092,11 +2097,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2113,37 +2113,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174178</v>
+        <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>107335</v>
+        <v>98486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725542</v>
+        <v>725758</v>
       </c>
       <c r="R15" t="n">
-        <v>6385111</v>
+        <v>6385124</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174217</v>
+        <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>107335</v>
+        <v>98342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R16" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174220</v>
+        <v>127174178</v>
       </c>
       <c r="B17" t="n">
         <v>107335</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725734</v>
+        <v>725542</v>
       </c>
       <c r="R17" t="n">
-        <v>6385261</v>
+        <v>6385111</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,11 +2417,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2451,37 +2446,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174203</v>
+        <v>127174217</v>
       </c>
       <c r="B18" t="n">
-        <v>98342</v>
+        <v>107335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R18" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2544,7 +2539,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2562,37 +2557,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174194</v>
+        <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>98486</v>
+        <v>107335</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725758</v>
+        <v>725734</v>
       </c>
       <c r="R19" t="n">
-        <v>6385124</v>
+        <v>6385261</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,6 +2639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3566,27 +3566,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174168</v>
+        <v>127174166</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>109277</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725457</v>
+        <v>725442</v>
       </c>
       <c r="R28" t="n">
-        <v>6385181</v>
+        <v>6385186</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174166</v>
+        <v>127174145</v>
       </c>
       <c r="B29" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,31 +3688,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725442</v>
+        <v>725591</v>
       </c>
       <c r="R29" t="n">
-        <v>6385186</v>
+        <v>6385252</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,6 +3757,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174193</v>
       </c>
       <c r="B30" t="n">
-        <v>98425</v>
+        <v>105488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,26 +3804,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3832,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725758</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385124</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3899,37 +3904,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174207</v>
       </c>
       <c r="B31" t="n">
-        <v>107335</v>
+        <v>98425</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3943,13 +3948,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725831</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385246</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3981,11 +3986,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174193</v>
+        <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>105488</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,26 +4026,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725758</v>
+        <v>725457</v>
       </c>
       <c r="R32" t="n">
-        <v>6385124</v>
+        <v>6385181</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R33" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,6 +4208,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4237,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,31 +4253,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4281,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R34" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,11 +4324,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4682,38 +4682,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174757</v>
+        <v>127174162</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>98425</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>219797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725778</v>
+        <v>725433</v>
       </c>
       <c r="R38" t="n">
-        <v>6385123</v>
+        <v>6385211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,11 +4764,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4773,6 +4772,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4900,42 +4904,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B40" t="n">
-        <v>98425</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R40" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4982,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4990,11 +4995,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174197</v>
+        <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>98425</v>
+        <v>107335</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725722</v>
+        <v>725513</v>
       </c>
       <c r="R41" t="n">
-        <v>6385158</v>
+        <v>6385250</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127174208</v>
+        <v>127174197</v>
       </c>
       <c r="B42" t="n">
-        <v>98472</v>
+        <v>98425</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,26 +5133,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219862</v>
+        <v>219797</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>725831</v>
+        <v>725722</v>
       </c>
       <c r="R42" t="n">
-        <v>6385246</v>
+        <v>6385158</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174158</v>
+        <v>127174208</v>
       </c>
       <c r="B43" t="n">
-        <v>107335</v>
+        <v>98472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725513</v>
+        <v>725831</v>
       </c>
       <c r="R43" t="n">
-        <v>6385250</v>
+        <v>6385246</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B44" t="n">
-        <v>98487</v>
+        <v>98486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R44" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B45" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,31 +5466,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R45" t="n">
         <v>6385121</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174177</v>
+        <v>127174182</v>
       </c>
       <c r="B46" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,31 +5577,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725520</v>
+        <v>725616</v>
       </c>
       <c r="R46" t="n">
         <v>6385121</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174186</v>
       </c>
       <c r="B47" t="n">
-        <v>98486</v>
+        <v>98487</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>219875</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725669</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,37 +5799,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,11 +5870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5895,10 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,46 +5910,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,6 +5972,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109277</v>
+        <v>98486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174158</v>
+        <v>127174208</v>
       </c>
       <c r="B41" t="n">
-        <v>107335</v>
+        <v>98472</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725513</v>
+        <v>725831</v>
       </c>
       <c r="R41" t="n">
-        <v>6385250</v>
+        <v>6385246</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174208</v>
+        <v>127174158</v>
       </c>
       <c r="B43" t="n">
-        <v>98472</v>
+        <v>107335</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725831</v>
+        <v>725513</v>
       </c>
       <c r="R43" t="n">
-        <v>6385246</v>
+        <v>6385250</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127174189</v>
+        <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>107335</v>
+        <v>98472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725683</v>
+        <v>725835</v>
       </c>
       <c r="R2" t="n">
-        <v>6385125</v>
+        <v>6385243</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,37 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174205</v>
+        <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>98472</v>
+        <v>107335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725835</v>
+        <v>725683</v>
       </c>
       <c r="R3" t="n">
-        <v>6385243</v>
+        <v>6385125</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174604</v>
+        <v>127174179</v>
       </c>
       <c r="B4" t="n">
-        <v>96052</v>
+        <v>107335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725732</v>
+        <v>725566</v>
       </c>
       <c r="R4" t="n">
-        <v>6385256</v>
+        <v>6385110</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,13 +985,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1012,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174195</v>
+        <v>127174150</v>
       </c>
       <c r="B5" t="n">
-        <v>98486</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,26 +1019,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725722</v>
+        <v>725532</v>
       </c>
       <c r="R5" t="n">
-        <v>6385158</v>
+        <v>6385259</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174187</v>
+        <v>127174195</v>
       </c>
       <c r="B6" t="n">
         <v>98486</v>
@@ -1153,7 +1149,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725669</v>
+        <v>725722</v>
       </c>
       <c r="R6" t="n">
-        <v>6385120</v>
+        <v>6385158</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,37 +1230,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174179</v>
+        <v>127174187</v>
       </c>
       <c r="B7" t="n">
-        <v>107335</v>
+        <v>98486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725566</v>
+        <v>725669</v>
       </c>
       <c r="R7" t="n">
-        <v>6385110</v>
+        <v>6385120</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174150</v>
+        <v>127174604</v>
       </c>
       <c r="B8" t="n">
-        <v>98473</v>
+        <v>96052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,46 +1352,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725532</v>
+        <v>725732</v>
       </c>
       <c r="R8" t="n">
-        <v>6385259</v>
+        <v>6385256</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1432,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174155</v>
+        <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>98486</v>
+        <v>107335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725522</v>
+        <v>725647</v>
       </c>
       <c r="R9" t="n">
-        <v>6385261</v>
+        <v>6385302</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>107335</v>
+        <v>98472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R10" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174209</v>
+        <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98472</v>
+        <v>98486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725832</v>
+        <v>725522</v>
       </c>
       <c r="R12" t="n">
-        <v>6385251</v>
+        <v>6385261</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127174171</v>
+        <v>127174657</v>
       </c>
       <c r="B13" t="n">
-        <v>109277</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,46 +1911,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725473</v>
+        <v>725602</v>
       </c>
       <c r="R13" t="n">
-        <v>6385147</v>
+        <v>6385131</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,6 +1973,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Angrep av reliktbock i flera tallar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1986,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2011,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127174657</v>
+        <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>5493</v>
+        <v>109277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2013,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725602</v>
+        <v>725473</v>
       </c>
       <c r="R14" t="n">
-        <v>6385131</v>
+        <v>6385147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,11 +2084,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Angrep av reliktbock i flera tallar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2097,6 +2092,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2895,37 +2895,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127174188</v>
+        <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>107335</v>
+        <v>98487</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725669</v>
+        <v>725522</v>
       </c>
       <c r="R22" t="n">
-        <v>6385120</v>
+        <v>6385261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3006,37 +3006,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174153</v>
+        <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>98487</v>
+        <v>107335</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219875</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725522</v>
+        <v>725669</v>
       </c>
       <c r="R23" t="n">
-        <v>6385261</v>
+        <v>6385120</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174173</v>
+        <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98472</v>
+        <v>98486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725473</v>
+        <v>725532</v>
       </c>
       <c r="R25" t="n">
-        <v>6385147</v>
+        <v>6385259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3326,7 +3321,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3344,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
         <v>98486</v>
@@ -3374,7 +3369,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3388,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174147</v>
+        <v>127174173</v>
       </c>
       <c r="B27" t="n">
-        <v>98486</v>
+        <v>98472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,26 +3461,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725549</v>
+        <v>725473</v>
       </c>
       <c r="R27" t="n">
-        <v>6385258</v>
+        <v>6385147</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3532,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3677,37 +3677,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174145</v>
+        <v>127174193</v>
       </c>
       <c r="B29" t="n">
-        <v>107335</v>
+        <v>105488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725591</v>
+        <v>725758</v>
       </c>
       <c r="R29" t="n">
-        <v>6385252</v>
+        <v>6385124</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3775,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174193</v>
+        <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>105488</v>
+        <v>98425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,26 +3799,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3837,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725758</v>
+        <v>725831</v>
       </c>
       <c r="R30" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3904,37 +3899,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174207</v>
+        <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>98425</v>
+        <v>107335</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725831</v>
+        <v>725591</v>
       </c>
       <c r="R31" t="n">
-        <v>6385246</v>
+        <v>6385252</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3986,6 +3981,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B33" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R33" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,11 +4208,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4224,7 +4219,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B34" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,31 +4248,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4286,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R34" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,6 +4319,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109277</v>
+        <v>98486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,42 +4682,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127174162</v>
+        <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>98425</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4726,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725433</v>
+        <v>725778</v>
       </c>
       <c r="R38" t="n">
-        <v>6385211</v>
+        <v>6385123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,6 +4760,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4772,11 +4773,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalktallskog.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4793,37 +4789,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127174196</v>
+        <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>107335</v>
+        <v>98425</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4837,13 +4833,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725722</v>
+        <v>725433</v>
       </c>
       <c r="R39" t="n">
-        <v>6385158</v>
+        <v>6385211</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4882,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4904,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127174757</v>
+        <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>107335</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,27 +4911,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725778</v>
+        <v>725722</v>
       </c>
       <c r="R40" t="n">
-        <v>6385123</v>
+        <v>6385158</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4982,11 +4982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillkråkehack för födosök i död Högstubbe av tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4995,6 +4990,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkblandskog av blandad ålder.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5011,37 +5011,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127174208</v>
+        <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>98472</v>
+        <v>107335</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725831</v>
+        <v>725513</v>
       </c>
       <c r="R41" t="n">
-        <v>6385246</v>
+        <v>6385250</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127174197</v>
+        <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98425</v>
+        <v>98472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,26 +5133,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219797</v>
+        <v>219862</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>725722</v>
+        <v>725831</v>
       </c>
       <c r="R42" t="n">
-        <v>6385158</v>
+        <v>6385246</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5233,37 +5233,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174158</v>
+        <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>107335</v>
+        <v>98425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725513</v>
+        <v>725722</v>
       </c>
       <c r="R43" t="n">
-        <v>6385250</v>
+        <v>6385158</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5344,42 +5344,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B44" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R44" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,37 +5455,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174177</v>
+        <v>127174183</v>
       </c>
       <c r="B45" t="n">
-        <v>107335</v>
+        <v>98486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725520</v>
+        <v>725652</v>
       </c>
       <c r="R45" t="n">
-        <v>6385121</v>
+        <v>6385115</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B46" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,31 +5577,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R46" t="n">
         <v>6385121</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B48" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,46 +5799,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5870,6 +5861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5881,7 +5877,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5899,10 +5895,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B49" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,37 +5906,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5972,11 +5977,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B51" t="n">
-        <v>107335</v>
+        <v>109277</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,43 +6128,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R51" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,6 +6190,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6210,7 +6206,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6228,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B52" t="n">
-        <v>109277</v>
+        <v>107335</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6239,34 +6235,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R52" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6301,11 +6306,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98486</v>
+        <v>109277</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109277</v>
+        <v>98486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,57 +897,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174179</v>
+        <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>107335</v>
+        <v>96058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725566</v>
+        <v>725732</v>
       </c>
       <c r="R4" t="n">
-        <v>6385110</v>
+        <v>6385256</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +988,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174150</v>
+        <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>107341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725532</v>
+        <v>725566</v>
       </c>
       <c r="R5" t="n">
-        <v>6385259</v>
+        <v>6385110</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174195</v>
+        <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98486</v>
+        <v>98479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725722</v>
+        <v>725532</v>
       </c>
       <c r="R6" t="n">
-        <v>6385158</v>
+        <v>6385259</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174187</v>
+        <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>98486</v>
+        <v>98492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725669</v>
+        <v>725722</v>
       </c>
       <c r="R7" t="n">
-        <v>6385120</v>
+        <v>6385158</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174604</v>
+        <v>127174187</v>
       </c>
       <c r="B8" t="n">
-        <v>96052</v>
+        <v>98492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,49 +1356,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>223621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725732</v>
+        <v>725669</v>
       </c>
       <c r="R8" t="n">
-        <v>6385256</v>
+        <v>6385120</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,13 +1433,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
         <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>98486</v>
+        <v>98492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174194</v>
+        <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>98486</v>
+        <v>98348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,26 +2124,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223621</v>
+        <v>219769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725758</v>
+        <v>725843</v>
       </c>
       <c r="R15" t="n">
-        <v>6385124</v>
+        <v>6385204</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174203</v>
+        <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>98342</v>
+        <v>107341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725843</v>
+        <v>725542</v>
       </c>
       <c r="R16" t="n">
-        <v>6385204</v>
+        <v>6385111</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174178</v>
+        <v>127174217</v>
       </c>
       <c r="B17" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725542</v>
+        <v>725732</v>
       </c>
       <c r="R17" t="n">
-        <v>6385111</v>
+        <v>6385256</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174217</v>
+        <v>127174220</v>
       </c>
       <c r="B18" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725732</v>
+        <v>725734</v>
       </c>
       <c r="R18" t="n">
-        <v>6385256</v>
+        <v>6385261</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,6 +2526,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,37 +2562,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174220</v>
+        <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>107335</v>
+        <v>98492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2601,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725734</v>
+        <v>725758</v>
       </c>
       <c r="R19" t="n">
-        <v>6385261</v>
+        <v>6385124</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,11 +2644,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
         <v>127174192</v>
       </c>
       <c r="B20" t="n">
-        <v>98486</v>
+        <v>98492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174206</v>
       </c>
       <c r="B21" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98487</v>
+        <v>98493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98484</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174152</v>
+        <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98486</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725532</v>
+        <v>725473</v>
       </c>
       <c r="R25" t="n">
-        <v>6385259</v>
+        <v>6385147</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3326,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3339,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174147</v>
+        <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98486</v>
+        <v>98492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3374,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725549</v>
+        <v>725532</v>
       </c>
       <c r="R26" t="n">
-        <v>6385258</v>
+        <v>6385259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3450,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174173</v>
+        <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98472</v>
+        <v>98492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,26 +3466,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3494,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725473</v>
+        <v>725549</v>
       </c>
       <c r="R27" t="n">
-        <v>6385147</v>
+        <v>6385258</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3532,11 +3537,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,42 +3566,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174166</v>
+        <v>127174193</v>
       </c>
       <c r="B28" t="n">
-        <v>109277</v>
+        <v>105494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725442</v>
+        <v>725758</v>
       </c>
       <c r="R28" t="n">
-        <v>6385186</v>
+        <v>6385124</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,42 +3677,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174193</v>
+        <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>105488</v>
+        <v>109283</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725758</v>
+        <v>725442</v>
       </c>
       <c r="R29" t="n">
-        <v>6385124</v>
+        <v>6385186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
         <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>98425</v>
+        <v>98431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98484</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127174201</v>
+        <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>107335</v>
+        <v>109283</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725807</v>
+        <v>725464</v>
       </c>
       <c r="R33" t="n">
-        <v>6385133</v>
+        <v>6385167</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,6 +4208,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd mot V.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4237,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127174169</v>
+        <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>109277</v>
+        <v>107341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,31 +4253,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4281,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725464</v>
+        <v>725807</v>
       </c>
       <c r="R34" t="n">
-        <v>6385167</v>
+        <v>6385133</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,11 +4324,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd mot V.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,48 +4353,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>109277</v>
+        <v>98492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R35" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4424,11 +4433,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,57 +4464,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>98486</v>
+        <v>109283</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R36" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>98425</v>
+        <v>98431</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98425</v>
+        <v>98431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>109277</v>
+        <v>107341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,31 +5355,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R44" t="n">
         <v>6385121</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5455,42 +5455,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174183</v>
+        <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>98486</v>
+        <v>109283</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725652</v>
+        <v>725616</v>
       </c>
       <c r="R45" t="n">
-        <v>6385115</v>
+        <v>6385121</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,37 +5566,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174177</v>
+        <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>107335</v>
+        <v>98493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220079</v>
+        <v>219875</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725520</v>
+        <v>725669</v>
       </c>
       <c r="R46" t="n">
-        <v>6385121</v>
+        <v>6385120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>98487</v>
+        <v>98492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127174160</v>
+        <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>109277</v>
+        <v>107341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,37 +5799,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>725487</v>
+        <v>725532</v>
       </c>
       <c r="R48" t="n">
         <v>6385259</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,11 +5870,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5895,10 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127174151</v>
+        <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>107335</v>
+        <v>109283</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5906,46 +5910,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>725532</v>
+        <v>725487</v>
       </c>
       <c r="R49" t="n">
         <v>6385259</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,6 +5972,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog, yngre; tiidgare hyggesplöjt.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>109277</v>
+        <v>107341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,34 +6128,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R51" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,11 +6199,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6224,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>107335</v>
+        <v>109283</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,43 +6239,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R52" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,6 +6301,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
         <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>98486</v>
+        <v>98492</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>98486</v>
+        <v>107341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R55" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,6 +6639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6650,7 +6655,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6668,10 +6673,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98486</v>
+        <v>98478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,26 +6684,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6712,13 +6717,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R56" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6750,6 +6755,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6761,7 +6771,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6779,37 +6789,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>107335</v>
+        <v>98492</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6823,10 +6833,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R57" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6861,11 +6871,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6895,10 +6900,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98472</v>
+        <v>98492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6906,26 +6911,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6939,13 +6944,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R58" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6977,11 +6982,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,60 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174604</v>
+        <v>127174179</v>
       </c>
       <c r="B4" t="n">
-        <v>96058</v>
+        <v>107344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725732</v>
+        <v>725566</v>
       </c>
       <c r="R4" t="n">
-        <v>6385256</v>
+        <v>6385110</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,13 +985,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1012,37 +1008,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174179</v>
+        <v>127174150</v>
       </c>
       <c r="B5" t="n">
-        <v>107341</v>
+        <v>98482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725566</v>
+        <v>725532</v>
       </c>
       <c r="R5" t="n">
-        <v>6385110</v>
+        <v>6385259</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174150</v>
+        <v>127174187</v>
       </c>
       <c r="B6" t="n">
-        <v>98479</v>
+        <v>98495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,26 +1130,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725532</v>
+        <v>725669</v>
       </c>
       <c r="R6" t="n">
-        <v>6385259</v>
+        <v>6385120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1237,7 +1233,7 @@
         <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174187</v>
+        <v>127174604</v>
       </c>
       <c r="B8" t="n">
-        <v>98492</v>
+        <v>96061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,46 +1352,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223621</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725669</v>
+        <v>725732</v>
       </c>
       <c r="R8" t="n">
-        <v>6385120</v>
+        <v>6385256</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1432,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174224</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>107341</v>
+        <v>98495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725647</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385302</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174209</v>
+        <v>127174224</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>107344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725832</v>
+        <v>725647</v>
       </c>
       <c r="R10" t="n">
-        <v>6385251</v>
+        <v>6385302</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174172</v>
+        <v>127174209</v>
       </c>
       <c r="B11" t="n">
-        <v>107341</v>
+        <v>98481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725473</v>
+        <v>725832</v>
       </c>
       <c r="R11" t="n">
-        <v>6385147</v>
+        <v>6385251</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B12" t="n">
-        <v>98492</v>
+        <v>107344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R12" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>98348</v>
+        <v>98351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127174217</v>
       </c>
       <c r="B17" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>127174220</v>
       </c>
       <c r="B18" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127174192</v>
+        <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98492</v>
+        <v>98481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725752</v>
+        <v>725840</v>
       </c>
       <c r="R20" t="n">
-        <v>6385124</v>
+        <v>6385253</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127174206</v>
+        <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98495</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725840</v>
+        <v>725752</v>
       </c>
       <c r="R21" t="n">
-        <v>6385253</v>
+        <v>6385124</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98493</v>
+        <v>98496</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98484</v>
+        <v>98487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>127174193</v>
       </c>
       <c r="B28" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>98431</v>
+        <v>98434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>98484</v>
+        <v>98487</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>127174148</v>
       </c>
       <c r="B35" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>127174165</v>
       </c>
       <c r="B36" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>98431</v>
+        <v>98434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127174208</v>
+        <v>127174197</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>98434</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,26 +5133,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219862</v>
+        <v>219797</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>725831</v>
+        <v>725722</v>
       </c>
       <c r="R42" t="n">
-        <v>6385246</v>
+        <v>6385158</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174197</v>
+        <v>127174208</v>
       </c>
       <c r="B43" t="n">
-        <v>98431</v>
+        <v>98481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,26 +5244,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219797</v>
+        <v>219862</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725722</v>
+        <v>725831</v>
       </c>
       <c r="R43" t="n">
-        <v>6385158</v>
+        <v>6385246</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B46" t="n">
-        <v>98493</v>
+        <v>98495</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R46" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174186</v>
       </c>
       <c r="B47" t="n">
-        <v>98492</v>
+        <v>98496</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>219875</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725669</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B51" t="n">
-        <v>107341</v>
+        <v>109286</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,43 +6128,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R51" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,6 +6190,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6210,7 +6206,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6228,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B52" t="n">
-        <v>109283</v>
+        <v>107344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6239,34 +6235,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R52" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6301,11 +6306,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B53" t="n">
-        <v>109283</v>
+        <v>98495</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R53" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B54" t="n">
-        <v>98492</v>
+        <v>109286</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R54" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98478</v>
+        <v>98481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,57 +897,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174179</v>
+        <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>107344</v>
+        <v>96069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725566</v>
+        <v>725732</v>
       </c>
       <c r="R4" t="n">
-        <v>6385110</v>
+        <v>6385256</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +988,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +1012,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174150</v>
+        <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>98482</v>
+        <v>107352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725532</v>
+        <v>725566</v>
       </c>
       <c r="R5" t="n">
-        <v>6385259</v>
+        <v>6385110</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174187</v>
+        <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98495</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725669</v>
+        <v>725532</v>
       </c>
       <c r="R6" t="n">
-        <v>6385120</v>
+        <v>6385259</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1216,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B7" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R7" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174604</v>
+        <v>127174195</v>
       </c>
       <c r="B8" t="n">
-        <v>96061</v>
+        <v>98503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,49 +1356,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>223621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725732</v>
+        <v>725722</v>
       </c>
       <c r="R8" t="n">
-        <v>6385256</v>
+        <v>6385158</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,13 +1433,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174155</v>
+        <v>127174224</v>
       </c>
       <c r="B9" t="n">
-        <v>98495</v>
+        <v>107352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725522</v>
+        <v>725647</v>
       </c>
       <c r="R9" t="n">
-        <v>6385261</v>
+        <v>6385302</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174224</v>
+        <v>127174209</v>
       </c>
       <c r="B10" t="n">
-        <v>107344</v>
+        <v>98489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725647</v>
+        <v>725832</v>
       </c>
       <c r="R10" t="n">
-        <v>6385302</v>
+        <v>6385251</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174209</v>
+        <v>127174172</v>
       </c>
       <c r="B11" t="n">
-        <v>98481</v>
+        <v>107352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725832</v>
+        <v>725473</v>
       </c>
       <c r="R11" t="n">
-        <v>6385251</v>
+        <v>6385147</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174172</v>
+        <v>127174155</v>
       </c>
       <c r="B12" t="n">
-        <v>107344</v>
+        <v>98503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725473</v>
+        <v>725522</v>
       </c>
       <c r="R12" t="n">
-        <v>6385147</v>
+        <v>6385261</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>127174203</v>
       </c>
       <c r="B15" t="n">
-        <v>98351</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>127174178</v>
       </c>
       <c r="B16" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127174217</v>
       </c>
       <c r="B17" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>127174220</v>
       </c>
       <c r="B18" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127174194</v>
       </c>
       <c r="B19" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98496</v>
+        <v>98504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98487</v>
+        <v>98495</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127174173</v>
       </c>
       <c r="B25" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>127174152</v>
       </c>
       <c r="B26" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127174147</v>
       </c>
       <c r="B27" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>127174193</v>
       </c>
       <c r="B28" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>127174166</v>
       </c>
       <c r="B29" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>127174207</v>
       </c>
       <c r="B30" t="n">
-        <v>98434</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127174145</v>
       </c>
       <c r="B31" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>127174168</v>
       </c>
       <c r="B32" t="n">
-        <v>98487</v>
+        <v>98495</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,57 +4353,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127174148</v>
+        <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>98495</v>
+        <v>109294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725549</v>
+        <v>725436</v>
       </c>
       <c r="R35" t="n">
-        <v>6385264</v>
+        <v>6385191</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,6 +4424,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,48 +4460,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127174165</v>
+        <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>109286</v>
+        <v>98503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725436</v>
+        <v>725549</v>
       </c>
       <c r="R36" t="n">
-        <v>6385191</v>
+        <v>6385264</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4535,11 +4540,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>127174757</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>98434</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127174197</v>
+        <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98434</v>
+        <v>98489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,26 +5133,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219797</v>
+        <v>219862</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>725722</v>
+        <v>725831</v>
       </c>
       <c r="R42" t="n">
-        <v>6385158</v>
+        <v>6385246</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127174208</v>
+        <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98481</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,26 +5244,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219862</v>
+        <v>219797</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>725831</v>
+        <v>725722</v>
       </c>
       <c r="R43" t="n">
-        <v>6385246</v>
+        <v>6385158</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>127174177</v>
       </c>
       <c r="B44" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>127174182</v>
       </c>
       <c r="B45" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174183</v>
+        <v>127174186</v>
       </c>
       <c r="B46" t="n">
-        <v>98495</v>
+        <v>98504</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223621</v>
+        <v>219875</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725652</v>
+        <v>725669</v>
       </c>
       <c r="R46" t="n">
-        <v>6385115</v>
+        <v>6385120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174186</v>
+        <v>127174183</v>
       </c>
       <c r="B47" t="n">
-        <v>98496</v>
+        <v>98503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219875</v>
+        <v>223621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725669</v>
+        <v>725652</v>
       </c>
       <c r="R47" t="n">
-        <v>6385120</v>
+        <v>6385115</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127174163</v>
+        <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>109286</v>
+        <v>107352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6128,34 +6128,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>725433</v>
+        <v>725652</v>
       </c>
       <c r="R51" t="n">
-        <v>6385211</v>
+        <v>6385115</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,11 +6199,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd, rikligt.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6224,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127174184</v>
+        <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>107344</v>
+        <v>109294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,43 +6239,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gothem Hangre 1:16 (1); A 30236-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>725652</v>
+        <v>725433</v>
       </c>
       <c r="R52" t="n">
-        <v>6385115</v>
+        <v>6385211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,6 +6301,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spridd, rikligt.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6335,42 +6335,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127174149</v>
+        <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>98495</v>
+        <v>109294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>725540</v>
+        <v>725591</v>
       </c>
       <c r="R53" t="n">
-        <v>6385270</v>
+        <v>6385252</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6446,42 +6446,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127174146</v>
+        <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>109286</v>
+        <v>98503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>223621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>725591</v>
+        <v>725540</v>
       </c>
       <c r="R54" t="n">
-        <v>6385252</v>
+        <v>6385270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>127174204</v>
       </c>
       <c r="B55" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>127174174</v>
       </c>
       <c r="B56" t="n">
-        <v>98481</v>
+        <v>98489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127174218</v>
       </c>
       <c r="B57" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>127174157</v>
       </c>
       <c r="B58" t="n">
-        <v>98495</v>
+        <v>98503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127174205</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127174189</v>
       </c>
       <c r="B3" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127174604</v>
       </c>
       <c r="B4" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127174179</v>
       </c>
       <c r="B5" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127174150</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174187</v>
+        <v>127174195</v>
       </c>
       <c r="B7" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725669</v>
+        <v>725722</v>
       </c>
       <c r="R7" t="n">
-        <v>6385120</v>
+        <v>6385158</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174195</v>
+        <v>127174187</v>
       </c>
       <c r="B8" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725722</v>
+        <v>725669</v>
       </c>
       <c r="R8" t="n">
-        <v>6385158</v>
+        <v>6385120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,37 +1456,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127174224</v>
+        <v>127174155</v>
       </c>
       <c r="B9" t="n">
-        <v>107352</v>
+        <v>98504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725647</v>
+        <v>725522</v>
       </c>
       <c r="R9" t="n">
-        <v>6385302</v>
+        <v>6385261</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,37 +1567,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127174209</v>
+        <v>127174224</v>
       </c>
       <c r="B10" t="n">
-        <v>98489</v>
+        <v>107353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725832</v>
+        <v>725647</v>
       </c>
       <c r="R10" t="n">
-        <v>6385251</v>
+        <v>6385302</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,37 +1678,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127174172</v>
+        <v>127174209</v>
       </c>
       <c r="B11" t="n">
-        <v>107352</v>
+        <v>98490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725473</v>
+        <v>725832</v>
       </c>
       <c r="R11" t="n">
-        <v>6385147</v>
+        <v>6385251</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1789,37 +1789,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127174155</v>
+        <v>127174172</v>
       </c>
       <c r="B12" t="n">
-        <v>98503</v>
+        <v>107353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725522</v>
+        <v>725473</v>
       </c>
       <c r="R12" t="n">
-        <v>6385261</v>
+        <v>6385147</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på kalkgrusås.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>127174171</v>
       </c>
       <c r="B14" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127174203</v>
+        <v>127174194</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,26 +2124,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>223621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725843</v>
+        <v>725758</v>
       </c>
       <c r="R15" t="n">
-        <v>6385204</v>
+        <v>6385124</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,37 +2224,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127174178</v>
+        <v>127174203</v>
       </c>
       <c r="B16" t="n">
-        <v>107352</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725542</v>
+        <v>725843</v>
       </c>
       <c r="R16" t="n">
-        <v>6385111</v>
+        <v>6385204</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127174217</v>
+        <v>127174178</v>
       </c>
       <c r="B17" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725732</v>
+        <v>725542</v>
       </c>
       <c r="R17" t="n">
-        <v>6385256</v>
+        <v>6385111</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127174220</v>
+        <v>127174217</v>
       </c>
       <c r="B18" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725734</v>
+        <v>725732</v>
       </c>
       <c r="R18" t="n">
-        <v>6385261</v>
+        <v>6385256</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,11 +2526,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>"Knärotsskog".</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,37 +2557,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127174194</v>
+        <v>127174220</v>
       </c>
       <c r="B19" t="n">
-        <v>98503</v>
+        <v>107353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725758</v>
+        <v>725734</v>
       </c>
       <c r="R19" t="n">
-        <v>6385124</v>
+        <v>6385261</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,6 +2639,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>"Knärotsskog".</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
         <v>127174206</v>
       </c>
       <c r="B20" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>127174192</v>
       </c>
       <c r="B21" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127174153</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127174188</v>
       </c>
       <c r="B23" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127174199</v>
       </c>
       <c r="B24" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174173</v>
+        <v>127174152</v>
       </c>
       <c r="B25" t="n">
-        <v>98489</v>
+        <v>98504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,26 +3239,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725473</v>
+        <v>725532</v>
       </c>
       <c r="R25" t="n">
-        <v>6385147</v>
+        <v>6385259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Varav 1 fjolårsstängel.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3326,7 +3321,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3344,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174152</v>
+        <v>127174147</v>
       </c>
       <c r="B26" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3369,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3388,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725532</v>
+        <v>725549</v>
       </c>
       <c r="R26" t="n">
-        <v>6385259</v>
+        <v>6385258</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174147</v>
+        <v>127174173</v>
       </c>
       <c r="B27" t="n">
-        <v>98503</v>
+        <v>98490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,26 +3461,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725549</v>
+        <v>725473</v>
       </c>
       <c r="R27" t="n">
-        <v>6385258</v>
+        <v>6385147</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3532,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Varav 1 fjolårsstängel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,42 +3566,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127174193</v>
+        <v>127174166</v>
       </c>
       <c r="B28" t="n">
-        <v>105505</v>
+        <v>109295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725758</v>
+        <v>725442</v>
       </c>
       <c r="R28" t="n">
-        <v>6385124</v>
+        <v>6385186</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3677,42 +3677,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127174166</v>
+        <v>127174207</v>
       </c>
       <c r="B29" t="n">
-        <v>109294</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725442</v>
+        <v>725831</v>
       </c>
       <c r="R29" t="n">
-        <v>6385186</v>
+        <v>6385246</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3788,37 +3788,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127174207</v>
+        <v>127174145</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>107353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725831</v>
+        <v>725591</v>
       </c>
       <c r="R30" t="n">
-        <v>6385246</v>
+        <v>6385252</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3870,6 +3870,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Även spridd längs körväg genom skogen.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3881,7 +3886,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3899,37 +3904,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127174145</v>
+        <v>127174168</v>
       </c>
       <c r="B31" t="n">
-        <v>107352</v>
+        <v>98496</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3943,13 +3948,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725591</v>
+        <v>725457</v>
       </c>
       <c r="R31" t="n">
-        <v>6385252</v>
+        <v>6385181</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,11 +3984,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Även spridd längs körväg genom skogen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127174168</v>
+        <v>127174193</v>
       </c>
       <c r="B32" t="n">
-        <v>98495</v>
+        <v>105506</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,26 +4026,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725457</v>
+        <v>725758</v>
       </c>
       <c r="R32" t="n">
-        <v>6385181</v>
+        <v>6385124</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
         <v>127174169</v>
       </c>
       <c r="B33" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>127174201</v>
       </c>
       <c r="B34" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>127174165</v>
       </c>
       <c r="B35" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>127174148</v>
       </c>
       <c r="B36" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127174161</v>
       </c>
       <c r="B37" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127174162</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127174196</v>
       </c>
       <c r="B40" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>127174158</v>
       </c>
       <c r="B41" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>127174208</v>
       </c>
       <c r="B42" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127174197</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5344,37 +5344,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127174177</v>
+        <v>127174183</v>
       </c>
       <c r="B44" t="n">
-        <v>107352</v>
+        <v>98504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>725520</v>
+        <v>725652</v>
       </c>
       <c r="R44" t="n">
-        <v>6385121</v>
+        <v>6385115</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127174182</v>
+        <v>127174177</v>
       </c>
       <c r="B45" t="n">
-        <v>109294</v>
+        <v>107353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,31 +5466,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>725616</v>
+        <v>725520</v>
       </c>
       <c r="R45" t="n">
         <v>6385121</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; vid körväg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5566,42 +5566,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127174186</v>
+        <v>127174182</v>
       </c>
       <c r="B46" t="n">
-        <v>98504</v>
+        <v>109295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>725669</v>
+        <v>725616</v>
       </c>
       <c r="R46" t="n">
-        <v>6385120</v>
+        <v>6385121</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127174183</v>
+        <v>127174186</v>
       </c>
       <c r="B47" t="n">
-        <v>98503</v>
+        <v>98505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223621</v>
+        <v>219875</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>725652</v>
+        <v>725669</v>
       </c>
       <c r="R47" t="n">
-        <v>6385115</v>
+        <v>6385120</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127174151</v>
       </c>
       <c r="B48" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>127174160</v>
       </c>
       <c r="B49" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>127174164</v>
       </c>
       <c r="B50" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>127174184</v>
       </c>
       <c r="B51" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>127174163</v>
       </c>
       <c r="B52" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>127174146</v>
       </c>
       <c r="B53" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>127174149</v>
       </c>
       <c r="B54" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,37 +6557,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127174204</v>
+        <v>127174218</v>
       </c>
       <c r="B55" t="n">
-        <v>107352</v>
+        <v>98504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>223621</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>725843</v>
+        <v>725732</v>
       </c>
       <c r="R55" t="n">
-        <v>6385204</v>
+        <v>6385256</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6639,11 +6639,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6655,7 +6650,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder.</t>
+          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6673,10 +6668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127174174</v>
+        <v>127174157</v>
       </c>
       <c r="B56" t="n">
-        <v>98489</v>
+        <v>98504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,26 +6679,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219862</v>
+        <v>223621</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6717,13 +6712,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>725478</v>
+        <v>725519</v>
       </c>
       <c r="R56" t="n">
-        <v>6385143</v>
+        <v>6385256</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,11 +6750,6 @@
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Varav 3 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6771,7 +6761,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
+          <t>Kalktallskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6789,37 +6779,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127174218</v>
+        <v>127174204</v>
       </c>
       <c r="B57" t="n">
-        <v>98503</v>
+        <v>107353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223621</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6833,10 +6823,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>725732</v>
+        <v>725843</v>
       </c>
       <c r="R57" t="n">
-        <v>6385256</v>
+        <v>6385204</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6871,6 +6861,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mellanskog snitsel mot hästbetad något yngre skog i SO.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkblandskog av blandad ålder; i mossa!.</t>
+          <t>Kalkblandskog av blandad ålder.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6900,10 +6895,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127174157</v>
+        <v>127174174</v>
       </c>
       <c r="B58" t="n">
-        <v>98503</v>
+        <v>98490</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,26 +6906,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223621</v>
+        <v>219862</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6944,13 +6939,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>725519</v>
+        <v>725478</v>
       </c>
       <c r="R58" t="n">
-        <v>6385256</v>
+        <v>6385143</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6982,6 +6977,11 @@
           <t>2025-06-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Varav 3 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
+          <t>Kalktallskog äldre med mossa på sluttning av kalkgrusås. Mest på äldre avverkningsväg.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7009,6 +7009,7710 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128791517</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>424</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>725712</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6385261</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128791453</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>725494</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6385080</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128784654</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>725494</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6385035</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128784663</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>725739</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6385174</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128786101</v>
+      </c>
+      <c r="B63" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>725528</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6385185</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128786091</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>725507</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6385159</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128791475</v>
+      </c>
+      <c r="B65" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>725503</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6385246</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128791459</v>
+      </c>
+      <c r="B66" t="n">
+        <v>86753</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>725746</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6385092</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128791478</v>
+      </c>
+      <c r="B67" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>725685</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6385124</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128791449</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>725457</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6385042</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128791463</v>
+      </c>
+      <c r="B69" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>725426</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6385160</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128784653</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>725496</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6385075</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128786092</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>725499</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6385065</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128791503</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>433</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>725496</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6385236</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128784660</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>725724</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6385117</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128791476</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>725519</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6385262</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128791455</v>
+      </c>
+      <c r="B75" t="n">
+        <v>87121</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>451</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sotbandad spindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius fuscoperonatus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>725394</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6385091</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>? Något mindre kollekt</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128784664</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>725593</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6385221</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128791488</v>
+      </c>
+      <c r="B77" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>449</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>725580</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6385121</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128791506</v>
+      </c>
+      <c r="B78" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>433</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>725546</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6385296</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128791481</v>
+      </c>
+      <c r="B79" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>725669</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6385183</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128791465</v>
+      </c>
+      <c r="B80" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>725458</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6385186</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128786097</v>
+      </c>
+      <c r="B81" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>725551</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6385217</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128791466</v>
+      </c>
+      <c r="B82" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>725740</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6385101</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128791458</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86753</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>725410</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6385108</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128791482</v>
+      </c>
+      <c r="B84" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>725720</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6385276</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128791501</v>
+      </c>
+      <c r="B85" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>433</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>725439</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6385189</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128791474</v>
+      </c>
+      <c r="B86" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>725471</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6385206</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128786098</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98613</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>725577</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6385250</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128791489</v>
+      </c>
+      <c r="B88" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>449</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>725612</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6385206</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128791452</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>725424</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6384953</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128791502</v>
+      </c>
+      <c r="B90" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>433</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>725467</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6385196</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128784669</v>
+      </c>
+      <c r="B91" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>449</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>725759</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6385120</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128784659</v>
+      </c>
+      <c r="B92" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>725626</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6385141</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128784662</v>
+      </c>
+      <c r="B93" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>725771</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6385166</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128784675</v>
+      </c>
+      <c r="B94" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>442</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>725536</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6385137</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128791469</v>
+      </c>
+      <c r="B95" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>725461</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6385028</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128786089</v>
+      </c>
+      <c r="B96" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>725556</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6385239</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128791498</v>
+      </c>
+      <c r="B97" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>433</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>725697</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6385241</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128791477</v>
+      </c>
+      <c r="B98" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>725588</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6385289</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128791514</v>
+      </c>
+      <c r="B99" t="n">
+        <v>86815</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>442</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>725527</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6385142</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128791504</v>
+      </c>
+      <c r="B100" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>433</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>725500</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6385247</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128791516</v>
+      </c>
+      <c r="B101" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>424</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>725744</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6385244</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128791505</v>
+      </c>
+      <c r="B102" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>433</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>725506</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6385254</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128791473</v>
+      </c>
+      <c r="B103" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>725405</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6385117</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128784657</v>
+      </c>
+      <c r="B104" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>424</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>725724</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6385171</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128784661</v>
+      </c>
+      <c r="B105" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>725740</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6385127</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128784666</v>
+      </c>
+      <c r="B106" t="n">
+        <v>107500</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>725501</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6385056</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128784652</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92752</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>725629</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6385285</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128786100</v>
+      </c>
+      <c r="B108" t="n">
+        <v>90904</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Kantjordstjärna</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Geastrum striatum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>725528</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6385185</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128786099</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91001</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>725542</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6385225</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128791479</v>
+      </c>
+      <c r="B110" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>725712</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6385103</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128791499</v>
+      </c>
+      <c r="B111" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>433</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>725431</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6385191</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128786096</v>
+      </c>
+      <c r="B112" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>725551</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6385237</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128791468</v>
+      </c>
+      <c r="B113" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>725588</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6385224</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128786106</v>
+      </c>
+      <c r="B114" t="n">
+        <v>86753</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>725520</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6385158</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128791480</v>
+      </c>
+      <c r="B115" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>725785</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6385095</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128791467</v>
+      </c>
+      <c r="B116" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>725756</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6385191</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128791487</v>
+      </c>
+      <c r="B117" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>449</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>725771</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6385103</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128791462</v>
+      </c>
+      <c r="B118" t="n">
+        <v>86729</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>725541</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6385088</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128784668</v>
+      </c>
+      <c r="B119" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>725725</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6385117</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128784676</v>
+      </c>
+      <c r="B120" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>725647</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6385255</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128791510</v>
+      </c>
+      <c r="B121" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>433</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>725665</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6385180</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128791508</v>
+      </c>
+      <c r="B122" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>433</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>725757</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6385187</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128784658</v>
+      </c>
+      <c r="B123" t="n">
+        <v>86775</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>424</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>725646</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6385281</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128786105</v>
+      </c>
+      <c r="B124" t="n">
+        <v>96187</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>725537</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6385216</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128786090</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>725545</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6385234</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128791485</v>
+      </c>
+      <c r="B126" t="n">
+        <v>98613</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>725724</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6385174</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128791483</v>
+      </c>
+      <c r="B127" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>725645</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6385261</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128784670</v>
+      </c>
+      <c r="B128" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>433</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Storhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>725570</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6385186</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128786102</v>
+      </c>
+      <c r="B129" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>725513</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6385159</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128791448</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91244</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>725501</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6385071</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128791495</v>
+      </c>
+      <c r="B131" t="n">
+        <v>90882</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1000938</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Geastrum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>725745</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6385094</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128791460</v>
+      </c>
+      <c r="B132" t="n">
+        <v>86753</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>725718</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6385251</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128791512</v>
+      </c>
+      <c r="B133" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>433</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>725631</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6385124</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7118,10 +7118,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128791453</v>
+        <v>128786101</v>
       </c>
       <c r="B60" t="n">
-        <v>91244</v>
+        <v>86843</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7129,34 +7129,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725494</v>
+        <v>725528</v>
       </c>
       <c r="R60" t="n">
-        <v>6385080</v>
+        <v>6385185</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7186,50 +7186,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784654</v>
+        <v>128791453</v>
       </c>
       <c r="B61" t="n">
-        <v>91244</v>
+        <v>91245</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7257,14 +7246,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>725494</v>
       </c>
       <c r="R61" t="n">
-        <v>6385035</v>
+        <v>6385080</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7294,74 +7283,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784663</v>
+        <v>128786091</v>
       </c>
       <c r="B62" t="n">
-        <v>86927</v>
+        <v>91245</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725739</v>
+        <v>725507</v>
       </c>
       <c r="R62" t="n">
-        <v>6385174</v>
+        <v>6385159</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7402,29 +7402,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128786101</v>
+        <v>128784654</v>
       </c>
       <c r="B63" t="n">
-        <v>86843</v>
+        <v>91245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7432,34 +7431,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725528</v>
+        <v>725494</v>
       </c>
       <c r="R63" t="n">
-        <v>6385185</v>
+        <v>6385035</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7506,57 +7505,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128786091</v>
+        <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>91244</v>
+        <v>86927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725507</v>
+        <v>725739</v>
       </c>
       <c r="R64" t="n">
-        <v>6385159</v>
+        <v>6385174</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7597,50 +7596,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791475</v>
+        <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86927</v>
+        <v>86753</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725503</v>
+        <v>725746</v>
       </c>
       <c r="R65" t="n">
-        <v>6385246</v>
+        <v>6385092</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,7 +7704,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7723,32 +7722,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791459</v>
+        <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86753</v>
+        <v>86927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7758,10 +7757,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725746</v>
+        <v>725503</v>
       </c>
       <c r="R66" t="n">
-        <v>6385092</v>
+        <v>6385246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7793,7 +7792,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7803,7 +7802,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7812,6 +7811,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B68" t="n">
-        <v>91244</v>
+        <v>86927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R68" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,6 +8027,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8045,32 +8046,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>91245</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8080,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R69" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8125,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8134,7 +8135,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128784653</v>
+        <v>128791503</v>
       </c>
       <c r="B70" t="n">
-        <v>91244</v>
+        <v>86984</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,34 +8164,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>725496</v>
       </c>
       <c r="R70" t="n">
-        <v>6385075</v>
+        <v>6385236</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8221,9 +8217,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8238,12 +8244,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8253,7 +8259,7 @@
         <v>128786092</v>
       </c>
       <c r="B71" t="n">
-        <v>91244</v>
+        <v>91245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8347,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791503</v>
+        <v>128784653</v>
       </c>
       <c r="B72" t="n">
-        <v>86984</v>
+        <v>91245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,30 +8364,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385236</v>
+        <v>6385075</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8411,19 +8421,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8656,45 +8656,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791455</v>
+        <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>87121</v>
+        <v>86927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>451</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>725394</v>
+        <v>725593</v>
       </c>
       <c r="R75" t="n">
-        <v>6385091</v>
+        <v>6385221</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8724,24 +8724,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>? Något mindre kollekt</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8757,57 +8742,53 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128784664</v>
+        <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>86927</v>
+        <v>86984</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>725593</v>
+        <v>725546</v>
       </c>
       <c r="R76" t="n">
-        <v>6385221</v>
+        <v>6385296</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8837,30 +8818,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8974,30 +8964,34 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791506</v>
+        <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9005,10 +8999,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>725546</v>
+        <v>725458</v>
       </c>
       <c r="R78" t="n">
-        <v>6385296</v>
+        <v>6385186</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9040,7 +9034,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9050,7 +9044,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9059,6 +9053,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9185,32 +9180,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791465</v>
+        <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86927</v>
+        <v>86753</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9220,10 +9215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>725458</v>
+        <v>725410</v>
       </c>
       <c r="R80" t="n">
-        <v>6385186</v>
+        <v>6385108</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9255,7 +9250,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9265,7 +9260,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9274,7 +9269,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9293,7 +9287,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128786097</v>
+        <v>128791466</v>
       </c>
       <c r="B81" t="n">
         <v>86927</v>
@@ -9324,14 +9318,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>725551</v>
+        <v>725740</v>
       </c>
       <c r="R81" t="n">
-        <v>6385217</v>
+        <v>6385101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9361,9 +9355,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9379,19 +9383,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791466</v>
+        <v>128791474</v>
       </c>
       <c r="B82" t="n">
         <v>86927</v>
@@ -9426,10 +9430,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>725740</v>
+        <v>725471</v>
       </c>
       <c r="R82" t="n">
-        <v>6385101</v>
+        <v>6385206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9461,7 +9465,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9471,7 +9475,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9499,32 +9503,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791458</v>
+        <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86753</v>
+        <v>86927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9534,10 +9538,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>725410</v>
+        <v>725720</v>
       </c>
       <c r="R83" t="n">
-        <v>6385108</v>
+        <v>6385276</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9569,7 +9573,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9579,7 +9583,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9588,6 +9592,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9606,7 +9611,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791482</v>
+        <v>128786097</v>
       </c>
       <c r="B84" t="n">
         <v>86927</v>
@@ -9637,14 +9642,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>725720</v>
+        <v>725551</v>
       </c>
       <c r="R84" t="n">
-        <v>6385276</v>
+        <v>6385217</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9674,19 +9679,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9702,22 +9697,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791501</v>
+        <v>128791452</v>
       </c>
       <c r="B85" t="n">
-        <v>86984</v>
+        <v>91245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9725,19 +9720,23 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9745,10 +9744,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725439</v>
+        <v>725424</v>
       </c>
       <c r="R85" t="n">
-        <v>6385189</v>
+        <v>6384953</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9780,7 +9779,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9790,7 +9789,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9817,32 +9816,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791474</v>
+        <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9852,7 +9851,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725471</v>
+        <v>725612</v>
       </c>
       <c r="R86" t="n">
         <v>6385206</v>
@@ -9887,7 +9886,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9897,7 +9896,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9906,7 +9905,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9928,7 +9926,7 @@
         <v>128786098</v>
       </c>
       <c r="B87" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10022,10 +10020,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128791489</v>
+        <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>86949</v>
+        <v>86984</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10033,23 +10031,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10057,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>725612</v>
+        <v>725467</v>
       </c>
       <c r="R88" t="n">
-        <v>6385206</v>
+        <v>6385196</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10092,7 +10086,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10102,7 +10096,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10129,10 +10123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791452</v>
+        <v>128784675</v>
       </c>
       <c r="B89" t="n">
-        <v>91244</v>
+        <v>86815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10140,34 +10134,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2015</v>
+        <v>442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725424</v>
+        <v>725536</v>
       </c>
       <c r="R89" t="n">
-        <v>6384953</v>
+        <v>6385137</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10197,19 +10191,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,22 +10208,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128791502</v>
+        <v>128784669</v>
       </c>
       <c r="B90" t="n">
-        <v>86984</v>
+        <v>86949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10247,30 +10231,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725467</v>
+        <v>725759</v>
       </c>
       <c r="R90" t="n">
-        <v>6385196</v>
+        <v>6385120</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10300,19 +10288,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10327,57 +10305,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784669</v>
+        <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725759</v>
+        <v>725461</v>
       </c>
       <c r="R91" t="n">
-        <v>6385120</v>
+        <v>6385028</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10407,36 +10385,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784659</v>
+        <v>128784662</v>
       </c>
       <c r="B92" t="n">
         <v>86927</v>
@@ -10471,10 +10460,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725626</v>
+        <v>725771</v>
       </c>
       <c r="R92" t="n">
-        <v>6385141</v>
+        <v>6385166</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10534,7 +10523,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784662</v>
+        <v>128784659</v>
       </c>
       <c r="B93" t="n">
         <v>86927</v>
@@ -10569,10 +10558,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725771</v>
+        <v>725626</v>
       </c>
       <c r="R93" t="n">
-        <v>6385166</v>
+        <v>6385141</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10632,45 +10621,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128784675</v>
+        <v>128786089</v>
       </c>
       <c r="B94" t="n">
-        <v>86815</v>
+        <v>92771</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>442</v>
+        <v>6047725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725536</v>
+        <v>725556</v>
       </c>
       <c r="R94" t="n">
-        <v>6385137</v>
+        <v>6385239</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10717,19 +10702,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128791469</v>
+        <v>128791477</v>
       </c>
       <c r="B95" t="n">
         <v>86927</v>
@@ -10764,10 +10749,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725461</v>
+        <v>725588</v>
       </c>
       <c r="R95" t="n">
-        <v>6385028</v>
+        <v>6385289</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10799,7 +10784,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10809,7 +10794,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10837,41 +10822,41 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B96" t="n">
-        <v>92770</v>
+        <v>86984</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R96" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10901,36 +10886,52 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791498</v>
+        <v>128791504</v>
       </c>
       <c r="B97" t="n">
         <v>86984</v>
@@ -10961,10 +10962,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725697</v>
+        <v>725500</v>
       </c>
       <c r="R97" t="n">
-        <v>6385241</v>
+        <v>6385247</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10996,7 +10997,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11006,12 +11007,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11020,7 +11016,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11039,32 +11034,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791477</v>
+        <v>128791514</v>
       </c>
       <c r="B98" t="n">
-        <v>86927</v>
+        <v>86815</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11074,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725588</v>
+        <v>725527</v>
       </c>
       <c r="R98" t="n">
-        <v>6385289</v>
+        <v>6385142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11109,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11119,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11128,7 +11123,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11147,10 +11141,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128791514</v>
+        <v>128784657</v>
       </c>
       <c r="B99" t="n">
-        <v>86815</v>
+        <v>86775</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,34 +11152,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725527</v>
+        <v>725724</v>
       </c>
       <c r="R99" t="n">
-        <v>6385142</v>
+        <v>6385171</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11215,19 +11209,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11242,22 +11226,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128791504</v>
+        <v>128791516</v>
       </c>
       <c r="B100" t="n">
-        <v>86984</v>
+        <v>86775</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11265,19 +11249,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11285,10 +11273,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725500</v>
+        <v>725744</v>
       </c>
       <c r="R100" t="n">
-        <v>6385247</v>
+        <v>6385244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11320,7 +11308,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11330,7 +11318,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11357,10 +11345,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128791516</v>
+        <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>86775</v>
+        <v>86984</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11368,23 +11356,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11392,10 +11376,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>725744</v>
+        <v>725506</v>
       </c>
       <c r="R101" t="n">
-        <v>6385244</v>
+        <v>6385254</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11427,7 +11411,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11437,7 +11421,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11464,41 +11448,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128791505</v>
+        <v>128784661</v>
       </c>
       <c r="B102" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725506</v>
+        <v>725740</v>
       </c>
       <c r="R102" t="n">
-        <v>6385254</v>
+        <v>6385127</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11528,39 +11516,30 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11675,45 +11654,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128784657</v>
+        <v>128786100</v>
       </c>
       <c r="B104" t="n">
-        <v>86775</v>
+        <v>90905</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>424</v>
+        <v>4190</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725724</v>
+        <v>725528</v>
       </c>
       <c r="R104" t="n">
-        <v>6385171</v>
+        <v>6385185</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11754,50 +11733,51 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784661</v>
+        <v>128784652</v>
       </c>
       <c r="B105" t="n">
-        <v>86927</v>
+        <v>92753</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>4363</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11807,10 +11787,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725740</v>
+        <v>725629</v>
       </c>
       <c r="R105" t="n">
-        <v>6385127</v>
+        <v>6385285</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,7 +11831,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11870,45 +11849,41 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128784666</v>
+        <v>128791499</v>
       </c>
       <c r="B106" t="n">
-        <v>107500</v>
+        <v>86984</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220079</v>
+        <v>433</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725501</v>
+        <v>725431</v>
       </c>
       <c r="R106" t="n">
-        <v>6385056</v>
+        <v>6385191</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11938,9 +11913,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11955,57 +11940,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128784652</v>
+        <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>92752</v>
+        <v>91002</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4363</v>
+        <v>5747</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725629</v>
+        <v>725542</v>
       </c>
       <c r="R107" t="n">
-        <v>6385285</v>
+        <v>6385225</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,57 +12037,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128786100</v>
+        <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>90904</v>
+        <v>107505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4190</v>
+        <v>220079</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725528</v>
+        <v>725501</v>
       </c>
       <c r="R108" t="n">
-        <v>6385185</v>
+        <v>6385056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12143,64 +12128,63 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128786099</v>
+        <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725542</v>
+        <v>725712</v>
       </c>
       <c r="R109" t="n">
-        <v>6385225</v>
+        <v>6385103</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12230,36 +12214,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128791479</v>
+        <v>128786096</v>
       </c>
       <c r="B110" t="n">
         <v>86927</v>
@@ -12290,14 +12285,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>725712</v>
+        <v>725551</v>
       </c>
       <c r="R110" t="n">
-        <v>6385103</v>
+        <v>6385237</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12327,19 +12322,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12355,42 +12340,46 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128791499</v>
+        <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86984</v>
+        <v>86927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12398,10 +12387,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>725431</v>
+        <v>725588</v>
       </c>
       <c r="R111" t="n">
-        <v>6385191</v>
+        <v>6385224</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12433,7 +12422,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12443,7 +12432,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12452,6 +12441,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12470,45 +12460,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128786096</v>
+        <v>128791487</v>
       </c>
       <c r="B112" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>725551</v>
+        <v>725771</v>
       </c>
       <c r="R112" t="n">
-        <v>6385237</v>
+        <v>6385103</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12538,9 +12528,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12556,44 +12556,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791468</v>
+        <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725588</v>
+        <v>725541</v>
       </c>
       <c r="R113" t="n">
-        <v>6385224</v>
+        <v>6385088</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,7 +12657,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12989,45 +12988,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128791487</v>
+        <v>128784676</v>
       </c>
       <c r="B117" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725771</v>
+        <v>725647</v>
       </c>
       <c r="R117" t="n">
-        <v>6385103</v>
+        <v>6385255</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,85 +13056,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128791462</v>
+        <v>128784668</v>
       </c>
       <c r="B118" t="n">
-        <v>86729</v>
+        <v>86843</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725541</v>
+        <v>725725</v>
       </c>
       <c r="R118" t="n">
-        <v>6385088</v>
+        <v>6385117</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13165,19 +13153,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13192,22 +13170,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128784668</v>
+        <v>128791508</v>
       </c>
       <c r="B119" t="n">
-        <v>86843</v>
+        <v>86984</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13215,34 +13193,30 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725725</v>
+        <v>725757</v>
       </c>
       <c r="R119" t="n">
-        <v>6385117</v>
+        <v>6385187</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13272,9 +13246,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13289,57 +13273,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128784676</v>
+        <v>128791483</v>
       </c>
       <c r="B120" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725647</v>
+        <v>725645</v>
       </c>
       <c r="R120" t="n">
-        <v>6385255</v>
+        <v>6385261</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13369,70 +13353,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128791510</v>
+        <v>128786090</v>
       </c>
       <c r="B121" t="n">
-        <v>86984</v>
+        <v>92771</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725665</v>
+        <v>725545</v>
       </c>
       <c r="R121" t="n">
-        <v>6385180</v>
+        <v>6385234</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13462,19 +13457,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13489,53 +13474,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128791508</v>
+        <v>128786105</v>
       </c>
       <c r="B122" t="n">
-        <v>86984</v>
+        <v>96188</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>433</v>
+        <v>2180</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725757</v>
+        <v>725537</v>
       </c>
       <c r="R122" t="n">
-        <v>6385187</v>
+        <v>6385216</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13565,19 +13554,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13592,12 +13571,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13701,10 +13680,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786105</v>
+        <v>128791485</v>
       </c>
       <c r="B124" t="n">
-        <v>96187</v>
+        <v>98614</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13712,34 +13691,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2180</v>
+        <v>219862</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725537</v>
+        <v>725724</v>
       </c>
       <c r="R124" t="n">
-        <v>6385216</v>
+        <v>6385174</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13769,9 +13748,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13786,22 +13775,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128786090</v>
+        <v>128791460</v>
       </c>
       <c r="B125" t="n">
-        <v>92770</v>
+        <v>86753</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13809,30 +13798,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6047725</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725545</v>
+        <v>725718</v>
       </c>
       <c r="R125" t="n">
-        <v>6385234</v>
+        <v>6385251</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13862,9 +13855,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13879,57 +13882,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128791485</v>
+        <v>128786102</v>
       </c>
       <c r="B126" t="n">
-        <v>98613</v>
+        <v>86843</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219862</v>
+        <v>248956</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725724</v>
+        <v>725513</v>
       </c>
       <c r="R126" t="n">
-        <v>6385174</v>
+        <v>6385159</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13959,19 +13962,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13986,44 +13979,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791483</v>
+        <v>128791448</v>
       </c>
       <c r="B127" t="n">
-        <v>86927</v>
+        <v>91245</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14033,10 +14026,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725645</v>
+        <v>725501</v>
       </c>
       <c r="R127" t="n">
-        <v>6385261</v>
+        <v>6385071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14068,7 +14061,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14078,7 +14071,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14087,7 +14080,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14199,10 +14191,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128786102</v>
+        <v>128791512</v>
       </c>
       <c r="B129" t="n">
-        <v>86843</v>
+        <v>86984</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14210,34 +14202,30 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725513</v>
+        <v>725631</v>
       </c>
       <c r="R129" t="n">
-        <v>6385159</v>
+        <v>6385124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14267,9 +14255,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14284,44 +14282,39 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791448</v>
+        <v>128791495</v>
       </c>
       <c r="B130" t="n">
-        <v>91244</v>
+        <v>90883</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Vit taggsvamp</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14331,10 +14324,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725501</v>
+        <v>725745</v>
       </c>
       <c r="R130" t="n">
-        <v>6385071</v>
+        <v>6385094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14366,7 +14359,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14376,7 +14369,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14403,27 +14396,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128791495</v>
+        <v>128815373</v>
       </c>
       <c r="B131" t="n">
-        <v>90882</v>
+        <v>86961</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1000938</v>
+        <v>248939</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tallpraktspindling</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius terpsichores</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Melot</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14433,10 +14431,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>725745</v>
+        <v>725787</v>
       </c>
       <c r="R131" t="n">
-        <v>6385094</v>
+        <v>6385165</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14468,7 +14466,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14478,7 +14476,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Annas fynd. Ej exakta koordinater, från samma lokal.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14505,45 +14508,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128791460</v>
+        <v>128791455</v>
       </c>
       <c r="B132" t="n">
-        <v>86753</v>
+        <v>87121</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>451</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>725718</v>
+        <v>725394</v>
       </c>
       <c r="R132" t="n">
-        <v>6385251</v>
+        <v>6385091</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14575,7 +14581,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14585,7 +14591,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>? Något mindre kollekt</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14594,6 +14605,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14612,41 +14624,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128791512</v>
+        <v>128815450</v>
       </c>
       <c r="B133" t="n">
-        <v>86984</v>
+        <v>86893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>433</v>
+        <v>6037417</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>725631</v>
+        <v>725669</v>
       </c>
       <c r="R133" t="n">
-        <v>6385124</v>
+        <v>6385183</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14678,7 +14697,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14688,7 +14707,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14697,6 +14716,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +14732,306 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128791501</v>
+      </c>
+      <c r="B134" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>433</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>725439</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6385189</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128786095</v>
+      </c>
+      <c r="B135" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>433</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>725515</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6385157</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128791510</v>
+      </c>
+      <c r="B136" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>433</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Gothem Hangre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>725665</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6385180</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791517</v>
+        <v>128791453</v>
       </c>
       <c r="B59" t="n">
-        <v>86775</v>
+        <v>91272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,21 +7022,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725712</v>
+        <v>725494</v>
       </c>
       <c r="R59" t="n">
-        <v>6385261</v>
+        <v>6385080</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,6 +7100,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7118,10 +7119,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128786101</v>
+        <v>128786091</v>
       </c>
       <c r="B60" t="n">
-        <v>86843</v>
+        <v>91272</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7129,21 +7130,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7153,10 +7154,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725528</v>
+        <v>725507</v>
       </c>
       <c r="R60" t="n">
-        <v>6385185</v>
+        <v>6385159</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,10 +7216,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128791453</v>
+        <v>128784654</v>
       </c>
       <c r="B61" t="n">
-        <v>91245</v>
+        <v>91272</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7246,14 +7247,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>725494</v>
       </c>
       <c r="R61" t="n">
-        <v>6385080</v>
+        <v>6385035</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7283,50 +7284,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128786091</v>
+        <v>128791517</v>
       </c>
       <c r="B62" t="n">
-        <v>91245</v>
+        <v>86802</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7334,34 +7324,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725507</v>
+        <v>725712</v>
       </c>
       <c r="R62" t="n">
-        <v>6385159</v>
+        <v>6385261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7391,9 +7381,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7408,22 +7408,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128784654</v>
+        <v>128786101</v>
       </c>
       <c r="B63" t="n">
-        <v>91245</v>
+        <v>86870</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7431,34 +7431,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725494</v>
+        <v>725528</v>
       </c>
       <c r="R63" t="n">
-        <v>6385035</v>
+        <v>6385185</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7505,12 +7505,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
         <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7615,32 +7615,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791459</v>
+        <v>128791475</v>
       </c>
       <c r="B65" t="n">
-        <v>86753</v>
+        <v>86954</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725746</v>
+        <v>725503</v>
       </c>
       <c r="R65" t="n">
-        <v>6385092</v>
+        <v>6385246</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,6 +7704,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7722,10 +7723,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791475</v>
+        <v>128791478</v>
       </c>
       <c r="B66" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7757,10 +7758,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725503</v>
+        <v>725685</v>
       </c>
       <c r="R66" t="n">
-        <v>6385246</v>
+        <v>6385124</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7792,7 +7793,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7802,7 +7803,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7830,32 +7831,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128791478</v>
+        <v>128791459</v>
       </c>
       <c r="B67" t="n">
-        <v>86927</v>
+        <v>86780</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7865,10 +7866,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>725685</v>
+        <v>725746</v>
       </c>
       <c r="R67" t="n">
-        <v>6385124</v>
+        <v>6385092</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7900,7 +7901,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7910,7 +7911,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7919,7 +7920,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>86927</v>
+        <v>91272</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R68" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,7 +8027,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8046,32 +8045,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>91245</v>
+        <v>86954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8081,10 +8080,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R69" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,6 +8134,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>128791503</v>
       </c>
       <c r="B70" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>128786092</v>
       </c>
       <c r="B71" t="n">
-        <v>91245</v>
+        <v>91272</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>128784653</v>
       </c>
       <c r="B72" t="n">
-        <v>91245</v>
+        <v>91272</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128791488</v>
       </c>
       <c r="B77" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>128791481</v>
       </c>
       <c r="B79" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>128791452</v>
       </c>
       <c r="B85" t="n">
-        <v>91245</v>
+        <v>91272</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>128786098</v>
       </c>
       <c r="B87" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128784675</v>
+        <v>128784669</v>
       </c>
       <c r="B89" t="n">
-        <v>86815</v>
+        <v>86976</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725536</v>
+        <v>725759</v>
       </c>
       <c r="R89" t="n">
-        <v>6385137</v>
+        <v>6385120</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784669</v>
+        <v>128784675</v>
       </c>
       <c r="B90" t="n">
-        <v>86949</v>
+        <v>86842</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725759</v>
+        <v>725536</v>
       </c>
       <c r="R90" t="n">
-        <v>6385120</v>
+        <v>6385137</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10320,7 +10320,7 @@
         <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>128784662</v>
       </c>
       <c r="B92" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>128784659</v>
       </c>
       <c r="B93" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10621,41 +10621,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>92771</v>
+        <v>87011</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R94" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10685,74 +10685,86 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128791477</v>
+        <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>86927</v>
+        <v>92798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725588</v>
+        <v>725556</v>
       </c>
       <c r="R95" t="n">
-        <v>6385289</v>
+        <v>6385239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10782,70 +10794,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791498</v>
+        <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>86984</v>
+        <v>86954</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10853,10 +10858,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725697</v>
+        <v>725588</v>
       </c>
       <c r="R96" t="n">
-        <v>6385241</v>
+        <v>6385289</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10888,7 +10893,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10898,12 +10903,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10931,10 +10931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B97" t="n">
-        <v>86984</v>
+        <v>86842</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,19 +10942,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10962,10 +10966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R97" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11007,7 +11011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11034,10 +11038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B98" t="n">
-        <v>86815</v>
+        <v>87011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11045,23 +11049,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R98" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11141,10 +11141,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B99" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,14 +11172,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R99" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,9 +11209,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,22 +11236,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B100" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,14 +11279,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R100" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11306,19 +11316,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,12 +11333,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11348,7 +11348,7 @@
         <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>128784661</v>
       </c>
       <c r="B102" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>128791473</v>
       </c>
       <c r="B103" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11654,45 +11654,41 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128786100</v>
+        <v>128791499</v>
       </c>
       <c r="B104" t="n">
-        <v>90905</v>
+        <v>87011</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4190</v>
+        <v>433</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>DC.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725528</v>
+        <v>725431</v>
       </c>
       <c r="R104" t="n">
-        <v>6385185</v>
+        <v>6385191</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11722,75 +11718,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784652</v>
+        <v>128786099</v>
       </c>
       <c r="B105" t="n">
-        <v>92753</v>
+        <v>91029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4363</v>
+        <v>5747</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725629</v>
+        <v>725542</v>
       </c>
       <c r="R105" t="n">
-        <v>6385285</v>
+        <v>6385225</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11837,53 +11842,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128791499</v>
+        <v>128786100</v>
       </c>
       <c r="B106" t="n">
-        <v>86984</v>
+        <v>90932</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>433</v>
+        <v>4190</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Geastrum striatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725431</v>
+        <v>725528</v>
       </c>
       <c r="R106" t="n">
-        <v>6385191</v>
+        <v>6385185</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11913,84 +11922,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128786099</v>
+        <v>128784652</v>
       </c>
       <c r="B107" t="n">
-        <v>91002</v>
+        <v>92780</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5747</v>
+        <v>4363</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725542</v>
+        <v>725629</v>
       </c>
       <c r="R107" t="n">
-        <v>6385225</v>
+        <v>6385285</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12037,12 +12037,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12052,7 +12052,7 @@
         <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,32 +12460,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128791487</v>
+        <v>128791462</v>
       </c>
       <c r="B112" t="n">
-        <v>86949</v>
+        <v>86756</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>725771</v>
+        <v>725541</v>
       </c>
       <c r="R112" t="n">
-        <v>6385103</v>
+        <v>6385088</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12549,7 +12549,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12568,10 +12567,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791462</v>
+        <v>128786106</v>
       </c>
       <c r="B113" t="n">
-        <v>86729</v>
+        <v>86780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12579,34 +12578,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725541</v>
+        <v>725520</v>
       </c>
       <c r="R113" t="n">
-        <v>6385088</v>
+        <v>6385158</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12636,19 +12635,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12663,57 +12652,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128786106</v>
+        <v>128791487</v>
       </c>
       <c r="B114" t="n">
-        <v>86753</v>
+        <v>86976</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725520</v>
+        <v>725771</v>
       </c>
       <c r="R114" t="n">
-        <v>6385158</v>
+        <v>6385103</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12743,29 +12732,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12775,7 +12775,7 @@
         <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12988,45 +12988,41 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128784676</v>
+        <v>128791508</v>
       </c>
       <c r="B117" t="n">
-        <v>86890</v>
+        <v>87011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725647</v>
+        <v>725757</v>
       </c>
       <c r="R117" t="n">
-        <v>6385255</v>
+        <v>6385187</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13056,9 +13052,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13073,44 +13079,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784668</v>
+        <v>128784676</v>
       </c>
       <c r="B118" t="n">
-        <v>86843</v>
+        <v>86917</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13120,10 +13126,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725725</v>
+        <v>725647</v>
       </c>
       <c r="R118" t="n">
-        <v>6385117</v>
+        <v>6385255</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13182,10 +13188,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128791508</v>
+        <v>128784668</v>
       </c>
       <c r="B119" t="n">
-        <v>86984</v>
+        <v>86870</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13193,30 +13199,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725757</v>
+        <v>725725</v>
       </c>
       <c r="R119" t="n">
-        <v>6385187</v>
+        <v>6385117</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13246,19 +13256,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13273,57 +13273,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128791483</v>
+        <v>128784658</v>
       </c>
       <c r="B120" t="n">
-        <v>86927</v>
+        <v>86802</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725645</v>
+        <v>725646</v>
       </c>
       <c r="R120" t="n">
-        <v>6385261</v>
+        <v>6385281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13353,50 +13353,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128786090</v>
+        <v>128786105</v>
       </c>
       <c r="B121" t="n">
-        <v>92771</v>
+        <v>96215</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13404,19 +13393,23 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6047725</v>
+        <v>2180</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13424,10 +13417,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725545</v>
+        <v>725537</v>
       </c>
       <c r="R121" t="n">
-        <v>6385234</v>
+        <v>6385216</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13486,10 +13479,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128786105</v>
+        <v>128791485</v>
       </c>
       <c r="B122" t="n">
-        <v>96188</v>
+        <v>98641</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13497,34 +13490,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2180</v>
+        <v>219862</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725537</v>
+        <v>725724</v>
       </c>
       <c r="R122" t="n">
-        <v>6385216</v>
+        <v>6385174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13554,9 +13547,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13571,57 +13574,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128784658</v>
+        <v>128791483</v>
       </c>
       <c r="B123" t="n">
-        <v>86775</v>
+        <v>86954</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725646</v>
+        <v>725645</v>
       </c>
       <c r="R123" t="n">
-        <v>6385281</v>
+        <v>6385261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13651,39 +13654,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128791485</v>
+        <v>128786090</v>
       </c>
       <c r="B124" t="n">
-        <v>98614</v>
+        <v>92798</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13691,34 +13705,30 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219862</v>
+        <v>6047725</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725724</v>
+        <v>725545</v>
       </c>
       <c r="R124" t="n">
-        <v>6385174</v>
+        <v>6385234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13748,19 +13758,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13775,12 +13775,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
         <v>128791460</v>
       </c>
       <c r="B125" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>128786102</v>
       </c>
       <c r="B126" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13991,32 +13991,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791448</v>
+        <v>128791495</v>
       </c>
       <c r="B127" t="n">
-        <v>91245</v>
+        <v>90910</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Vit taggsvamp</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14026,10 +14021,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725501</v>
+        <v>725745</v>
       </c>
       <c r="R127" t="n">
-        <v>6385071</v>
+        <v>6385094</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14061,7 +14056,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14071,7 +14066,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14098,10 +14093,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128784670</v>
+        <v>128791512</v>
       </c>
       <c r="B128" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14125,14 +14120,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725570</v>
+        <v>725631</v>
       </c>
       <c r="R128" t="n">
-        <v>6385186</v>
+        <v>6385124</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14162,9 +14157,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14179,22 +14184,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791512</v>
+        <v>128784670</v>
       </c>
       <c r="B129" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14218,14 +14223,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725631</v>
+        <v>725570</v>
       </c>
       <c r="R129" t="n">
-        <v>6385124</v>
+        <v>6385186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14255,19 +14260,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14282,39 +14277,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791495</v>
+        <v>128791448</v>
       </c>
       <c r="B130" t="n">
-        <v>90883</v>
+        <v>91272</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1000938</v>
+        <v>2015</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725745</v>
+        <v>725501</v>
       </c>
       <c r="R130" t="n">
-        <v>6385094</v>
+        <v>6385071</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14399,7 +14399,7 @@
         <v>128815373</v>
       </c>
       <c r="B131" t="n">
-        <v>86961</v>
+        <v>86988</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>128791455</v>
       </c>
       <c r="B132" t="n">
-        <v>87121</v>
+        <v>87148</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>128815450</v>
       </c>
       <c r="B133" t="n">
-        <v>86893</v>
+        <v>86920</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>128791501</v>
       </c>
       <c r="B134" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>128786095</v>
       </c>
       <c r="B135" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>128791510</v>
       </c>
       <c r="B136" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791453</v>
+        <v>128791517</v>
       </c>
       <c r="B59" t="n">
-        <v>91272</v>
+        <v>86802</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,21 +7022,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725494</v>
+        <v>725712</v>
       </c>
       <c r="R59" t="n">
-        <v>6385080</v>
+        <v>6385261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,7 +7100,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7119,7 +7118,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128786091</v>
+        <v>128791453</v>
       </c>
       <c r="B60" t="n">
         <v>91272</v>
@@ -7150,14 +7149,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R60" t="n">
-        <v>6385159</v>
+        <v>6385080</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7187,36 +7186,47 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784654</v>
+        <v>128786091</v>
       </c>
       <c r="B61" t="n">
         <v>91272</v>
@@ -7247,14 +7257,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R61" t="n">
-        <v>6385035</v>
+        <v>6385159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7301,22 +7311,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128791517</v>
+        <v>128784654</v>
       </c>
       <c r="B62" t="n">
-        <v>86802</v>
+        <v>91272</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7324,34 +7334,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725712</v>
+        <v>725494</v>
       </c>
       <c r="R62" t="n">
-        <v>6385261</v>
+        <v>6385035</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7381,19 +7391,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7408,12 +7408,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7615,32 +7615,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791475</v>
+        <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86954</v>
+        <v>86780</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725503</v>
+        <v>725746</v>
       </c>
       <c r="R65" t="n">
-        <v>6385246</v>
+        <v>6385092</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,7 +7704,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7723,7 +7722,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791478</v>
+        <v>128791475</v>
       </c>
       <c r="B66" t="n">
         <v>86954</v>
@@ -7758,10 +7757,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725685</v>
+        <v>725503</v>
       </c>
       <c r="R66" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7793,7 +7792,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7803,7 +7802,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7831,32 +7830,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128791459</v>
+        <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86780</v>
+        <v>86954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7866,10 +7865,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>725746</v>
+        <v>725685</v>
       </c>
       <c r="R67" t="n">
-        <v>6385092</v>
+        <v>6385124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7901,7 +7900,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7911,7 +7910,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7920,6 +7919,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B68" t="n">
-        <v>91272</v>
+        <v>86954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R68" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,6 +8027,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8045,32 +8046,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B69" t="n">
-        <v>86954</v>
+        <v>91272</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8080,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R69" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8125,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8134,7 +8135,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9709,10 +9709,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791452</v>
+        <v>128791489</v>
       </c>
       <c r="B85" t="n">
-        <v>91272</v>
+        <v>86976</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9720,21 +9720,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725424</v>
+        <v>725612</v>
       </c>
       <c r="R85" t="n">
-        <v>6384953</v>
+        <v>6385206</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9816,10 +9816,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791489</v>
+        <v>128791452</v>
       </c>
       <c r="B86" t="n">
-        <v>86976</v>
+        <v>91272</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9827,21 +9827,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>2015</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725612</v>
+        <v>725424</v>
       </c>
       <c r="R86" t="n">
-        <v>6385206</v>
+        <v>6384953</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11757,32 +11757,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128786099</v>
+        <v>128786100</v>
       </c>
       <c r="B105" t="n">
-        <v>91029</v>
+        <v>90932</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5747</v>
+        <v>4190</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725542</v>
+        <v>725528</v>
       </c>
       <c r="R105" t="n">
-        <v>6385225</v>
+        <v>6385185</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,6 +11836,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11854,10 +11855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B106" t="n">
-        <v>90932</v>
+        <v>92780</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11865,34 +11866,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R106" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11933,64 +11934,63 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128784652</v>
+        <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>92780</v>
+        <v>91029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4363</v>
+        <v>5747</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725629</v>
+        <v>725542</v>
       </c>
       <c r="R107" t="n">
-        <v>6385285</v>
+        <v>6385225</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12037,22 +12037,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128784666</v>
+        <v>128791479</v>
       </c>
       <c r="B108" t="n">
-        <v>107533</v>
+        <v>86954</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12060,34 +12060,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725501</v>
+        <v>725712</v>
       </c>
       <c r="R108" t="n">
-        <v>6385056</v>
+        <v>6385103</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,39 +12117,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128791479</v>
+        <v>128784666</v>
       </c>
       <c r="B109" t="n">
-        <v>86954</v>
+        <v>107533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12157,34 +12168,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725712</v>
+        <v>725501</v>
       </c>
       <c r="R109" t="n">
-        <v>6385103</v>
+        <v>6385056</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,40 +12225,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12988,41 +12988,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128791508</v>
+        <v>128784676</v>
       </c>
       <c r="B117" t="n">
-        <v>87011</v>
+        <v>86917</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725757</v>
+        <v>725647</v>
       </c>
       <c r="R117" t="n">
-        <v>6385187</v>
+        <v>6385255</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,19 +13056,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13079,57 +13073,53 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784676</v>
+        <v>128791508</v>
       </c>
       <c r="B118" t="n">
-        <v>86917</v>
+        <v>87011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725647</v>
+        <v>725757</v>
       </c>
       <c r="R118" t="n">
-        <v>6385255</v>
+        <v>6385187</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,9 +13149,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13176,12 +13176,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13285,45 +13285,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128784658</v>
+        <v>128791485</v>
       </c>
       <c r="B120" t="n">
-        <v>86802</v>
+        <v>98641</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>219862</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725646</v>
+        <v>725724</v>
       </c>
       <c r="R120" t="n">
-        <v>6385281</v>
+        <v>6385174</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13353,9 +13353,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13370,57 +13380,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128786105</v>
+        <v>128784658</v>
       </c>
       <c r="B121" t="n">
-        <v>96215</v>
+        <v>86802</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725537</v>
+        <v>725646</v>
       </c>
       <c r="R121" t="n">
-        <v>6385216</v>
+        <v>6385281</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13467,22 +13477,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128791485</v>
+        <v>128786105</v>
       </c>
       <c r="B122" t="n">
-        <v>98641</v>
+        <v>96215</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13490,34 +13500,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219862</v>
+        <v>2180</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725724</v>
+        <v>725537</v>
       </c>
       <c r="R122" t="n">
-        <v>6385174</v>
+        <v>6385216</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13547,19 +13557,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13574,12 +13574,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13787,34 +13787,30 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791460</v>
+        <v>128791512</v>
       </c>
       <c r="B125" t="n">
-        <v>86780</v>
+        <v>87011</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13822,10 +13818,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725718</v>
+        <v>725631</v>
       </c>
       <c r="R125" t="n">
-        <v>6385251</v>
+        <v>6385124</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13867,7 +13863,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13894,10 +13890,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128786102</v>
+        <v>128784670</v>
       </c>
       <c r="B126" t="n">
-        <v>86870</v>
+        <v>87011</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13905,34 +13901,30 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725513</v>
+        <v>725570</v>
       </c>
       <c r="R126" t="n">
-        <v>6385159</v>
+        <v>6385186</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13979,22 +13971,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791495</v>
+        <v>128791460</v>
       </c>
       <c r="B127" t="n">
-        <v>90910</v>
+        <v>86780</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14002,16 +13994,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1000938</v>
+        <v>3712</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14021,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725745</v>
+        <v>725718</v>
       </c>
       <c r="R127" t="n">
-        <v>6385094</v>
+        <v>6385251</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14056,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14066,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14093,10 +14090,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791512</v>
+        <v>128791448</v>
       </c>
       <c r="B128" t="n">
-        <v>87011</v>
+        <v>91272</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14104,19 +14101,23 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14124,10 +14125,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725631</v>
+        <v>725501</v>
       </c>
       <c r="R128" t="n">
-        <v>6385124</v>
+        <v>6385071</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14159,7 +14160,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14169,7 +14170,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14196,10 +14197,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128784670</v>
+        <v>128786102</v>
       </c>
       <c r="B129" t="n">
-        <v>87011</v>
+        <v>86870</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14207,30 +14208,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725570</v>
+        <v>725513</v>
       </c>
       <c r="R129" t="n">
-        <v>6385186</v>
+        <v>6385159</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14277,44 +14282,39 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791448</v>
+        <v>128791495</v>
       </c>
       <c r="B130" t="n">
-        <v>91272</v>
+        <v>90910</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Vit taggsvamp</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725501</v>
+        <v>725745</v>
       </c>
       <c r="R130" t="n">
-        <v>6385071</v>
+        <v>6385094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14396,10 +14396,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128815373</v>
+        <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>86988</v>
+        <v>87148</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14407,34 +14407,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>248939</v>
+        <v>451</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallpraktspindling</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius terpsichores</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Melot</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>725787</v>
+        <v>725394</v>
       </c>
       <c r="R131" t="n">
-        <v>6385165</v>
+        <v>6385091</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14466,7 +14469,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14476,12 +14479,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Bilddokumentation av Annas fynd. Ej exakta koordinater, från samma lokal.</t>
+          <t>? Något mindre kollekt</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14490,6 +14493,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14508,32 +14512,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128791455</v>
+        <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>87148</v>
+        <v>86920</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>451</v>
+        <v>6037417</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14546,10 +14550,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>725394</v>
+        <v>725669</v>
       </c>
       <c r="R132" t="n">
-        <v>6385091</v>
+        <v>6385183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14581,7 +14585,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14591,12 +14595,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>? Något mindre kollekt</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14624,48 +14623,41 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128815450</v>
+        <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>86920</v>
+        <v>87011</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6037417</v>
+        <v>433</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>725669</v>
+        <v>725439</v>
       </c>
       <c r="R133" t="n">
-        <v>6385183</v>
+        <v>6385189</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14697,7 +14689,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14707,7 +14699,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14716,7 +14708,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14735,7 +14726,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128791501</v>
+        <v>128786095</v>
       </c>
       <c r="B134" t="n">
         <v>87011</v>
@@ -14762,14 +14753,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>725439</v>
+        <v>725515</v>
       </c>
       <c r="R134" t="n">
-        <v>6385189</v>
+        <v>6385157</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14799,46 +14790,37 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128786095</v>
+        <v>128791510</v>
       </c>
       <c r="B135" t="n">
         <v>87011</v>
@@ -14865,14 +14847,14 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>725515</v>
+        <v>725665</v>
       </c>
       <c r="R135" t="n">
-        <v>6385157</v>
+        <v>6385180</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14902,71 +14884,87 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128791510</v>
+        <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>87011</v>
+        <v>86920</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>433</v>
+        <v>6037417</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>725665</v>
+        <v>725787</v>
       </c>
       <c r="R136" t="n">
-        <v>6385180</v>
+        <v>6385165</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14998,7 +14996,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15008,7 +15006,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Annas fynd. Ej exakta koordinater, från samma lokal.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15017,6 +15020,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791517</v>
+        <v>128791453</v>
       </c>
       <c r="B59" t="n">
-        <v>86802</v>
+        <v>91277</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,21 +7022,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725712</v>
+        <v>725494</v>
       </c>
       <c r="R59" t="n">
-        <v>6385261</v>
+        <v>6385080</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,6 +7100,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7118,10 +7119,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128791453</v>
+        <v>128786091</v>
       </c>
       <c r="B60" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7149,14 +7150,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R60" t="n">
-        <v>6385080</v>
+        <v>6385159</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7186,50 +7187,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128786091</v>
+        <v>128784654</v>
       </c>
       <c r="B61" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7257,14 +7247,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R61" t="n">
-        <v>6385159</v>
+        <v>6385035</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7311,44 +7301,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784654</v>
+        <v>128784663</v>
       </c>
       <c r="B62" t="n">
-        <v>91272</v>
+        <v>86958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7358,10 +7348,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725494</v>
+        <v>725739</v>
       </c>
       <c r="R62" t="n">
-        <v>6385035</v>
+        <v>6385174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7402,6 +7392,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7420,10 +7411,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128786101</v>
+        <v>128791517</v>
       </c>
       <c r="B63" t="n">
-        <v>86870</v>
+        <v>86806</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7431,34 +7422,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725528</v>
+        <v>725712</v>
       </c>
       <c r="R63" t="n">
-        <v>6385185</v>
+        <v>6385261</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7488,9 +7479,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7505,57 +7506,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128784663</v>
+        <v>128786101</v>
       </c>
       <c r="B64" t="n">
-        <v>86954</v>
+        <v>86874</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725739</v>
+        <v>725528</v>
       </c>
       <c r="R64" t="n">
-        <v>6385174</v>
+        <v>6385185</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7596,51 +7597,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791459</v>
+        <v>128791475</v>
       </c>
       <c r="B65" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725746</v>
+        <v>725503</v>
       </c>
       <c r="R65" t="n">
-        <v>6385092</v>
+        <v>6385246</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,6 +7704,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7722,10 +7723,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791475</v>
+        <v>128791478</v>
       </c>
       <c r="B66" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7757,10 +7758,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725503</v>
+        <v>725685</v>
       </c>
       <c r="R66" t="n">
-        <v>6385246</v>
+        <v>6385124</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7792,7 +7793,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7802,7 +7803,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7830,32 +7831,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128791478</v>
+        <v>128791459</v>
       </c>
       <c r="B67" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7865,10 +7866,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>725685</v>
+        <v>725746</v>
       </c>
       <c r="R67" t="n">
-        <v>6385124</v>
+        <v>6385092</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7900,7 +7901,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7910,7 +7911,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7919,7 +7920,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>86954</v>
+        <v>91277</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R68" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,7 +8027,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8046,32 +8045,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>91272</v>
+        <v>86958</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8081,10 +8080,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R69" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,6 +8134,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128791503</v>
+        <v>128786092</v>
       </c>
       <c r="B70" t="n">
-        <v>87011</v>
+        <v>91277</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,30 +8164,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>725496</v>
+        <v>725499</v>
       </c>
       <c r="R70" t="n">
-        <v>6385236</v>
+        <v>6385065</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8217,19 +8221,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,22 +8238,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128786092</v>
+        <v>128784653</v>
       </c>
       <c r="B71" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8287,14 +8281,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>725499</v>
+        <v>725496</v>
       </c>
       <c r="R71" t="n">
-        <v>6385065</v>
+        <v>6385075</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8341,22 +8335,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128784653</v>
+        <v>128791503</v>
       </c>
       <c r="B72" t="n">
-        <v>91272</v>
+        <v>87015</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,34 +8358,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385075</v>
+        <v>6385236</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8421,9 +8411,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128791488</v>
       </c>
       <c r="B77" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>128791481</v>
       </c>
       <c r="B79" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>128791489</v>
       </c>
       <c r="B85" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9816,45 +9816,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791452</v>
+        <v>128786098</v>
       </c>
       <c r="B86" t="n">
-        <v>91272</v>
+        <v>98647</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2015</v>
+        <v>219862</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725424</v>
+        <v>725577</v>
       </c>
       <c r="R86" t="n">
-        <v>6384953</v>
+        <v>6385250</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9884,19 +9884,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9911,57 +9901,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128786098</v>
+        <v>128791452</v>
       </c>
       <c r="B87" t="n">
-        <v>98641</v>
+        <v>91277</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219862</v>
+        <v>2015</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725577</v>
+        <v>725424</v>
       </c>
       <c r="R87" t="n">
-        <v>6385250</v>
+        <v>6384953</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9991,9 +9981,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>128784669</v>
       </c>
       <c r="B89" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>128784675</v>
       </c>
       <c r="B90" t="n">
-        <v>86842</v>
+        <v>86846</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>128784662</v>
       </c>
       <c r="B92" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>128784659</v>
       </c>
       <c r="B93" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10931,10 +10931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B97" t="n">
-        <v>86842</v>
+        <v>87015</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,23 +10942,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10966,10 +10962,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R97" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11001,7 +10997,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11011,7 +11007,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11038,10 +11034,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B98" t="n">
-        <v>87011</v>
+        <v>86846</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11049,19 +11045,23 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R98" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11144,7 +11144,7 @@
         <v>128791516</v>
       </c>
       <c r="B99" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128784657</v>
       </c>
       <c r="B100" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>128784661</v>
       </c>
       <c r="B102" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>128791473</v>
       </c>
       <c r="B103" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11654,41 +11654,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128791499</v>
+        <v>128786100</v>
       </c>
       <c r="B104" t="n">
-        <v>87011</v>
+        <v>90937</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>4190</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Geastrum striatum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725431</v>
+        <v>725528</v>
       </c>
       <c r="R104" t="n">
-        <v>6385191</v>
+        <v>6385185</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11718,49 +11722,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B105" t="n">
-        <v>90932</v>
+        <v>92785</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11768,34 +11763,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R105" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,64 +11831,63 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128784652</v>
+        <v>128786099</v>
       </c>
       <c r="B106" t="n">
-        <v>92780</v>
+        <v>91034</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4363</v>
+        <v>5747</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725629</v>
+        <v>725542</v>
       </c>
       <c r="R106" t="n">
-        <v>6385285</v>
+        <v>6385225</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11940,22 +11934,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128786099</v>
+        <v>128791499</v>
       </c>
       <c r="B107" t="n">
-        <v>91029</v>
+        <v>87015</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11963,34 +11957,30 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5747</v>
+        <v>433</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725542</v>
+        <v>725431</v>
       </c>
       <c r="R107" t="n">
-        <v>6385225</v>
+        <v>6385191</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12020,9 +12010,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,22 +12037,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128791479</v>
+        <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>86954</v>
+        <v>107539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12060,34 +12060,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725712</v>
+        <v>725501</v>
       </c>
       <c r="R108" t="n">
-        <v>6385103</v>
+        <v>6385056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,50 +12117,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128784666</v>
+        <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>107533</v>
+        <v>86958</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12168,34 +12157,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725501</v>
+        <v>725712</v>
       </c>
       <c r="R109" t="n">
-        <v>6385056</v>
+        <v>6385103</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12225,29 +12214,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,32 +12460,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128791462</v>
+        <v>128791487</v>
       </c>
       <c r="B112" t="n">
-        <v>86756</v>
+        <v>86980</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>725541</v>
+        <v>725771</v>
       </c>
       <c r="R112" t="n">
-        <v>6385088</v>
+        <v>6385103</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12549,6 +12549,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12567,10 +12568,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128786106</v>
+        <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86780</v>
+        <v>86760</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12578,34 +12579,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725520</v>
+        <v>725541</v>
       </c>
       <c r="R113" t="n">
-        <v>6385158</v>
+        <v>6385088</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12635,9 +12636,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12652,57 +12663,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128791487</v>
+        <v>128786106</v>
       </c>
       <c r="B114" t="n">
-        <v>86976</v>
+        <v>86784</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725771</v>
+        <v>725520</v>
       </c>
       <c r="R114" t="n">
-        <v>6385103</v>
+        <v>6385158</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12732,40 +12743,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12775,7 +12775,7 @@
         <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12988,45 +12988,41 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128784676</v>
+        <v>128791508</v>
       </c>
       <c r="B117" t="n">
-        <v>86917</v>
+        <v>87015</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725647</v>
+        <v>725757</v>
       </c>
       <c r="R117" t="n">
-        <v>6385255</v>
+        <v>6385187</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13056,9 +13052,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13073,53 +13079,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128791508</v>
+        <v>128784676</v>
       </c>
       <c r="B118" t="n">
-        <v>87011</v>
+        <v>86921</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725757</v>
+        <v>725647</v>
       </c>
       <c r="R118" t="n">
-        <v>6385187</v>
+        <v>6385255</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13149,19 +13159,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13176,12 +13176,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13191,7 +13191,7 @@
         <v>128784668</v>
       </c>
       <c r="B119" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13285,32 +13285,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128791485</v>
+        <v>128791483</v>
       </c>
       <c r="B120" t="n">
-        <v>98641</v>
+        <v>86958</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13320,10 +13320,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725724</v>
+        <v>725645</v>
       </c>
       <c r="R120" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13374,6 +13374,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13392,45 +13393,41 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128784658</v>
+        <v>128786090</v>
       </c>
       <c r="B121" t="n">
-        <v>86802</v>
+        <v>92803</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725646</v>
+        <v>725545</v>
       </c>
       <c r="R121" t="n">
-        <v>6385281</v>
+        <v>6385234</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13477,57 +13474,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128786105</v>
+        <v>128784658</v>
       </c>
       <c r="B122" t="n">
-        <v>96215</v>
+        <v>86806</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725537</v>
+        <v>725646</v>
       </c>
       <c r="R122" t="n">
-        <v>6385216</v>
+        <v>6385281</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13574,57 +13571,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128791483</v>
+        <v>128786105</v>
       </c>
       <c r="B123" t="n">
-        <v>86954</v>
+        <v>96221</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725645</v>
+        <v>725537</v>
       </c>
       <c r="R123" t="n">
-        <v>6385261</v>
+        <v>6385216</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13654,50 +13651,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786090</v>
+        <v>128791485</v>
       </c>
       <c r="B124" t="n">
-        <v>92798</v>
+        <v>98647</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13705,30 +13691,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6047725</v>
+        <v>219862</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725545</v>
+        <v>725724</v>
       </c>
       <c r="R124" t="n">
-        <v>6385234</v>
+        <v>6385174</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13758,9 +13748,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13775,12 +13775,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
         <v>128791512</v>
       </c>
       <c r="B125" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>128784670</v>
       </c>
       <c r="B126" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13983,32 +13983,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791460</v>
+        <v>128791448</v>
       </c>
       <c r="B127" t="n">
-        <v>86780</v>
+        <v>91277</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14018,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725718</v>
+        <v>725501</v>
       </c>
       <c r="R127" t="n">
-        <v>6385251</v>
+        <v>6385071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14090,32 +14090,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791448</v>
+        <v>128791460</v>
       </c>
       <c r="B128" t="n">
-        <v>91272</v>
+        <v>86784</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725501</v>
+        <v>725718</v>
       </c>
       <c r="R128" t="n">
-        <v>6385071</v>
+        <v>6385251</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14197,45 +14197,40 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128786102</v>
+        <v>128791495</v>
       </c>
       <c r="B129" t="n">
-        <v>86870</v>
+        <v>90915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>248956</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Gulsträngad fagerspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725513</v>
+        <v>725745</v>
       </c>
       <c r="R129" t="n">
-        <v>6385159</v>
+        <v>6385094</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14265,9 +14260,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14282,52 +14287,57 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791495</v>
+        <v>128786102</v>
       </c>
       <c r="B130" t="n">
-        <v>90910</v>
+        <v>86874</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1000938</v>
+        <v>248956</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725745</v>
+        <v>725513</v>
       </c>
       <c r="R130" t="n">
-        <v>6385094</v>
+        <v>6385159</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14357,19 +14367,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -14399,7 +14399,7 @@
         <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>87148</v>
+        <v>87152</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>86920</v>
+        <v>86924</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>128786095</v>
       </c>
       <c r="B134" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>128791510</v>
       </c>
       <c r="B135" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>86920</v>
+        <v>86924</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791453</v>
+        <v>128791517</v>
       </c>
       <c r="B59" t="n">
-        <v>91277</v>
+        <v>86806</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,21 +7022,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725494</v>
+        <v>725712</v>
       </c>
       <c r="R59" t="n">
-        <v>6385080</v>
+        <v>6385261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,7 +7100,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7119,10 +7118,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128786091</v>
+        <v>128791453</v>
       </c>
       <c r="B60" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7150,14 +7149,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R60" t="n">
-        <v>6385159</v>
+        <v>6385080</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7187,39 +7186,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784654</v>
+        <v>128786091</v>
       </c>
       <c r="B61" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7247,14 +7257,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R61" t="n">
-        <v>6385035</v>
+        <v>6385159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7301,44 +7311,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784663</v>
+        <v>128784654</v>
       </c>
       <c r="B62" t="n">
-        <v>86958</v>
+        <v>91282</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7348,10 +7358,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725739</v>
+        <v>725494</v>
       </c>
       <c r="R62" t="n">
-        <v>6385174</v>
+        <v>6385035</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7392,7 +7402,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7411,45 +7420,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128791517</v>
+        <v>128784663</v>
       </c>
       <c r="B63" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725712</v>
+        <v>725739</v>
       </c>
       <c r="R63" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,39 +7488,30 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7521,7 +7521,7 @@
         <v>128786101</v>
       </c>
       <c r="B64" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7615,32 +7615,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791475</v>
+        <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86958</v>
+        <v>86784</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725503</v>
+        <v>725746</v>
       </c>
       <c r="R65" t="n">
-        <v>6385246</v>
+        <v>6385092</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,7 +7704,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7723,10 +7722,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791478</v>
+        <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7758,10 +7757,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725685</v>
+        <v>725503</v>
       </c>
       <c r="R66" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7793,7 +7792,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7803,7 +7802,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7831,32 +7830,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128791459</v>
+        <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7866,10 +7865,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>725746</v>
+        <v>725685</v>
       </c>
       <c r="R67" t="n">
-        <v>6385092</v>
+        <v>6385124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7901,7 +7900,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7911,7 +7910,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7920,6 +7919,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128786092</v>
+        <v>128791503</v>
       </c>
       <c r="B70" t="n">
-        <v>91277</v>
+        <v>87016</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,34 +8164,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>725499</v>
+        <v>725496</v>
       </c>
       <c r="R70" t="n">
-        <v>6385065</v>
+        <v>6385236</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8221,9 +8217,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8238,22 +8244,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784653</v>
+        <v>128786092</v>
       </c>
       <c r="B71" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8281,14 +8287,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>725496</v>
+        <v>725499</v>
       </c>
       <c r="R71" t="n">
-        <v>6385075</v>
+        <v>6385065</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8335,22 +8341,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791503</v>
+        <v>128784653</v>
       </c>
       <c r="B72" t="n">
-        <v>87015</v>
+        <v>91282</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,30 +8364,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385236</v>
+        <v>6385075</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8411,19 +8421,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8754,30 +8754,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791506</v>
+        <v>128791465</v>
       </c>
       <c r="B76" t="n">
-        <v>87015</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8785,10 +8789,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>725546</v>
+        <v>725458</v>
       </c>
       <c r="R76" t="n">
-        <v>6385296</v>
+        <v>6385186</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8820,7 +8824,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8830,7 +8834,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8839,6 +8843,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8857,32 +8862,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791488</v>
+        <v>128791481</v>
       </c>
       <c r="B77" t="n">
-        <v>86980</v>
+        <v>86959</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>725580</v>
+        <v>725669</v>
       </c>
       <c r="R77" t="n">
-        <v>6385121</v>
+        <v>6385183</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8927,7 +8932,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8937,7 +8942,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8946,6 +8951,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8964,34 +8970,30 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791465</v>
+        <v>128791506</v>
       </c>
       <c r="B78" t="n">
-        <v>86958</v>
+        <v>87016</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8999,10 +9001,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>725458</v>
+        <v>725546</v>
       </c>
       <c r="R78" t="n">
-        <v>6385186</v>
+        <v>6385296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9034,7 +9036,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9044,7 +9046,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9053,7 +9055,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9072,32 +9073,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128791481</v>
+        <v>128791488</v>
       </c>
       <c r="B79" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9108,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>725669</v>
+        <v>725580</v>
       </c>
       <c r="R79" t="n">
-        <v>6385183</v>
+        <v>6385121</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9142,7 +9143,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9152,7 +9153,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,7 +9162,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9709,45 +9709,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791489</v>
+        <v>128786098</v>
       </c>
       <c r="B85" t="n">
-        <v>86980</v>
+        <v>98654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725612</v>
+        <v>725577</v>
       </c>
       <c r="R85" t="n">
-        <v>6385206</v>
+        <v>6385250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,19 +9777,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9804,57 +9794,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128786098</v>
+        <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>98647</v>
+        <v>86981</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725577</v>
+        <v>725612</v>
       </c>
       <c r="R86" t="n">
-        <v>6385250</v>
+        <v>6385206</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9884,9 +9874,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9901,12 +9901,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
         <v>128791452</v>
       </c>
       <c r="B87" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128784669</v>
+        <v>128784675</v>
       </c>
       <c r="B89" t="n">
-        <v>86980</v>
+        <v>86846</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725759</v>
+        <v>725536</v>
       </c>
       <c r="R89" t="n">
-        <v>6385120</v>
+        <v>6385137</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784675</v>
+        <v>128784669</v>
       </c>
       <c r="B90" t="n">
-        <v>86846</v>
+        <v>86981</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725536</v>
+        <v>725759</v>
       </c>
       <c r="R90" t="n">
-        <v>6385137</v>
+        <v>6385120</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10320,7 +10320,7 @@
         <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>128784662</v>
       </c>
       <c r="B92" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>128784659</v>
       </c>
       <c r="B93" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>128791504</v>
       </c>
       <c r="B97" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B99" t="n">
         <v>86806</v>
@@ -11172,14 +11172,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R99" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,19 +11209,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11236,19 +11226,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B100" t="n">
         <v>86806</v>
@@ -11279,14 +11269,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R100" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11316,9 +11306,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,12 +11333,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11348,7 +11348,7 @@
         <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>128784661</v>
       </c>
       <c r="B102" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>128791473</v>
       </c>
       <c r="B103" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B104" t="n">
-        <v>90937</v>
+        <v>92790</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,34 +11665,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R104" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11733,29 +11733,28 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784652</v>
+        <v>128786100</v>
       </c>
       <c r="B105" t="n">
-        <v>92785</v>
+        <v>90942</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11763,34 +11762,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4363</v>
+        <v>4190</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725629</v>
+        <v>725528</v>
       </c>
       <c r="R105" t="n">
-        <v>6385285</v>
+        <v>6385185</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11831,18 +11830,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11852,7 +11852,7 @@
         <v>128786099</v>
       </c>
       <c r="B106" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>128791499</v>
       </c>
       <c r="B107" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>107539</v>
+        <v>107546</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>128791487</v>
       </c>
       <c r="B112" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>128791508</v>
       </c>
       <c r="B117" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>128784676</v>
       </c>
       <c r="B118" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>128784668</v>
       </c>
       <c r="B119" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13285,32 +13285,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128791483</v>
+        <v>128791485</v>
       </c>
       <c r="B120" t="n">
-        <v>86958</v>
+        <v>98654</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13320,10 +13320,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725645</v>
+        <v>725724</v>
       </c>
       <c r="R120" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13374,7 +13374,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13393,41 +13392,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128786090</v>
+        <v>128791483</v>
       </c>
       <c r="B121" t="n">
-        <v>92803</v>
+        <v>86959</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725545</v>
+        <v>725645</v>
       </c>
       <c r="R121" t="n">
-        <v>6385234</v>
+        <v>6385261</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13457,74 +13460,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128784658</v>
+        <v>128786090</v>
       </c>
       <c r="B122" t="n">
-        <v>86806</v>
+        <v>92808</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725646</v>
+        <v>725545</v>
       </c>
       <c r="R122" t="n">
-        <v>6385281</v>
+        <v>6385234</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13571,57 +13581,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128786105</v>
+        <v>128784658</v>
       </c>
       <c r="B123" t="n">
-        <v>96221</v>
+        <v>86806</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725537</v>
+        <v>725646</v>
       </c>
       <c r="R123" t="n">
-        <v>6385216</v>
+        <v>6385281</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13668,22 +13678,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128791485</v>
+        <v>128786105</v>
       </c>
       <c r="B124" t="n">
-        <v>98647</v>
+        <v>96228</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13691,34 +13701,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219862</v>
+        <v>2180</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725724</v>
+        <v>725537</v>
       </c>
       <c r="R124" t="n">
-        <v>6385174</v>
+        <v>6385216</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13748,19 +13758,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13775,42 +13775,46 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791512</v>
+        <v>128791460</v>
       </c>
       <c r="B125" t="n">
-        <v>87015</v>
+        <v>86784</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>433</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13818,10 +13822,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725631</v>
+        <v>725718</v>
       </c>
       <c r="R125" t="n">
-        <v>6385124</v>
+        <v>6385251</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13853,7 +13857,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13863,7 +13867,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13893,7 +13897,7 @@
         <v>128784670</v>
       </c>
       <c r="B126" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13983,10 +13987,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791448</v>
+        <v>128791512</v>
       </c>
       <c r="B127" t="n">
-        <v>91277</v>
+        <v>87016</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13994,23 +13998,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14018,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725501</v>
+        <v>725631</v>
       </c>
       <c r="R127" t="n">
-        <v>6385071</v>
+        <v>6385124</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14090,32 +14090,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791460</v>
+        <v>128791448</v>
       </c>
       <c r="B128" t="n">
-        <v>86784</v>
+        <v>91282</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725718</v>
+        <v>725501</v>
       </c>
       <c r="R128" t="n">
-        <v>6385251</v>
+        <v>6385071</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14200,7 +14200,7 @@
         <v>128791495</v>
       </c>
       <c r="B129" t="n">
-        <v>90915</v>
+        <v>90920</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>128786102</v>
       </c>
       <c r="B130" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>87152</v>
+        <v>87153</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>86924</v>
+        <v>86925</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>128786095</v>
       </c>
       <c r="B134" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>128791510</v>
       </c>
       <c r="B135" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>86924</v>
+        <v>86925</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,45 +7011,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791517</v>
+        <v>128784663</v>
       </c>
       <c r="B59" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725712</v>
+        <v>725739</v>
       </c>
       <c r="R59" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7079,49 +7079,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128791453</v>
+        <v>128786101</v>
       </c>
       <c r="B60" t="n">
-        <v>91282</v>
+        <v>86875</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7129,34 +7120,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725494</v>
+        <v>725528</v>
       </c>
       <c r="R60" t="n">
-        <v>6385080</v>
+        <v>6385185</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7186,50 +7177,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128786091</v>
+        <v>128791517</v>
       </c>
       <c r="B61" t="n">
-        <v>91282</v>
+        <v>86806</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7237,34 +7217,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725507</v>
+        <v>725712</v>
       </c>
       <c r="R61" t="n">
-        <v>6385159</v>
+        <v>6385261</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7294,9 +7274,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7311,19 +7301,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784654</v>
+        <v>128791453</v>
       </c>
       <c r="B62" t="n">
         <v>91282</v>
@@ -7354,14 +7344,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>725494</v>
       </c>
       <c r="R62" t="n">
-        <v>6385035</v>
+        <v>6385080</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7391,74 +7381,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128784663</v>
+        <v>128786091</v>
       </c>
       <c r="B63" t="n">
-        <v>86959</v>
+        <v>91282</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725739</v>
+        <v>725507</v>
       </c>
       <c r="R63" t="n">
-        <v>6385174</v>
+        <v>6385159</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7499,29 +7500,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128786101</v>
+        <v>128784654</v>
       </c>
       <c r="B64" t="n">
-        <v>86875</v>
+        <v>91282</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7529,34 +7529,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725528</v>
+        <v>725494</v>
       </c>
       <c r="R64" t="n">
-        <v>6385185</v>
+        <v>6385035</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7603,12 +7603,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B68" t="n">
-        <v>91282</v>
+        <v>86959</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R68" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,6 +8027,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8045,32 +8046,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B69" t="n">
-        <v>86959</v>
+        <v>91282</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8080,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R69" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8125,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8134,7 +8135,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8754,34 +8754,30 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791465</v>
+        <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>87016</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8789,10 +8785,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>725458</v>
+        <v>725546</v>
       </c>
       <c r="R76" t="n">
-        <v>6385186</v>
+        <v>6385296</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8824,7 +8820,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8834,7 +8830,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8843,7 +8839,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8862,32 +8857,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791481</v>
+        <v>128791488</v>
       </c>
       <c r="B77" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8897,10 +8892,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>725669</v>
+        <v>725580</v>
       </c>
       <c r="R77" t="n">
-        <v>6385183</v>
+        <v>6385121</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8932,7 +8927,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8942,7 +8937,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8951,7 +8946,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8970,30 +8964,34 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791506</v>
+        <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>87016</v>
+        <v>86959</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9001,10 +8999,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>725546</v>
+        <v>725458</v>
       </c>
       <c r="R78" t="n">
-        <v>6385296</v>
+        <v>6385186</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9036,7 +9034,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9046,7 +9044,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9055,6 +9053,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9073,32 +9072,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128791488</v>
+        <v>128791481</v>
       </c>
       <c r="B79" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9108,10 +9107,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>725580</v>
+        <v>725669</v>
       </c>
       <c r="R79" t="n">
-        <v>6385121</v>
+        <v>6385183</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9143,7 +9142,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9153,7 +9152,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9162,6 +9161,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9709,45 +9709,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128786098</v>
+        <v>128791452</v>
       </c>
       <c r="B85" t="n">
-        <v>98654</v>
+        <v>91282</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219862</v>
+        <v>2015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725577</v>
+        <v>725424</v>
       </c>
       <c r="R85" t="n">
-        <v>6385250</v>
+        <v>6384953</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,9 +9777,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9794,12 +9804,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9913,45 +9923,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791452</v>
+        <v>128786098</v>
       </c>
       <c r="B87" t="n">
-        <v>91282</v>
+        <v>98654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2015</v>
+        <v>219862</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725424</v>
+        <v>725577</v>
       </c>
       <c r="R87" t="n">
-        <v>6384953</v>
+        <v>6385250</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9981,19 +9991,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128784675</v>
+        <v>128784669</v>
       </c>
       <c r="B89" t="n">
-        <v>86846</v>
+        <v>86981</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725536</v>
+        <v>725759</v>
       </c>
       <c r="R89" t="n">
-        <v>6385137</v>
+        <v>6385120</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784669</v>
+        <v>128784675</v>
       </c>
       <c r="B90" t="n">
-        <v>86981</v>
+        <v>86846</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725759</v>
+        <v>725536</v>
       </c>
       <c r="R90" t="n">
-        <v>6385120</v>
+        <v>6385137</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10621,41 +10621,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128791498</v>
+        <v>128786089</v>
       </c>
       <c r="B94" t="n">
-        <v>87016</v>
+        <v>92808</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725697</v>
+        <v>725556</v>
       </c>
       <c r="R94" t="n">
-        <v>6385241</v>
+        <v>6385239</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10685,86 +10685,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128786089</v>
+        <v>128791477</v>
       </c>
       <c r="B95" t="n">
-        <v>92808</v>
+        <v>86959</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725556</v>
+        <v>725588</v>
       </c>
       <c r="R95" t="n">
-        <v>6385239</v>
+        <v>6385289</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10794,63 +10782,70 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791477</v>
+        <v>128791498</v>
       </c>
       <c r="B96" t="n">
-        <v>86959</v>
+        <v>87016</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10858,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725588</v>
+        <v>725697</v>
       </c>
       <c r="R96" t="n">
-        <v>6385289</v>
+        <v>6385241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10893,7 +10888,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10903,7 +10898,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10931,10 +10931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B97" t="n">
-        <v>87016</v>
+        <v>86846</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,19 +10942,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10962,10 +10966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R97" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11007,7 +11011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11034,10 +11038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B98" t="n">
-        <v>86846</v>
+        <v>87016</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11045,23 +11049,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R98" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11141,7 +11141,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B99" t="n">
         <v>86806</v>
@@ -11172,14 +11172,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R99" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,9 +11209,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,19 +11236,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B100" t="n">
         <v>86806</v>
@@ -11269,14 +11279,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R100" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11306,19 +11316,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,12 +11333,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11654,45 +11654,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128784652</v>
+        <v>128791479</v>
       </c>
       <c r="B104" t="n">
-        <v>92790</v>
+        <v>86959</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4363</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725629</v>
+        <v>725712</v>
       </c>
       <c r="R104" t="n">
-        <v>6385285</v>
+        <v>6385103</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11722,29 +11722,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11849,45 +11860,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128786099</v>
+        <v>128784666</v>
       </c>
       <c r="B106" t="n">
-        <v>91039</v>
+        <v>107546</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5747</v>
+        <v>220079</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725542</v>
+        <v>725501</v>
       </c>
       <c r="R106" t="n">
-        <v>6385225</v>
+        <v>6385056</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11934,12 +11945,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12049,45 +12060,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128784666</v>
+        <v>128786099</v>
       </c>
       <c r="B108" t="n">
-        <v>107546</v>
+        <v>91039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220079</v>
+        <v>5747</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725501</v>
+        <v>725542</v>
       </c>
       <c r="R108" t="n">
-        <v>6385056</v>
+        <v>6385225</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12134,57 +12145,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128791479</v>
+        <v>128784652</v>
       </c>
       <c r="B109" t="n">
-        <v>86959</v>
+        <v>92790</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>4363</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725712</v>
+        <v>725629</v>
       </c>
       <c r="R109" t="n">
-        <v>6385103</v>
+        <v>6385285</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,40 +12225,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12568,32 +12568,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791462</v>
+        <v>128791480</v>
       </c>
       <c r="B113" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725541</v>
+        <v>725785</v>
       </c>
       <c r="R113" t="n">
-        <v>6385088</v>
+        <v>6385095</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,6 +12657,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12675,45 +12676,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128786106</v>
+        <v>128791467</v>
       </c>
       <c r="B114" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725520</v>
+        <v>725756</v>
       </c>
       <c r="R114" t="n">
-        <v>6385158</v>
+        <v>6385191</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12743,61 +12744,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128791480</v>
+        <v>128791462</v>
       </c>
       <c r="B115" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12807,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>725785</v>
+        <v>725541</v>
       </c>
       <c r="R115" t="n">
-        <v>6385095</v>
+        <v>6385088</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12842,7 +12854,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12852,7 +12864,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,7 +12873,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12880,45 +12891,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128791467</v>
+        <v>128786106</v>
       </c>
       <c r="B116" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>725756</v>
+        <v>725520</v>
       </c>
       <c r="R116" t="n">
-        <v>6385191</v>
+        <v>6385158</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12948,40 +12959,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13285,45 +13285,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128791485</v>
+        <v>128784658</v>
       </c>
       <c r="B120" t="n">
-        <v>98654</v>
+        <v>86806</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219862</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725724</v>
+        <v>725646</v>
       </c>
       <c r="R120" t="n">
-        <v>6385174</v>
+        <v>6385281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13353,19 +13353,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13380,57 +13370,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128791483</v>
+        <v>128786105</v>
       </c>
       <c r="B121" t="n">
-        <v>86959</v>
+        <v>96228</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725645</v>
+        <v>725537</v>
       </c>
       <c r="R121" t="n">
-        <v>6385261</v>
+        <v>6385216</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13460,50 +13450,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128786090</v>
+        <v>128791485</v>
       </c>
       <c r="B122" t="n">
-        <v>92808</v>
+        <v>98654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13511,30 +13490,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6047725</v>
+        <v>219862</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725545</v>
+        <v>725724</v>
       </c>
       <c r="R122" t="n">
-        <v>6385234</v>
+        <v>6385174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13564,9 +13547,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13581,57 +13574,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128784658</v>
+        <v>128791483</v>
       </c>
       <c r="B123" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725646</v>
+        <v>725645</v>
       </c>
       <c r="R123" t="n">
-        <v>6385281</v>
+        <v>6385261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13661,39 +13654,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786105</v>
+        <v>128786090</v>
       </c>
       <c r="B124" t="n">
-        <v>96228</v>
+        <v>92808</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13701,23 +13705,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2180</v>
+        <v>6047725</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725537</v>
+        <v>725545</v>
       </c>
       <c r="R124" t="n">
-        <v>6385216</v>
+        <v>6385234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13787,10 +13787,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791460</v>
+        <v>128791495</v>
       </c>
       <c r="B125" t="n">
-        <v>86784</v>
+        <v>90920</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,21 +13798,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3712</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Blå slemspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13822,10 +13817,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725718</v>
+        <v>725745</v>
       </c>
       <c r="R125" t="n">
-        <v>6385251</v>
+        <v>6385094</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13857,7 +13852,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13867,7 +13862,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13894,10 +13889,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128784670</v>
+        <v>128786102</v>
       </c>
       <c r="B126" t="n">
-        <v>87016</v>
+        <v>86875</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13905,30 +13900,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725570</v>
+        <v>725513</v>
       </c>
       <c r="R126" t="n">
-        <v>6385186</v>
+        <v>6385159</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13975,19 +13974,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791512</v>
+        <v>128784670</v>
       </c>
       <c r="B127" t="n">
         <v>87016</v>
@@ -14014,14 +14013,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725631</v>
+        <v>725570</v>
       </c>
       <c r="R127" t="n">
-        <v>6385124</v>
+        <v>6385186</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14051,19 +14050,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14078,12 +14067,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14197,29 +14186,30 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791495</v>
+        <v>128791512</v>
       </c>
       <c r="B129" t="n">
-        <v>90920</v>
+        <v>87016</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1000938</v>
+        <v>433</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Geastrum</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14227,10 +14217,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725745</v>
+        <v>725631</v>
       </c>
       <c r="R129" t="n">
-        <v>6385094</v>
+        <v>6385124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14262,7 +14252,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14272,7 +14262,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14299,45 +14289,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128786102</v>
+        <v>128791460</v>
       </c>
       <c r="B130" t="n">
-        <v>86875</v>
+        <v>86784</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725513</v>
+        <v>725718</v>
       </c>
       <c r="R130" t="n">
-        <v>6385159</v>
+        <v>6385251</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,9 +14357,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,45 +7011,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128784663</v>
+        <v>128791517</v>
       </c>
       <c r="B59" t="n">
-        <v>86959</v>
+        <v>86806</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725739</v>
+        <v>725712</v>
       </c>
       <c r="R59" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7079,40 +7079,49 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128786101</v>
+        <v>128791453</v>
       </c>
       <c r="B60" t="n">
-        <v>86875</v>
+        <v>91282</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7120,34 +7129,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725528</v>
+        <v>725494</v>
       </c>
       <c r="R60" t="n">
-        <v>6385185</v>
+        <v>6385080</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7177,39 +7186,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128791517</v>
+        <v>128786091</v>
       </c>
       <c r="B61" t="n">
-        <v>86806</v>
+        <v>91282</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7217,34 +7237,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725712</v>
+        <v>725507</v>
       </c>
       <c r="R61" t="n">
-        <v>6385261</v>
+        <v>6385159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7274,19 +7294,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7301,19 +7311,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128791453</v>
+        <v>128784654</v>
       </c>
       <c r="B62" t="n">
         <v>91282</v>
@@ -7344,14 +7354,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>725494</v>
       </c>
       <c r="R62" t="n">
-        <v>6385080</v>
+        <v>6385035</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7381,50 +7391,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128786091</v>
+        <v>128786101</v>
       </c>
       <c r="B63" t="n">
-        <v>91282</v>
+        <v>86875</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7432,21 +7431,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7456,10 +7455,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725507</v>
+        <v>725528</v>
       </c>
       <c r="R63" t="n">
-        <v>6385159</v>
+        <v>6385185</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7518,32 +7517,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128784654</v>
+        <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>91282</v>
+        <v>86959</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7553,10 +7552,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725494</v>
+        <v>725739</v>
       </c>
       <c r="R64" t="n">
-        <v>6385035</v>
+        <v>6385174</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7597,6 +7596,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>86959</v>
+        <v>91282</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R68" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,7 +8027,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8046,32 +8045,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>91282</v>
+        <v>86959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8081,10 +8080,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R69" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,6 +8134,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9709,10 +9709,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791452</v>
+        <v>128791489</v>
       </c>
       <c r="B85" t="n">
-        <v>91282</v>
+        <v>86981</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9720,21 +9720,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725424</v>
+        <v>725612</v>
       </c>
       <c r="R85" t="n">
-        <v>6384953</v>
+        <v>6385206</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9816,10 +9816,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791489</v>
+        <v>128791452</v>
       </c>
       <c r="B86" t="n">
-        <v>86981</v>
+        <v>91282</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9827,21 +9827,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>2015</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725612</v>
+        <v>725424</v>
       </c>
       <c r="R86" t="n">
-        <v>6385206</v>
+        <v>6384953</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10621,41 +10621,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>92808</v>
+        <v>87016</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R94" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10685,29 +10685,45 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10822,41 +10838,41 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791498</v>
+        <v>128786089</v>
       </c>
       <c r="B96" t="n">
-        <v>87016</v>
+        <v>92808</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>433</v>
+        <v>6047725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725697</v>
+        <v>725556</v>
       </c>
       <c r="R96" t="n">
-        <v>6385241</v>
+        <v>6385239</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10886,45 +10902,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11654,34 +11654,30 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128791479</v>
+        <v>128791499</v>
       </c>
       <c r="B104" t="n">
-        <v>86959</v>
+        <v>87016</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11689,10 +11685,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725712</v>
+        <v>725431</v>
       </c>
       <c r="R104" t="n">
-        <v>6385103</v>
+        <v>6385191</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11720,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11730,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11743,7 +11739,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11762,10 +11757,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B105" t="n">
-        <v>90942</v>
+        <v>92790</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,34 +11768,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R105" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11841,64 +11836,63 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128784666</v>
+        <v>128786100</v>
       </c>
       <c r="B106" t="n">
-        <v>107546</v>
+        <v>90942</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220079</v>
+        <v>4190</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725501</v>
+        <v>725528</v>
       </c>
       <c r="R106" t="n">
-        <v>6385056</v>
+        <v>6385185</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11939,28 +11933,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128791499</v>
+        <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>87016</v>
+        <v>91039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11968,30 +11963,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725431</v>
+        <v>725542</v>
       </c>
       <c r="R107" t="n">
-        <v>6385191</v>
+        <v>6385225</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12021,19 +12020,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12048,57 +12037,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128786099</v>
+        <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>91039</v>
+        <v>107546</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5747</v>
+        <v>220079</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725542</v>
+        <v>725501</v>
       </c>
       <c r="R108" t="n">
-        <v>6385225</v>
+        <v>6385056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12145,57 +12134,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128784652</v>
+        <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>92790</v>
+        <v>86959</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4363</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725629</v>
+        <v>725712</v>
       </c>
       <c r="R109" t="n">
-        <v>6385285</v>
+        <v>6385103</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12225,29 +12214,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12568,32 +12568,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791480</v>
+        <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725785</v>
+        <v>725541</v>
       </c>
       <c r="R113" t="n">
-        <v>6385095</v>
+        <v>6385088</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,7 +12657,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12676,45 +12675,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128791467</v>
+        <v>128786106</v>
       </c>
       <c r="B114" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725756</v>
+        <v>725520</v>
       </c>
       <c r="R114" t="n">
-        <v>6385191</v>
+        <v>6385158</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,72 +12743,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128791462</v>
+        <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12807,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>725541</v>
+        <v>725785</v>
       </c>
       <c r="R115" t="n">
-        <v>6385088</v>
+        <v>6385095</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12854,7 +12842,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12864,7 +12852,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12873,6 +12861,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12891,45 +12880,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128786106</v>
+        <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>725520</v>
+        <v>725756</v>
       </c>
       <c r="R116" t="n">
-        <v>6385158</v>
+        <v>6385191</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12959,39 +12948,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128791508</v>
+        <v>128784668</v>
       </c>
       <c r="B117" t="n">
-        <v>87016</v>
+        <v>86875</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12999,30 +12999,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725757</v>
+        <v>725725</v>
       </c>
       <c r="R117" t="n">
-        <v>6385187</v>
+        <v>6385117</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,19 +13056,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13079,57 +13073,53 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784676</v>
+        <v>128791508</v>
       </c>
       <c r="B118" t="n">
-        <v>86922</v>
+        <v>87016</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725647</v>
+        <v>725757</v>
       </c>
       <c r="R118" t="n">
-        <v>6385255</v>
+        <v>6385187</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,9 +13149,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13176,44 +13176,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128784668</v>
+        <v>128784676</v>
       </c>
       <c r="B119" t="n">
-        <v>86875</v>
+        <v>86922</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13223,10 +13223,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725725</v>
+        <v>725647</v>
       </c>
       <c r="R119" t="n">
-        <v>6385117</v>
+        <v>6385255</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13586,45 +13586,41 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128791483</v>
+        <v>128786090</v>
       </c>
       <c r="B123" t="n">
-        <v>86959</v>
+        <v>92808</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725645</v>
+        <v>725545</v>
       </c>
       <c r="R123" t="n">
-        <v>6385261</v>
+        <v>6385234</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13654,81 +13650,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786090</v>
+        <v>128791483</v>
       </c>
       <c r="B124" t="n">
-        <v>92808</v>
+        <v>86959</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725545</v>
+        <v>725645</v>
       </c>
       <c r="R124" t="n">
-        <v>6385234</v>
+        <v>6385261</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13758,56 +13747,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791495</v>
+        <v>128791448</v>
       </c>
       <c r="B125" t="n">
-        <v>90920</v>
+        <v>91282</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1000938</v>
+        <v>2015</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13817,10 +13822,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725745</v>
+        <v>725501</v>
       </c>
       <c r="R125" t="n">
-        <v>6385094</v>
+        <v>6385071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13852,7 +13857,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13862,7 +13867,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13889,45 +13894,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128786102</v>
+        <v>128791460</v>
       </c>
       <c r="B126" t="n">
-        <v>86875</v>
+        <v>86784</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725513</v>
+        <v>725718</v>
       </c>
       <c r="R126" t="n">
-        <v>6385159</v>
+        <v>6385251</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13957,9 +13962,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13974,19 +13989,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128784670</v>
+        <v>128791512</v>
       </c>
       <c r="B127" t="n">
         <v>87016</v>
@@ -14013,14 +14028,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725570</v>
+        <v>725631</v>
       </c>
       <c r="R127" t="n">
-        <v>6385186</v>
+        <v>6385124</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14050,9 +14065,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,22 +14092,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791448</v>
+        <v>128784670</v>
       </c>
       <c r="B128" t="n">
-        <v>91282</v>
+        <v>87016</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14090,34 +14115,30 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725501</v>
+        <v>725570</v>
       </c>
       <c r="R128" t="n">
-        <v>6385071</v>
+        <v>6385186</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14147,19 +14168,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14174,42 +14185,41 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791512</v>
+        <v>128791495</v>
       </c>
       <c r="B129" t="n">
-        <v>87016</v>
+        <v>90920</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>433</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Duvspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Geastrum</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14217,10 +14227,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725631</v>
+        <v>725745</v>
       </c>
       <c r="R129" t="n">
-        <v>6385124</v>
+        <v>6385094</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14252,7 +14262,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14262,7 +14272,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14289,45 +14299,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791460</v>
+        <v>128786102</v>
       </c>
       <c r="B130" t="n">
-        <v>86784</v>
+        <v>86875</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725718</v>
+        <v>725513</v>
       </c>
       <c r="R130" t="n">
-        <v>6385251</v>
+        <v>6385159</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14357,19 +14367,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7014,7 +7014,7 @@
         <v>128791517</v>
       </c>
       <c r="B59" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>128791453</v>
       </c>
       <c r="B60" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>128786091</v>
       </c>
       <c r="B61" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>128784654</v>
       </c>
       <c r="B62" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>128786101</v>
       </c>
       <c r="B63" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128791503</v>
+        <v>128786092</v>
       </c>
       <c r="B70" t="n">
-        <v>87016</v>
+        <v>91286</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,30 +8164,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>725496</v>
+        <v>725499</v>
       </c>
       <c r="R70" t="n">
-        <v>6385236</v>
+        <v>6385065</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8217,19 +8221,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,22 +8238,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128786092</v>
+        <v>128784653</v>
       </c>
       <c r="B71" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8287,14 +8281,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>725499</v>
+        <v>725496</v>
       </c>
       <c r="R71" t="n">
-        <v>6385065</v>
+        <v>6385075</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8341,22 +8335,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128784653</v>
+        <v>128791503</v>
       </c>
       <c r="B72" t="n">
-        <v>91282</v>
+        <v>87020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,34 +8358,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385075</v>
+        <v>6385236</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8421,9 +8411,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128791488</v>
       </c>
       <c r="B77" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>128791481</v>
       </c>
       <c r="B79" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>128791489</v>
       </c>
       <c r="B85" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>128791452</v>
       </c>
       <c r="B86" t="n">
-        <v>91282</v>
+        <v>91286</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>128786098</v>
       </c>
       <c r="B87" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10123,45 +10123,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128784669</v>
+        <v>128791469</v>
       </c>
       <c r="B89" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725759</v>
+        <v>725461</v>
       </c>
       <c r="R89" t="n">
-        <v>6385120</v>
+        <v>6385028</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,61 +10191,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784675</v>
+        <v>128784662</v>
       </c>
       <c r="B90" t="n">
-        <v>86846</v>
+        <v>86963</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10255,10 +10266,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725536</v>
+        <v>725771</v>
       </c>
       <c r="R90" t="n">
-        <v>6385137</v>
+        <v>6385166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10299,6 +10310,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10317,10 +10329,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128791469</v>
+        <v>128784659</v>
       </c>
       <c r="B91" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10348,14 +10360,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725461</v>
+        <v>725626</v>
       </c>
       <c r="R91" t="n">
-        <v>6385028</v>
+        <v>6385141</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10385,19 +10397,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10413,44 +10415,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784662</v>
+        <v>128784669</v>
       </c>
       <c r="B92" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10460,10 +10462,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725771</v>
+        <v>725759</v>
       </c>
       <c r="R92" t="n">
-        <v>6385166</v>
+        <v>6385120</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10504,7 +10506,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10523,32 +10524,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784659</v>
+        <v>128784675</v>
       </c>
       <c r="B93" t="n">
-        <v>86959</v>
+        <v>86850</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10558,10 +10559,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725626</v>
+        <v>725536</v>
       </c>
       <c r="R93" t="n">
-        <v>6385141</v>
+        <v>6385137</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10602,7 +10603,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10730,45 +10730,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128791477</v>
+        <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>86959</v>
+        <v>92812</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725588</v>
+        <v>725556</v>
       </c>
       <c r="R95" t="n">
-        <v>6385289</v>
+        <v>6385239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10798,81 +10794,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128786089</v>
+        <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>92808</v>
+        <v>86963</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725556</v>
+        <v>725588</v>
       </c>
       <c r="R96" t="n">
-        <v>6385239</v>
+        <v>6385289</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10902,29 +10891,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
         <v>128791514</v>
       </c>
       <c r="B97" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>128791504</v>
       </c>
       <c r="B98" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>128791516</v>
       </c>
       <c r="B99" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>128784657</v>
       </c>
       <c r="B100" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128784661</v>
+        <v>128791473</v>
       </c>
       <c r="B102" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11479,14 +11479,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725740</v>
+        <v>725405</v>
       </c>
       <c r="R102" t="n">
-        <v>6385127</v>
+        <v>6385117</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11516,9 +11516,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11534,22 +11544,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128791473</v>
+        <v>128784661</v>
       </c>
       <c r="B103" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11577,14 +11587,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>725405</v>
+        <v>725740</v>
       </c>
       <c r="R103" t="n">
-        <v>6385117</v>
+        <v>6385127</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11614,19 +11624,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11642,12 +11642,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
         <v>128791499</v>
       </c>
       <c r="B104" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784652</v>
+        <v>128786100</v>
       </c>
       <c r="B105" t="n">
-        <v>92790</v>
+        <v>90946</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11768,34 +11768,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4363</v>
+        <v>4190</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725629</v>
+        <v>725528</v>
       </c>
       <c r="R105" t="n">
-        <v>6385285</v>
+        <v>6385185</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,28 +11836,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B106" t="n">
-        <v>90942</v>
+        <v>92794</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11865,34 +11866,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R106" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11933,19 +11934,18 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
         <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>128791487</v>
       </c>
       <c r="B112" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>128786106</v>
       </c>
       <c r="B114" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12988,10 +12988,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128784668</v>
+        <v>128791508</v>
       </c>
       <c r="B117" t="n">
-        <v>86875</v>
+        <v>87020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12999,34 +12999,30 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725725</v>
+        <v>725757</v>
       </c>
       <c r="R117" t="n">
-        <v>6385117</v>
+        <v>6385187</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13056,9 +13052,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13073,22 +13079,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128791508</v>
+        <v>128784668</v>
       </c>
       <c r="B118" t="n">
-        <v>87016</v>
+        <v>86879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13096,30 +13102,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725757</v>
+        <v>725725</v>
       </c>
       <c r="R118" t="n">
-        <v>6385187</v>
+        <v>6385117</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13149,19 +13159,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13176,12 +13176,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13191,7 +13191,7 @@
         <v>128784676</v>
       </c>
       <c r="B119" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>128784658</v>
       </c>
       <c r="B120" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>128786105</v>
       </c>
       <c r="B121" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>128791485</v>
       </c>
       <c r="B122" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13586,41 +13586,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128786090</v>
+        <v>128791483</v>
       </c>
       <c r="B123" t="n">
-        <v>92808</v>
+        <v>86963</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725545</v>
+        <v>725645</v>
       </c>
       <c r="R123" t="n">
-        <v>6385234</v>
+        <v>6385261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13650,74 +13654,81 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128791483</v>
+        <v>128786090</v>
       </c>
       <c r="B124" t="n">
-        <v>86959</v>
+        <v>92812</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725645</v>
+        <v>725545</v>
       </c>
       <c r="R124" t="n">
-        <v>6385261</v>
+        <v>6385234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13747,50 +13758,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791448</v>
+        <v>128791512</v>
       </c>
       <c r="B125" t="n">
-        <v>91282</v>
+        <v>87020</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,23 +13798,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13822,10 +13818,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725501</v>
+        <v>725631</v>
       </c>
       <c r="R125" t="n">
-        <v>6385071</v>
+        <v>6385124</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13867,7 +13863,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13894,45 +13890,41 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128791460</v>
+        <v>128784670</v>
       </c>
       <c r="B126" t="n">
-        <v>86784</v>
+        <v>87020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725718</v>
+        <v>725570</v>
       </c>
       <c r="R126" t="n">
-        <v>6385251</v>
+        <v>6385186</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13962,19 +13954,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13989,22 +13971,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791512</v>
+        <v>128791448</v>
       </c>
       <c r="B127" t="n">
-        <v>87016</v>
+        <v>91286</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14012,19 +13994,23 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14032,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725631</v>
+        <v>725501</v>
       </c>
       <c r="R127" t="n">
-        <v>6385124</v>
+        <v>6385071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14067,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14077,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14104,41 +14090,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128784670</v>
+        <v>128791460</v>
       </c>
       <c r="B128" t="n">
-        <v>87016</v>
+        <v>86788</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>433</v>
+        <v>3712</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725570</v>
+        <v>725718</v>
       </c>
       <c r="R128" t="n">
-        <v>6385186</v>
+        <v>6385251</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14168,9 +14158,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14185,52 +14185,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791495</v>
+        <v>128786102</v>
       </c>
       <c r="B129" t="n">
-        <v>90920</v>
+        <v>86879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1000938</v>
+        <v>248956</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725745</v>
+        <v>725513</v>
       </c>
       <c r="R129" t="n">
-        <v>6385094</v>
+        <v>6385159</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14260,19 +14265,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14287,57 +14282,52 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128786102</v>
+        <v>128791495</v>
       </c>
       <c r="B130" t="n">
-        <v>86875</v>
+        <v>90924</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248956</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Gulsträngad fagerspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725513</v>
+        <v>725745</v>
       </c>
       <c r="R130" t="n">
-        <v>6385159</v>
+        <v>6385094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,9 +14357,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -14399,7 +14399,7 @@
         <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>87153</v>
+        <v>87157</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>86925</v>
+        <v>86929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>128786095</v>
       </c>
       <c r="B134" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>128791510</v>
       </c>
       <c r="B135" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>86925</v>
+        <v>86929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791517</v>
+        <v>128791453</v>
       </c>
       <c r="B59" t="n">
-        <v>86810</v>
+        <v>91286</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,21 +7022,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725712</v>
+        <v>725494</v>
       </c>
       <c r="R59" t="n">
-        <v>6385261</v>
+        <v>6385080</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7100,6 +7100,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7118,7 +7119,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128791453</v>
+        <v>128786091</v>
       </c>
       <c r="B60" t="n">
         <v>91286</v>
@@ -7149,14 +7150,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R60" t="n">
-        <v>6385080</v>
+        <v>6385159</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7186,47 +7187,36 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128786091</v>
+        <v>128784654</v>
       </c>
       <c r="B61" t="n">
         <v>91286</v>
@@ -7257,14 +7247,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R61" t="n">
-        <v>6385159</v>
+        <v>6385035</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7311,22 +7301,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784654</v>
+        <v>128791517</v>
       </c>
       <c r="B62" t="n">
-        <v>91286</v>
+        <v>86810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7334,34 +7324,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725494</v>
+        <v>725712</v>
       </c>
       <c r="R62" t="n">
-        <v>6385035</v>
+        <v>6385261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7391,9 +7381,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7408,12 +7408,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -9180,32 +9180,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791458</v>
+        <v>128791466</v>
       </c>
       <c r="B80" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>725410</v>
+        <v>725740</v>
       </c>
       <c r="R80" t="n">
-        <v>6385108</v>
+        <v>6385101</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9269,6 +9269,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9287,7 +9288,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791466</v>
+        <v>128791474</v>
       </c>
       <c r="B81" t="n">
         <v>86963</v>
@@ -9322,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>725740</v>
+        <v>725471</v>
       </c>
       <c r="R81" t="n">
-        <v>6385101</v>
+        <v>6385206</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9357,7 +9358,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9367,7 +9368,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9395,7 +9396,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791474</v>
+        <v>128791482</v>
       </c>
       <c r="B82" t="n">
         <v>86963</v>
@@ -9430,10 +9431,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>725471</v>
+        <v>725720</v>
       </c>
       <c r="R82" t="n">
-        <v>6385206</v>
+        <v>6385276</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9465,7 +9466,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9475,7 +9476,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9503,7 +9504,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791482</v>
+        <v>128786097</v>
       </c>
       <c r="B83" t="n">
         <v>86963</v>
@@ -9534,14 +9535,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>725720</v>
+        <v>725551</v>
       </c>
       <c r="R83" t="n">
-        <v>6385276</v>
+        <v>6385217</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9571,19 +9572,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9599,57 +9590,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128786097</v>
+        <v>128791458</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>725551</v>
+        <v>725410</v>
       </c>
       <c r="R84" t="n">
-        <v>6385217</v>
+        <v>6385108</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9679,75 +9670,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791489</v>
+        <v>128786098</v>
       </c>
       <c r="B85" t="n">
-        <v>86985</v>
+        <v>98658</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725612</v>
+        <v>725577</v>
       </c>
       <c r="R85" t="n">
-        <v>6385206</v>
+        <v>6385250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,19 +9777,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9804,12 +9794,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9923,45 +9913,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128786098</v>
+        <v>128791489</v>
       </c>
       <c r="B87" t="n">
-        <v>98658</v>
+        <v>86985</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725577</v>
+        <v>725612</v>
       </c>
       <c r="R87" t="n">
-        <v>6385250</v>
+        <v>6385206</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9991,9 +9981,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791469</v>
+        <v>128784659</v>
       </c>
       <c r="B89" t="n">
         <v>86963</v>
@@ -10154,14 +10154,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725461</v>
+        <v>725626</v>
       </c>
       <c r="R89" t="n">
-        <v>6385028</v>
+        <v>6385141</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,19 +10191,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,44 +10209,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784662</v>
+        <v>128784675</v>
       </c>
       <c r="B90" t="n">
-        <v>86963</v>
+        <v>86850</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10266,10 +10256,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725771</v>
+        <v>725536</v>
       </c>
       <c r="R90" t="n">
-        <v>6385166</v>
+        <v>6385137</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10310,7 +10300,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10329,32 +10318,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784659</v>
+        <v>128784669</v>
       </c>
       <c r="B91" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10364,10 +10353,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725626</v>
+        <v>725759</v>
       </c>
       <c r="R91" t="n">
-        <v>6385141</v>
+        <v>6385120</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10408,7 +10397,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10427,45 +10415,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784669</v>
+        <v>128791469</v>
       </c>
       <c r="B92" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725759</v>
+        <v>725461</v>
       </c>
       <c r="R92" t="n">
-        <v>6385120</v>
+        <v>6385028</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10495,61 +10483,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784675</v>
+        <v>128784662</v>
       </c>
       <c r="B93" t="n">
-        <v>86850</v>
+        <v>86963</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10559,10 +10558,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725536</v>
+        <v>725771</v>
       </c>
       <c r="R93" t="n">
-        <v>6385137</v>
+        <v>6385166</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10603,6 +10602,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10621,30 +10621,34 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128791498</v>
+        <v>128791477</v>
       </c>
       <c r="B94" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10652,10 +10656,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725697</v>
+        <v>725588</v>
       </c>
       <c r="R94" t="n">
-        <v>6385241</v>
+        <v>6385289</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10687,7 +10691,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10697,12 +10701,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10730,41 +10729,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B95" t="n">
-        <v>92812</v>
+        <v>87020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R95" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10794,74 +10793,86 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791477</v>
+        <v>128786089</v>
       </c>
       <c r="B96" t="n">
-        <v>86963</v>
+        <v>92812</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725588</v>
+        <v>725556</v>
       </c>
       <c r="R96" t="n">
-        <v>6385289</v>
+        <v>6385239</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,50 +10902,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B97" t="n">
-        <v>86850</v>
+        <v>87020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,23 +10942,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10966,10 +10962,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R97" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11001,7 +10997,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11011,7 +11007,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11038,10 +11034,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B98" t="n">
-        <v>87020</v>
+        <v>86850</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11049,19 +11045,23 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R98" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11141,7 +11141,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B99" t="n">
         <v>86810</v>
@@ -11172,14 +11172,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R99" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,19 +11209,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11236,19 +11226,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B100" t="n">
         <v>86810</v>
@@ -11279,14 +11269,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R100" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11316,9 +11306,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,12 +11333,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128791473</v>
+        <v>128784661</v>
       </c>
       <c r="B102" t="n">
         <v>86963</v>
@@ -11479,14 +11479,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725405</v>
+        <v>725740</v>
       </c>
       <c r="R102" t="n">
-        <v>6385117</v>
+        <v>6385127</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11516,19 +11516,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11544,19 +11534,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128784661</v>
+        <v>128791473</v>
       </c>
       <c r="B103" t="n">
         <v>86963</v>
@@ -11587,14 +11577,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>725740</v>
+        <v>725405</v>
       </c>
       <c r="R103" t="n">
-        <v>6385127</v>
+        <v>6385117</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11624,9 +11614,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11642,53 +11642,57 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128791499</v>
+        <v>128786100</v>
       </c>
       <c r="B104" t="n">
-        <v>87020</v>
+        <v>90946</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>4190</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Geastrum striatum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725431</v>
+        <v>725528</v>
       </c>
       <c r="R104" t="n">
-        <v>6385191</v>
+        <v>6385185</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11718,49 +11722,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B105" t="n">
-        <v>90946</v>
+        <v>92794</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11768,34 +11763,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R105" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,64 +11831,63 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128784652</v>
+        <v>128791479</v>
       </c>
       <c r="B106" t="n">
-        <v>92794</v>
+        <v>86963</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4363</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725629</v>
+        <v>725712</v>
       </c>
       <c r="R106" t="n">
-        <v>6385285</v>
+        <v>6385103</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11923,39 +11917,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128786099</v>
+        <v>128791499</v>
       </c>
       <c r="B107" t="n">
-        <v>91043</v>
+        <v>87020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11963,34 +11968,30 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5747</v>
+        <v>433</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725542</v>
+        <v>725431</v>
       </c>
       <c r="R107" t="n">
-        <v>6385225</v>
+        <v>6385191</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12020,9 +12021,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,57 +12048,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128784666</v>
+        <v>128786099</v>
       </c>
       <c r="B108" t="n">
-        <v>107550</v>
+        <v>91043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220079</v>
+        <v>5747</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725501</v>
+        <v>725542</v>
       </c>
       <c r="R108" t="n">
-        <v>6385056</v>
+        <v>6385225</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12134,22 +12145,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128791479</v>
+        <v>128784666</v>
       </c>
       <c r="B109" t="n">
-        <v>86963</v>
+        <v>107550</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12157,34 +12168,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725712</v>
+        <v>725501</v>
       </c>
       <c r="R109" t="n">
-        <v>6385103</v>
+        <v>6385056</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,40 +12225,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12568,32 +12568,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791462</v>
+        <v>128791480</v>
       </c>
       <c r="B113" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725541</v>
+        <v>725785</v>
       </c>
       <c r="R113" t="n">
-        <v>6385088</v>
+        <v>6385095</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,6 +12657,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12675,45 +12676,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128786106</v>
+        <v>128791467</v>
       </c>
       <c r="B114" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725520</v>
+        <v>725756</v>
       </c>
       <c r="R114" t="n">
-        <v>6385158</v>
+        <v>6385191</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12743,61 +12744,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128791480</v>
+        <v>128791462</v>
       </c>
       <c r="B115" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12807,10 +12819,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>725785</v>
+        <v>725541</v>
       </c>
       <c r="R115" t="n">
-        <v>6385095</v>
+        <v>6385088</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12842,7 +12854,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12852,7 +12864,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,7 +12873,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12880,45 +12891,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128791467</v>
+        <v>128786106</v>
       </c>
       <c r="B116" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>725756</v>
+        <v>725520</v>
       </c>
       <c r="R116" t="n">
-        <v>6385191</v>
+        <v>6385158</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12948,40 +12959,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13091,32 +13091,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784668</v>
+        <v>128784676</v>
       </c>
       <c r="B118" t="n">
-        <v>86879</v>
+        <v>86926</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725725</v>
+        <v>725647</v>
       </c>
       <c r="R118" t="n">
-        <v>6385117</v>
+        <v>6385255</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13188,32 +13188,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128784676</v>
+        <v>128784668</v>
       </c>
       <c r="B119" t="n">
-        <v>86926</v>
+        <v>86879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13223,10 +13223,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725647</v>
+        <v>725725</v>
       </c>
       <c r="R119" t="n">
-        <v>6385255</v>
+        <v>6385117</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13285,45 +13285,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128784658</v>
+        <v>128786105</v>
       </c>
       <c r="B120" t="n">
-        <v>86810</v>
+        <v>96232</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>2180</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725646</v>
+        <v>725537</v>
       </c>
       <c r="R120" t="n">
-        <v>6385281</v>
+        <v>6385216</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13370,22 +13370,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128786105</v>
+        <v>128791485</v>
       </c>
       <c r="B121" t="n">
-        <v>96232</v>
+        <v>98658</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13393,34 +13393,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2180</v>
+        <v>219862</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725537</v>
+        <v>725724</v>
       </c>
       <c r="R121" t="n">
-        <v>6385216</v>
+        <v>6385174</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13450,9 +13450,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13467,44 +13477,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128791485</v>
+        <v>128791483</v>
       </c>
       <c r="B122" t="n">
-        <v>98658</v>
+        <v>86963</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13514,10 +13524,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725724</v>
+        <v>725645</v>
       </c>
       <c r="R122" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13549,7 +13559,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13559,7 +13569,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13568,6 +13578,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13586,45 +13597,41 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128791483</v>
+        <v>128786090</v>
       </c>
       <c r="B123" t="n">
-        <v>86963</v>
+        <v>92812</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725645</v>
+        <v>725545</v>
       </c>
       <c r="R123" t="n">
-        <v>6385261</v>
+        <v>6385234</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13654,81 +13661,74 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786090</v>
+        <v>128784658</v>
       </c>
       <c r="B124" t="n">
-        <v>92812</v>
+        <v>86810</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725545</v>
+        <v>725646</v>
       </c>
       <c r="R124" t="n">
-        <v>6385234</v>
+        <v>6385281</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13775,22 +13775,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791512</v>
+        <v>128791448</v>
       </c>
       <c r="B125" t="n">
-        <v>87020</v>
+        <v>91286</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,19 +13798,23 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13818,10 +13822,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725631</v>
+        <v>725501</v>
       </c>
       <c r="R125" t="n">
-        <v>6385124</v>
+        <v>6385071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13853,7 +13857,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13863,7 +13867,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13983,10 +13987,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791448</v>
+        <v>128791512</v>
       </c>
       <c r="B127" t="n">
-        <v>91286</v>
+        <v>87020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13994,23 +13998,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14018,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725501</v>
+        <v>725631</v>
       </c>
       <c r="R127" t="n">
-        <v>6385071</v>
+        <v>6385124</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14197,45 +14197,40 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128786102</v>
+        <v>128791495</v>
       </c>
       <c r="B129" t="n">
-        <v>86879</v>
+        <v>90924</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>248956</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Gulsträngad fagerspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725513</v>
+        <v>725745</v>
       </c>
       <c r="R129" t="n">
-        <v>6385159</v>
+        <v>6385094</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14265,9 +14260,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14282,52 +14287,57 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128791495</v>
+        <v>128786102</v>
       </c>
       <c r="B130" t="n">
-        <v>90924</v>
+        <v>86879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1000938</v>
+        <v>248956</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725745</v>
+        <v>725513</v>
       </c>
       <c r="R130" t="n">
-        <v>6385094</v>
+        <v>6385159</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14357,19 +14367,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7313,45 +7313,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128791517</v>
+        <v>128784663</v>
       </c>
       <c r="B62" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725712</v>
+        <v>725739</v>
       </c>
       <c r="R62" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7381,39 +7381,30 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7517,45 +7508,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128784663</v>
+        <v>128791517</v>
       </c>
       <c r="B64" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725739</v>
+        <v>725712</v>
       </c>
       <c r="R64" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7585,30 +7576,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8754,30 +8754,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791506</v>
+        <v>128791465</v>
       </c>
       <c r="B76" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8785,10 +8789,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>725546</v>
+        <v>725458</v>
       </c>
       <c r="R76" t="n">
-        <v>6385296</v>
+        <v>6385186</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8820,7 +8824,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8830,7 +8834,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8839,6 +8843,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8857,32 +8862,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791488</v>
+        <v>128791481</v>
       </c>
       <c r="B77" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>725580</v>
+        <v>725669</v>
       </c>
       <c r="R77" t="n">
-        <v>6385121</v>
+        <v>6385183</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8927,7 +8932,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8937,7 +8942,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8946,6 +8951,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8964,34 +8970,30 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791465</v>
+        <v>128791506</v>
       </c>
       <c r="B78" t="n">
-        <v>86963</v>
+        <v>87020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8999,10 +9001,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>725458</v>
+        <v>725546</v>
       </c>
       <c r="R78" t="n">
-        <v>6385186</v>
+        <v>6385296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9034,7 +9036,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9044,7 +9046,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9053,7 +9055,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9072,32 +9073,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128791481</v>
+        <v>128791488</v>
       </c>
       <c r="B79" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9108,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>725669</v>
+        <v>725580</v>
       </c>
       <c r="R79" t="n">
-        <v>6385183</v>
+        <v>6385121</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9142,7 +9143,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9152,7 +9153,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,7 +9162,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9180,32 +9180,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791466</v>
+        <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>725740</v>
+        <v>725410</v>
       </c>
       <c r="R80" t="n">
-        <v>6385101</v>
+        <v>6385108</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9269,7 +9269,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9288,7 +9287,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791474</v>
+        <v>128791466</v>
       </c>
       <c r="B81" t="n">
         <v>86963</v>
@@ -9323,10 +9322,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>725471</v>
+        <v>725740</v>
       </c>
       <c r="R81" t="n">
-        <v>6385206</v>
+        <v>6385101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9358,7 +9357,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9368,7 +9367,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9396,7 +9395,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791482</v>
+        <v>128791474</v>
       </c>
       <c r="B82" t="n">
         <v>86963</v>
@@ -9431,10 +9430,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>725720</v>
+        <v>725471</v>
       </c>
       <c r="R82" t="n">
-        <v>6385276</v>
+        <v>6385206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9466,7 +9465,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9476,7 +9475,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9504,7 +9503,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128786097</v>
+        <v>128791482</v>
       </c>
       <c r="B83" t="n">
         <v>86963</v>
@@ -9535,14 +9534,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>725551</v>
+        <v>725720</v>
       </c>
       <c r="R83" t="n">
-        <v>6385217</v>
+        <v>6385276</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9572,9 +9571,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9590,57 +9599,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791458</v>
+        <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>725410</v>
+        <v>725551</v>
       </c>
       <c r="R84" t="n">
-        <v>6385108</v>
+        <v>6385217</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9670,84 +9679,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128786098</v>
+        <v>128791452</v>
       </c>
       <c r="B85" t="n">
-        <v>98658</v>
+        <v>91286</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219862</v>
+        <v>2015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725577</v>
+        <v>725424</v>
       </c>
       <c r="R85" t="n">
-        <v>6385250</v>
+        <v>6384953</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,9 +9777,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9794,22 +9804,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791452</v>
+        <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>91286</v>
+        <v>86985</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9817,21 +9827,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9841,10 +9851,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725424</v>
+        <v>725612</v>
       </c>
       <c r="R86" t="n">
-        <v>6384953</v>
+        <v>6385206</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9876,7 +9886,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9886,7 +9896,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9913,45 +9923,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791489</v>
+        <v>128786098</v>
       </c>
       <c r="B87" t="n">
-        <v>86985</v>
+        <v>98658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725612</v>
+        <v>725577</v>
       </c>
       <c r="R87" t="n">
-        <v>6385206</v>
+        <v>6385250</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9981,19 +9991,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128784659</v>
+        <v>128791469</v>
       </c>
       <c r="B89" t="n">
         <v>86963</v>
@@ -10154,14 +10154,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725626</v>
+        <v>725461</v>
       </c>
       <c r="R89" t="n">
-        <v>6385141</v>
+        <v>6385028</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,9 +10191,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10209,44 +10219,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784675</v>
+        <v>128784662</v>
       </c>
       <c r="B90" t="n">
-        <v>86850</v>
+        <v>86963</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10256,10 +10266,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725536</v>
+        <v>725771</v>
       </c>
       <c r="R90" t="n">
-        <v>6385137</v>
+        <v>6385166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10300,6 +10310,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10318,32 +10329,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784669</v>
+        <v>128784659</v>
       </c>
       <c r="B91" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10353,10 +10364,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725759</v>
+        <v>725626</v>
       </c>
       <c r="R91" t="n">
-        <v>6385120</v>
+        <v>6385141</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10397,6 +10408,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10415,45 +10427,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128791469</v>
+        <v>128784669</v>
       </c>
       <c r="B92" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725461</v>
+        <v>725759</v>
       </c>
       <c r="R92" t="n">
-        <v>6385028</v>
+        <v>6385120</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10483,72 +10495,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784662</v>
+        <v>128784675</v>
       </c>
       <c r="B93" t="n">
-        <v>86963</v>
+        <v>86850</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10558,10 +10559,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725771</v>
+        <v>725536</v>
       </c>
       <c r="R93" t="n">
-        <v>6385166</v>
+        <v>6385137</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10602,7 +10603,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10621,45 +10621,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128791477</v>
+        <v>128786089</v>
       </c>
       <c r="B94" t="n">
-        <v>86963</v>
+        <v>92812</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725588</v>
+        <v>725556</v>
       </c>
       <c r="R94" t="n">
-        <v>6385289</v>
+        <v>6385239</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10689,70 +10685,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128791498</v>
+        <v>128791477</v>
       </c>
       <c r="B95" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10760,10 +10749,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725697</v>
+        <v>725588</v>
       </c>
       <c r="R95" t="n">
-        <v>6385241</v>
+        <v>6385289</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10795,7 +10784,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10805,12 +10794,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10838,41 +10822,41 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B96" t="n">
-        <v>92812</v>
+        <v>87020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R96" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10902,39 +10886,55 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B97" t="n">
-        <v>87020</v>
+        <v>86850</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,19 +10942,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10962,10 +10966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R97" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11007,7 +11011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11034,10 +11038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B98" t="n">
-        <v>86850</v>
+        <v>87020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11045,23 +11049,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R98" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11141,7 +11141,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B99" t="n">
         <v>86810</v>
@@ -11172,14 +11172,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R99" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,9 +11209,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,19 +11236,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B100" t="n">
         <v>86810</v>
@@ -11269,14 +11279,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R100" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11306,19 +11316,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,12 +11333,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11849,34 +11849,30 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128791479</v>
+        <v>128791499</v>
       </c>
       <c r="B106" t="n">
-        <v>86963</v>
+        <v>87020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11884,10 +11880,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725712</v>
+        <v>725431</v>
       </c>
       <c r="R106" t="n">
-        <v>6385103</v>
+        <v>6385191</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11919,7 +11915,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11929,7 +11925,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11938,7 +11934,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11957,30 +11952,34 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128791499</v>
+        <v>128791479</v>
       </c>
       <c r="B107" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11988,10 +11987,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725431</v>
+        <v>725712</v>
       </c>
       <c r="R107" t="n">
-        <v>6385191</v>
+        <v>6385103</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12023,7 +12022,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12033,7 +12032,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,6 +12041,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12060,45 +12060,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128786099</v>
+        <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>91043</v>
+        <v>107550</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5747</v>
+        <v>220079</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725542</v>
+        <v>725501</v>
       </c>
       <c r="R108" t="n">
-        <v>6385225</v>
+        <v>6385056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12145,57 +12145,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128784666</v>
+        <v>128786099</v>
       </c>
       <c r="B109" t="n">
-        <v>107550</v>
+        <v>91043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220079</v>
+        <v>5747</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725501</v>
+        <v>725542</v>
       </c>
       <c r="R109" t="n">
-        <v>6385056</v>
+        <v>6385225</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12242,12 +12242,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12568,32 +12568,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791480</v>
+        <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725785</v>
+        <v>725541</v>
       </c>
       <c r="R113" t="n">
-        <v>6385095</v>
+        <v>6385088</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,7 +12657,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12676,45 +12675,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128791467</v>
+        <v>128786106</v>
       </c>
       <c r="B114" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725756</v>
+        <v>725520</v>
       </c>
       <c r="R114" t="n">
-        <v>6385191</v>
+        <v>6385158</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,72 +12743,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128791462</v>
+        <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12807,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>725541</v>
+        <v>725785</v>
       </c>
       <c r="R115" t="n">
-        <v>6385088</v>
+        <v>6385095</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12854,7 +12842,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12864,7 +12852,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12873,6 +12861,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12891,45 +12880,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128786106</v>
+        <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>725520</v>
+        <v>725756</v>
       </c>
       <c r="R116" t="n">
-        <v>6385158</v>
+        <v>6385191</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12959,70 +12948,85 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128791508</v>
+        <v>128784676</v>
       </c>
       <c r="B117" t="n">
-        <v>87020</v>
+        <v>86926</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725757</v>
+        <v>725647</v>
       </c>
       <c r="R117" t="n">
-        <v>6385187</v>
+        <v>6385255</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,19 +13056,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13079,44 +13073,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784676</v>
+        <v>128784668</v>
       </c>
       <c r="B118" t="n">
-        <v>86926</v>
+        <v>86879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13126,10 +13120,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725647</v>
+        <v>725725</v>
       </c>
       <c r="R118" t="n">
-        <v>6385255</v>
+        <v>6385117</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13188,10 +13182,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128784668</v>
+        <v>128791508</v>
       </c>
       <c r="B119" t="n">
-        <v>86879</v>
+        <v>87020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13199,34 +13193,30 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725725</v>
+        <v>725757</v>
       </c>
       <c r="R119" t="n">
-        <v>6385117</v>
+        <v>6385187</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13256,9 +13246,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13273,57 +13273,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128786105</v>
+        <v>128784658</v>
       </c>
       <c r="B120" t="n">
-        <v>96232</v>
+        <v>86810</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725537</v>
+        <v>725646</v>
       </c>
       <c r="R120" t="n">
-        <v>6385216</v>
+        <v>6385281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13370,44 +13370,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128791485</v>
+        <v>128791483</v>
       </c>
       <c r="B121" t="n">
-        <v>98658</v>
+        <v>86963</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13417,10 +13417,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725724</v>
+        <v>725645</v>
       </c>
       <c r="R121" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13471,6 +13471,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13489,45 +13490,41 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128791483</v>
+        <v>128786090</v>
       </c>
       <c r="B122" t="n">
-        <v>86963</v>
+        <v>92812</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725645</v>
+        <v>725545</v>
       </c>
       <c r="R122" t="n">
-        <v>6385261</v>
+        <v>6385234</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,50 +13554,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128786090</v>
+        <v>128791485</v>
       </c>
       <c r="B123" t="n">
-        <v>92812</v>
+        <v>98658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13608,30 +13594,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6047725</v>
+        <v>219862</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725545</v>
+        <v>725724</v>
       </c>
       <c r="R123" t="n">
-        <v>6385234</v>
+        <v>6385174</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13661,9 +13651,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13678,57 +13678,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128784658</v>
+        <v>128786105</v>
       </c>
       <c r="B124" t="n">
-        <v>86810</v>
+        <v>96232</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>424</v>
+        <v>2180</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725646</v>
+        <v>725537</v>
       </c>
       <c r="R124" t="n">
-        <v>6385281</v>
+        <v>6385216</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13775,12 +13775,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13894,41 +13894,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128784670</v>
+        <v>128791460</v>
       </c>
       <c r="B126" t="n">
-        <v>87020</v>
+        <v>86788</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>433</v>
+        <v>3712</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725570</v>
+        <v>725718</v>
       </c>
       <c r="R126" t="n">
-        <v>6385186</v>
+        <v>6385251</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13958,9 +13962,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13975,12 +13989,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14090,45 +14104,41 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791460</v>
+        <v>128784670</v>
       </c>
       <c r="B128" t="n">
-        <v>86788</v>
+        <v>87020</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725718</v>
+        <v>725570</v>
       </c>
       <c r="R128" t="n">
-        <v>6385251</v>
+        <v>6385186</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14158,19 +14168,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14185,12 +14185,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7014,7 +7014,7 @@
         <v>128791453</v>
       </c>
       <c r="B59" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>128786091</v>
       </c>
       <c r="B60" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>128784654</v>
       </c>
       <c r="B61" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7306,52 +7306,52 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784663</v>
+        <v>128791517</v>
       </c>
       <c r="B62" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725739</v>
+        <v>725712</v>
       </c>
       <c r="R62" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7381,75 +7381,84 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128786101</v>
+        <v>128784663</v>
       </c>
       <c r="B63" t="n">
-        <v>86879</v>
+        <v>86968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725528</v>
+        <v>725739</v>
       </c>
       <c r="R63" t="n">
-        <v>6385185</v>
+        <v>6385174</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7490,28 +7499,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791517</v>
+        <v>128786101</v>
       </c>
       <c r="B64" t="n">
-        <v>86810</v>
+        <v>86884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7519,34 +7529,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725712</v>
+        <v>725528</v>
       </c>
       <c r="R64" t="n">
-        <v>6385261</v>
+        <v>6385185</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7576,19 +7586,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,12 +7603,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
         <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128786092</v>
+        <v>128791503</v>
       </c>
       <c r="B70" t="n">
-        <v>91286</v>
+        <v>87025</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,34 +8164,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>725499</v>
+        <v>725496</v>
       </c>
       <c r="R70" t="n">
-        <v>6385065</v>
+        <v>6385236</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8221,9 +8217,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8238,22 +8244,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128784653</v>
+        <v>128786092</v>
       </c>
       <c r="B71" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8281,14 +8287,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>725496</v>
+        <v>725499</v>
       </c>
       <c r="R71" t="n">
-        <v>6385075</v>
+        <v>6385065</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8335,22 +8341,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791503</v>
+        <v>128784653</v>
       </c>
       <c r="B72" t="n">
-        <v>87020</v>
+        <v>91291</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,30 +8364,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385236</v>
+        <v>6385075</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8411,19 +8421,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8757,7 +8757,7 @@
         <v>128791465</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>128791481</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>128791506</v>
       </c>
       <c r="B78" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>128791488</v>
       </c>
       <c r="B79" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>128791452</v>
       </c>
       <c r="B85" t="n">
-        <v>91286</v>
+        <v>91291</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9816,45 +9816,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791489</v>
+        <v>128786098</v>
       </c>
       <c r="B86" t="n">
-        <v>86985</v>
+        <v>98665</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725612</v>
+        <v>725577</v>
       </c>
       <c r="R86" t="n">
-        <v>6385206</v>
+        <v>6385250</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9884,19 +9884,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9911,57 +9901,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128786098</v>
+        <v>128791489</v>
       </c>
       <c r="B87" t="n">
-        <v>98658</v>
+        <v>86990</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725577</v>
+        <v>725612</v>
       </c>
       <c r="R87" t="n">
-        <v>6385250</v>
+        <v>6385206</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9991,9 +9981,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10123,45 +10123,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791469</v>
+        <v>128784669</v>
       </c>
       <c r="B89" t="n">
-        <v>86963</v>
+        <v>86990</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725461</v>
+        <v>725759</v>
       </c>
       <c r="R89" t="n">
-        <v>6385028</v>
+        <v>6385120</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,72 +10191,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784662</v>
+        <v>128784675</v>
       </c>
       <c r="B90" t="n">
-        <v>86963</v>
+        <v>86855</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10266,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725771</v>
+        <v>725536</v>
       </c>
       <c r="R90" t="n">
-        <v>6385166</v>
+        <v>6385137</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10310,7 +10299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10322,17 +10310,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784659</v>
+        <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10360,14 +10348,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725626</v>
+        <v>725461</v>
       </c>
       <c r="R91" t="n">
-        <v>6385141</v>
+        <v>6385028</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10397,9 +10385,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10415,44 +10413,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784669</v>
+        <v>128784662</v>
       </c>
       <c r="B92" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10462,10 +10460,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725759</v>
+        <v>725771</v>
       </c>
       <c r="R92" t="n">
-        <v>6385120</v>
+        <v>6385166</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10506,6 +10504,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10517,39 +10516,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784675</v>
+        <v>128784659</v>
       </c>
       <c r="B93" t="n">
-        <v>86850</v>
+        <v>86968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10559,10 +10558,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725536</v>
+        <v>725626</v>
       </c>
       <c r="R93" t="n">
-        <v>6385137</v>
+        <v>6385141</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10603,6 +10602,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10614,48 +10614,48 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128786089</v>
+        <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>92812</v>
+        <v>87025</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6047725</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
+          <t>Cortinarius caesiocanescens s.lat.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>725556</v>
+        <v>725697</v>
       </c>
       <c r="R94" t="n">
-        <v>6385239</v>
+        <v>6385241</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10685,74 +10685,86 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Kollekt. KOH bulb rosa reaktion.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128791477</v>
+        <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>86963</v>
+        <v>92817</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>6047725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>725588</v>
+        <v>725556</v>
       </c>
       <c r="R95" t="n">
-        <v>6385289</v>
+        <v>6385239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10782,70 +10794,63 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128791498</v>
+        <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>87020</v>
+        <v>86968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10853,10 +10858,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>725697</v>
+        <v>725588</v>
       </c>
       <c r="R96" t="n">
-        <v>6385241</v>
+        <v>6385289</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10888,7 +10893,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10898,12 +10903,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Kollekt. KOH bulb rosa reaktion.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10934,7 +10934,7 @@
         <v>128791514</v>
       </c>
       <c r="B97" t="n">
-        <v>86850</v>
+        <v>86855</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>128791504</v>
       </c>
       <c r="B98" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11141,45 +11141,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128791516</v>
+        <v>128784661</v>
       </c>
       <c r="B99" t="n">
-        <v>86810</v>
+        <v>86968</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725744</v>
+        <v>725740</v>
       </c>
       <c r="R99" t="n">
-        <v>6385244</v>
+        <v>6385127</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,84 +11209,75 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128784657</v>
+        <v>128791473</v>
       </c>
       <c r="B100" t="n">
-        <v>86810</v>
+        <v>86968</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725724</v>
+        <v>725405</v>
       </c>
       <c r="R100" t="n">
-        <v>6385171</v>
+        <v>6385117</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11316,39 +11307,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128791505</v>
+        <v>128791516</v>
       </c>
       <c r="B101" t="n">
-        <v>87020</v>
+        <v>86815</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11356,19 +11358,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11376,10 +11382,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>725506</v>
+        <v>725744</v>
       </c>
       <c r="R101" t="n">
-        <v>6385254</v>
+        <v>6385244</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11411,7 +11417,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11421,7 +11427,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,32 +11454,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128784661</v>
+        <v>128784657</v>
       </c>
       <c r="B102" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11483,10 +11489,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725740</v>
+        <v>725724</v>
       </c>
       <c r="R102" t="n">
-        <v>6385127</v>
+        <v>6385171</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11527,7 +11533,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11539,41 +11544,37 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128791473</v>
+        <v>128791505</v>
       </c>
       <c r="B103" t="n">
-        <v>86963</v>
+        <v>87025</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11581,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>725405</v>
+        <v>725506</v>
       </c>
       <c r="R103" t="n">
-        <v>6385117</v>
+        <v>6385254</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11616,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11626,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11635,7 +11636,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11657,7 +11657,7 @@
         <v>128786100</v>
       </c>
       <c r="B104" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11752,45 +11752,41 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784652</v>
+        <v>128791499</v>
       </c>
       <c r="B105" t="n">
-        <v>92794</v>
+        <v>87025</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4363</v>
+        <v>433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725629</v>
+        <v>725431</v>
       </c>
       <c r="R105" t="n">
-        <v>6385285</v>
+        <v>6385191</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11820,9 +11816,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11837,53 +11843,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128791499</v>
+        <v>128784652</v>
       </c>
       <c r="B106" t="n">
-        <v>87020</v>
+        <v>92799</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>433</v>
+        <v>4363</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725431</v>
+        <v>725629</v>
       </c>
       <c r="R106" t="n">
-        <v>6385191</v>
+        <v>6385285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11913,19 +11923,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,57 +11940,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128791479</v>
+        <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>86963</v>
+        <v>91048</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725712</v>
+        <v>725542</v>
       </c>
       <c r="R107" t="n">
-        <v>6385103</v>
+        <v>6385225</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12020,40 +12020,29 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12063,7 +12052,7 @@
         <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12150,52 +12139,52 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128786099</v>
+        <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>91043</v>
+        <v>86968</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725542</v>
+        <v>725712</v>
       </c>
       <c r="R109" t="n">
-        <v>6385225</v>
+        <v>6385103</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12225,29 +12214,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>128791487</v>
       </c>
       <c r="B112" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>128791462</v>
       </c>
       <c r="B113" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>128786106</v>
       </c>
       <c r="B114" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>128791480</v>
       </c>
       <c r="B115" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>128791467</v>
       </c>
       <c r="B116" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>128784676</v>
       </c>
       <c r="B117" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13088,7 +13088,7 @@
         <v>128784668</v>
       </c>
       <c r="B118" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13185,7 +13185,7 @@
         <v>128791508</v>
       </c>
       <c r="B119" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>128784658</v>
       </c>
       <c r="B120" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13375,52 +13375,52 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128791483</v>
+        <v>128786105</v>
       </c>
       <c r="B121" t="n">
-        <v>86963</v>
+        <v>96239</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725645</v>
+        <v>725537</v>
       </c>
       <c r="R121" t="n">
-        <v>6385261</v>
+        <v>6385216</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13450,50 +13450,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128786090</v>
+        <v>128791485</v>
       </c>
       <c r="B122" t="n">
-        <v>92812</v>
+        <v>98665</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13501,30 +13490,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6047725</v>
+        <v>219862</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725545</v>
+        <v>725724</v>
       </c>
       <c r="R122" t="n">
-        <v>6385234</v>
+        <v>6385174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13554,9 +13547,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13571,44 +13574,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128791485</v>
+        <v>128791483</v>
       </c>
       <c r="B123" t="n">
-        <v>98658</v>
+        <v>86968</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13618,10 +13621,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725724</v>
+        <v>725645</v>
       </c>
       <c r="R123" t="n">
-        <v>6385174</v>
+        <v>6385261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13653,7 +13656,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13663,7 +13666,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13672,6 +13675,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13690,10 +13694,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128786105</v>
+        <v>128786090</v>
       </c>
       <c r="B124" t="n">
-        <v>96232</v>
+        <v>92817</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13701,23 +13705,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2180</v>
+        <v>6047725</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725537</v>
+        <v>725545</v>
       </c>
       <c r="R124" t="n">
-        <v>6385216</v>
+        <v>6385234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13787,10 +13787,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791448</v>
+        <v>128791512</v>
       </c>
       <c r="B125" t="n">
-        <v>91286</v>
+        <v>87025</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,23 +13798,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13822,10 +13818,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725501</v>
+        <v>725631</v>
       </c>
       <c r="R125" t="n">
-        <v>6385071</v>
+        <v>6385124</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13867,7 +13863,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13894,45 +13890,41 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128791460</v>
+        <v>128784670</v>
       </c>
       <c r="B126" t="n">
-        <v>86788</v>
+        <v>87025</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725718</v>
+        <v>725570</v>
       </c>
       <c r="R126" t="n">
-        <v>6385251</v>
+        <v>6385186</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13962,19 +13954,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13989,22 +13971,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791512</v>
+        <v>128791448</v>
       </c>
       <c r="B127" t="n">
-        <v>87020</v>
+        <v>91291</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14012,19 +13994,23 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14032,10 +14018,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725631</v>
+        <v>725501</v>
       </c>
       <c r="R127" t="n">
-        <v>6385124</v>
+        <v>6385071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14067,7 +14053,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14077,7 +14063,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14104,41 +14090,40 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128784670</v>
+        <v>128791495</v>
       </c>
       <c r="B128" t="n">
-        <v>87020</v>
+        <v>90929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>433</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Duvspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Geastrum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725570</v>
+        <v>725745</v>
       </c>
       <c r="R128" t="n">
-        <v>6385186</v>
+        <v>6385094</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14168,9 +14153,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14185,52 +14180,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791495</v>
+        <v>128786102</v>
       </c>
       <c r="B129" t="n">
-        <v>90924</v>
+        <v>86884</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1000938</v>
+        <v>248956</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725745</v>
+        <v>725513</v>
       </c>
       <c r="R129" t="n">
-        <v>6385094</v>
+        <v>6385159</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14260,19 +14260,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14287,57 +14277,57 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128786102</v>
+        <v>128791460</v>
       </c>
       <c r="B130" t="n">
-        <v>86879</v>
+        <v>86793</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725513</v>
+        <v>725718</v>
       </c>
       <c r="R130" t="n">
-        <v>6385159</v>
+        <v>6385251</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,9 +14357,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -14399,7 +14399,7 @@
         <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>87157</v>
+        <v>87162</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>86929</v>
+        <v>86934</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>128786095</v>
       </c>
       <c r="B134" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>128791510</v>
       </c>
       <c r="B135" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>86929</v>
+        <v>86934</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7411,10 +7411,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128791517</v>
+        <v>128786101</v>
       </c>
       <c r="B63" t="n">
-        <v>86822</v>
+        <v>86891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7422,34 +7422,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725712</v>
+        <v>725528</v>
       </c>
       <c r="R63" t="n">
-        <v>6385261</v>
+        <v>6385185</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,19 +7479,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7506,22 +7496,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128786101</v>
+        <v>128791517</v>
       </c>
       <c r="B64" t="n">
-        <v>86891</v>
+        <v>86822</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7529,34 +7519,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725528</v>
+        <v>725712</v>
       </c>
       <c r="R64" t="n">
-        <v>6385185</v>
+        <v>6385261</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7586,9 +7576,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,12 +7603,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9180,32 +9180,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791466</v>
+        <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86975</v>
+        <v>86800</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>725740</v>
+        <v>725410</v>
       </c>
       <c r="R80" t="n">
-        <v>6385101</v>
+        <v>6385108</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9269,7 +9269,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9288,7 +9287,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791474</v>
+        <v>128791466</v>
       </c>
       <c r="B81" t="n">
         <v>86975</v>
@@ -9323,10 +9322,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>725471</v>
+        <v>725740</v>
       </c>
       <c r="R81" t="n">
-        <v>6385206</v>
+        <v>6385101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9358,7 +9357,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9368,7 +9367,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9396,7 +9395,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791482</v>
+        <v>128791474</v>
       </c>
       <c r="B82" t="n">
         <v>86975</v>
@@ -9431,10 +9430,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>725720</v>
+        <v>725471</v>
       </c>
       <c r="R82" t="n">
-        <v>6385276</v>
+        <v>6385206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9466,7 +9465,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9476,7 +9475,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9504,7 +9503,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128786097</v>
+        <v>128791482</v>
       </c>
       <c r="B83" t="n">
         <v>86975</v>
@@ -9535,14 +9534,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>725551</v>
+        <v>725720</v>
       </c>
       <c r="R83" t="n">
-        <v>6385217</v>
+        <v>6385276</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9572,9 +9571,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9590,57 +9599,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791458</v>
+        <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86800</v>
+        <v>86975</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>725410</v>
+        <v>725551</v>
       </c>
       <c r="R84" t="n">
-        <v>6385108</v>
+        <v>6385217</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9670,39 +9679,30 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -12988,32 +12988,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128784676</v>
+        <v>128784668</v>
       </c>
       <c r="B117" t="n">
-        <v>86938</v>
+        <v>86891</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725647</v>
+        <v>725725</v>
       </c>
       <c r="R117" t="n">
-        <v>6385255</v>
+        <v>6385117</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128784668</v>
+        <v>128791508</v>
       </c>
       <c r="B118" t="n">
-        <v>86891</v>
+        <v>87032</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13096,34 +13096,30 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>725725</v>
+        <v>725757</v>
       </c>
       <c r="R118" t="n">
-        <v>6385117</v>
+        <v>6385187</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13153,9 +13149,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13170,53 +13176,57 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128791508</v>
+        <v>128784676</v>
       </c>
       <c r="B119" t="n">
-        <v>87032</v>
+        <v>86938</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725757</v>
+        <v>725647</v>
       </c>
       <c r="R119" t="n">
-        <v>6385187</v>
+        <v>6385255</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13246,19 +13256,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13273,12 +13273,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -13983,32 +13983,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791448</v>
+        <v>128791495</v>
       </c>
       <c r="B127" t="n">
-        <v>91298</v>
+        <v>90936</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Vit taggsvamp</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14018,10 +14013,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725501</v>
+        <v>725745</v>
       </c>
       <c r="R127" t="n">
-        <v>6385071</v>
+        <v>6385094</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14053,7 +14048,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14063,7 +14058,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14090,32 +14085,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791460</v>
+        <v>128791448</v>
       </c>
       <c r="B128" t="n">
-        <v>86800</v>
+        <v>91298</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14125,10 +14120,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725718</v>
+        <v>725501</v>
       </c>
       <c r="R128" t="n">
-        <v>6385251</v>
+        <v>6385071</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14160,7 +14155,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14170,7 +14165,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14197,10 +14192,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791495</v>
+        <v>128791460</v>
       </c>
       <c r="B129" t="n">
-        <v>90936</v>
+        <v>86800</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14208,16 +14203,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1000938</v>
+        <v>3712</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14227,10 +14227,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725745</v>
+        <v>725718</v>
       </c>
       <c r="R129" t="n">
-        <v>6385094</v>
+        <v>6385251</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7011,10 +7011,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128791453</v>
+        <v>128786101</v>
       </c>
       <c r="B59" t="n">
-        <v>91298</v>
+        <v>86894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7022,34 +7022,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>725494</v>
+        <v>725528</v>
       </c>
       <c r="R59" t="n">
-        <v>6385080</v>
+        <v>6385185</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7079,50 +7079,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128786091</v>
+        <v>128791453</v>
       </c>
       <c r="B60" t="n">
-        <v>91298</v>
+        <v>91301</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7150,14 +7139,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R60" t="n">
-        <v>6385159</v>
+        <v>6385080</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7187,39 +7176,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128784654</v>
+        <v>128786091</v>
       </c>
       <c r="B61" t="n">
-        <v>91298</v>
+        <v>91301</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7247,14 +7247,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R61" t="n">
-        <v>6385035</v>
+        <v>6385159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7301,44 +7301,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784663</v>
+        <v>128784654</v>
       </c>
       <c r="B62" t="n">
-        <v>86975</v>
+        <v>91301</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7348,10 +7348,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725739</v>
+        <v>725494</v>
       </c>
       <c r="R62" t="n">
-        <v>6385174</v>
+        <v>6385035</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7392,7 +7392,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7411,10 +7410,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128786101</v>
+        <v>128791517</v>
       </c>
       <c r="B63" t="n">
-        <v>86891</v>
+        <v>86825</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7422,34 +7421,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725528</v>
+        <v>725712</v>
       </c>
       <c r="R63" t="n">
-        <v>6385185</v>
+        <v>6385261</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,9 +7478,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7496,57 +7505,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128791517</v>
+        <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>725712</v>
+        <v>725739</v>
       </c>
       <c r="R64" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7576,71 +7585,62 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128791475</v>
+        <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86975</v>
+        <v>86803</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>725503</v>
+        <v>725746</v>
       </c>
       <c r="R65" t="n">
-        <v>6385246</v>
+        <v>6385092</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,7 +7704,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7723,10 +7722,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128791478</v>
+        <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7758,10 +7757,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>725685</v>
+        <v>725503</v>
       </c>
       <c r="R66" t="n">
-        <v>6385124</v>
+        <v>6385246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7793,7 +7792,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7803,7 +7802,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7831,32 +7830,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128791459</v>
+        <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86800</v>
+        <v>86978</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7866,10 +7865,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>725746</v>
+        <v>725685</v>
       </c>
       <c r="R67" t="n">
-        <v>6385092</v>
+        <v>6385124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7901,7 +7900,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7911,7 +7910,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7920,6 +7919,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B68" t="n">
-        <v>91298</v>
+        <v>86978</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R68" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,6 +8027,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8045,32 +8046,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B69" t="n">
-        <v>86975</v>
+        <v>91301</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8080,10 +8081,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R69" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8125,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8134,7 +8135,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128791503</v>
+        <v>128786092</v>
       </c>
       <c r="B70" t="n">
-        <v>87032</v>
+        <v>91301</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,30 +8164,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>725496</v>
+        <v>725499</v>
       </c>
       <c r="R70" t="n">
-        <v>6385236</v>
+        <v>6385065</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8217,19 +8221,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,22 +8238,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128786092</v>
+        <v>128784653</v>
       </c>
       <c r="B71" t="n">
-        <v>91298</v>
+        <v>91301</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8287,14 +8281,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>725499</v>
+        <v>725496</v>
       </c>
       <c r="R71" t="n">
-        <v>6385065</v>
+        <v>6385075</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8341,22 +8335,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128784653</v>
+        <v>128791503</v>
       </c>
       <c r="B72" t="n">
-        <v>91298</v>
+        <v>87035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,34 +8358,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>725496</v>
       </c>
       <c r="R72" t="n">
-        <v>6385075</v>
+        <v>6385236</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8421,9 +8411,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,12 +8438,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>128791506</v>
       </c>
       <c r="B76" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128791488</v>
       </c>
       <c r="B77" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>128791465</v>
       </c>
       <c r="B78" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>128791481</v>
       </c>
       <c r="B79" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9709,45 +9709,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791489</v>
+        <v>128786098</v>
       </c>
       <c r="B85" t="n">
-        <v>86997</v>
+        <v>98678</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>725612</v>
+        <v>725577</v>
       </c>
       <c r="R85" t="n">
-        <v>6385206</v>
+        <v>6385250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,19 +9777,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9804,22 +9794,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791452</v>
+        <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>91298</v>
+        <v>87000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9827,21 +9817,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9851,10 +9841,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>725424</v>
+        <v>725612</v>
       </c>
       <c r="R86" t="n">
-        <v>6384953</v>
+        <v>6385206</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9886,7 +9876,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9896,7 +9886,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9923,45 +9913,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128786098</v>
+        <v>128791452</v>
       </c>
       <c r="B87" t="n">
-        <v>98673</v>
+        <v>91301</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219862</v>
+        <v>2015</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>725577</v>
+        <v>725424</v>
       </c>
       <c r="R87" t="n">
-        <v>6385250</v>
+        <v>6384953</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9991,9 +9981,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,12 +10008,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>128791469</v>
       </c>
       <c r="B89" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>128784662</v>
       </c>
       <c r="B90" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>128784659</v>
       </c>
       <c r="B91" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10427,10 +10427,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784669</v>
+        <v>128784675</v>
       </c>
       <c r="B92" t="n">
-        <v>86997</v>
+        <v>86865</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10438,21 +10438,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10462,10 +10462,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725759</v>
+        <v>725536</v>
       </c>
       <c r="R92" t="n">
-        <v>6385120</v>
+        <v>6385137</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784675</v>
+        <v>128784669</v>
       </c>
       <c r="B93" t="n">
-        <v>86862</v>
+        <v>87000</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725536</v>
+        <v>725759</v>
       </c>
       <c r="R93" t="n">
-        <v>6385137</v>
+        <v>6385120</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10624,7 +10624,7 @@
         <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10931,10 +10931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128791514</v>
+        <v>128791504</v>
       </c>
       <c r="B97" t="n">
-        <v>86862</v>
+        <v>87035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10942,23 +10942,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10966,10 +10962,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>725527</v>
+        <v>725500</v>
       </c>
       <c r="R97" t="n">
-        <v>6385142</v>
+        <v>6385247</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11001,7 +10997,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11011,7 +11007,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11038,10 +11034,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128791504</v>
+        <v>128791514</v>
       </c>
       <c r="B98" t="n">
-        <v>87032</v>
+        <v>86865</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11049,19 +11045,23 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>725500</v>
+        <v>725527</v>
       </c>
       <c r="R98" t="n">
-        <v>6385247</v>
+        <v>6385142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11144,7 +11144,7 @@
         <v>128784661</v>
       </c>
       <c r="B99" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>128791473</v>
       </c>
       <c r="B100" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11347,10 +11347,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128791516</v>
+        <v>128784657</v>
       </c>
       <c r="B101" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11378,14 +11378,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>725744</v>
+        <v>725724</v>
       </c>
       <c r="R101" t="n">
-        <v>6385244</v>
+        <v>6385171</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11415,19 +11415,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11442,22 +11432,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128784657</v>
+        <v>128791516</v>
       </c>
       <c r="B102" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11485,14 +11475,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725724</v>
+        <v>725744</v>
       </c>
       <c r="R102" t="n">
-        <v>6385171</v>
+        <v>6385244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11522,9 +11512,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,12 +11539,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
         <v>128791505</v>
       </c>
       <c r="B103" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11654,41 +11654,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128791499</v>
+        <v>128786100</v>
       </c>
       <c r="B104" t="n">
-        <v>87032</v>
+        <v>90961</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>4190</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Geastrum striatum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725431</v>
+        <v>725528</v>
       </c>
       <c r="R104" t="n">
-        <v>6385191</v>
+        <v>6385185</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11718,49 +11722,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B105" t="n">
-        <v>90958</v>
+        <v>92812</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11768,34 +11763,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R105" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,64 +11831,59 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128784652</v>
+        <v>128791499</v>
       </c>
       <c r="B106" t="n">
-        <v>92807</v>
+        <v>87035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4363</v>
+        <v>433</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725629</v>
+        <v>725431</v>
       </c>
       <c r="R106" t="n">
-        <v>6385285</v>
+        <v>6385191</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11923,9 +11913,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,12 +11940,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
         <v>128786099</v>
       </c>
       <c r="B107" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12049,10 +12049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128791479</v>
+        <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>86975</v>
+        <v>107571</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12060,34 +12060,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>725712</v>
+        <v>725501</v>
       </c>
       <c r="R108" t="n">
-        <v>6385103</v>
+        <v>6385056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,50 +12117,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128784666</v>
+        <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>107566</v>
+        <v>86978</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12168,34 +12157,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>725501</v>
+        <v>725712</v>
       </c>
       <c r="R109" t="n">
-        <v>6385056</v>
+        <v>6385103</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12225,29 +12214,40 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,32 +12460,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128791487</v>
+        <v>128791462</v>
       </c>
       <c r="B112" t="n">
-        <v>86997</v>
+        <v>86779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>725771</v>
+        <v>725541</v>
       </c>
       <c r="R112" t="n">
-        <v>6385103</v>
+        <v>6385088</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12549,7 +12549,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12568,45 +12567,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128791480</v>
+        <v>128786106</v>
       </c>
       <c r="B113" t="n">
-        <v>86975</v>
+        <v>86803</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>725785</v>
+        <v>725520</v>
       </c>
       <c r="R113" t="n">
-        <v>6385095</v>
+        <v>6385158</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12636,50 +12635,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128791467</v>
+        <v>128791480</v>
       </c>
       <c r="B114" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12711,10 +12699,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>725756</v>
+        <v>725785</v>
       </c>
       <c r="R114" t="n">
-        <v>6385191</v>
+        <v>6385095</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,7 +12734,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12756,7 +12744,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12784,32 +12772,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128791462</v>
+        <v>128791467</v>
       </c>
       <c r="B115" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12819,10 +12807,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>725541</v>
+        <v>725756</v>
       </c>
       <c r="R115" t="n">
-        <v>6385088</v>
+        <v>6385191</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12854,7 +12842,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12864,7 +12852,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12873,6 +12861,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12891,45 +12880,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128786106</v>
+        <v>128791487</v>
       </c>
       <c r="B116" t="n">
-        <v>86800</v>
+        <v>87000</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>725520</v>
+        <v>725771</v>
       </c>
       <c r="R116" t="n">
-        <v>6385158</v>
+        <v>6385103</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12959,61 +12948,72 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128784668</v>
+        <v>128784676</v>
       </c>
       <c r="B117" t="n">
-        <v>86891</v>
+        <v>86941</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>725725</v>
+        <v>725647</v>
       </c>
       <c r="R117" t="n">
-        <v>6385117</v>
+        <v>6385255</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13088,7 +13088,7 @@
         <v>128791508</v>
       </c>
       <c r="B118" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13188,32 +13188,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128784676</v>
+        <v>128784668</v>
       </c>
       <c r="B119" t="n">
-        <v>86938</v>
+        <v>86894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13223,10 +13223,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>725647</v>
+        <v>725725</v>
       </c>
       <c r="R119" t="n">
-        <v>6385255</v>
+        <v>6385117</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13285,45 +13285,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128784658</v>
+        <v>128786105</v>
       </c>
       <c r="B120" t="n">
-        <v>86822</v>
+        <v>96252</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>2180</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>725646</v>
+        <v>725537</v>
       </c>
       <c r="R120" t="n">
-        <v>6385281</v>
+        <v>6385216</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13370,57 +13370,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128786105</v>
+        <v>128784658</v>
       </c>
       <c r="B121" t="n">
-        <v>96247</v>
+        <v>86825</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2180</v>
+        <v>424</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>725537</v>
+        <v>725646</v>
       </c>
       <c r="R121" t="n">
-        <v>6385216</v>
+        <v>6385281</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13467,44 +13467,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128791483</v>
+        <v>128791485</v>
       </c>
       <c r="B122" t="n">
-        <v>86975</v>
+        <v>98678</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>725645</v>
+        <v>725724</v>
       </c>
       <c r="R122" t="n">
-        <v>6385261</v>
+        <v>6385174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13568,7 +13568,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13587,41 +13586,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128786090</v>
+        <v>128791483</v>
       </c>
       <c r="B123" t="n">
-        <v>92825</v>
+        <v>86978</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>725545</v>
+        <v>725645</v>
       </c>
       <c r="R123" t="n">
-        <v>6385234</v>
+        <v>6385261</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13651,39 +13654,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128791485</v>
+        <v>128786090</v>
       </c>
       <c r="B124" t="n">
-        <v>98673</v>
+        <v>92830</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13691,34 +13705,30 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219862</v>
+        <v>6047725</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>725724</v>
+        <v>725545</v>
       </c>
       <c r="R124" t="n">
-        <v>6385174</v>
+        <v>6385234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13748,19 +13758,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13775,22 +13775,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128791512</v>
+        <v>128786102</v>
       </c>
       <c r="B125" t="n">
-        <v>87032</v>
+        <v>86894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,30 +13798,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>725631</v>
+        <v>725513</v>
       </c>
       <c r="R125" t="n">
-        <v>6385124</v>
+        <v>6385159</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13851,19 +13855,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13878,22 +13872,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128784670</v>
+        <v>128791448</v>
       </c>
       <c r="B126" t="n">
-        <v>87032</v>
+        <v>91301</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13901,30 +13895,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>725570</v>
+        <v>725501</v>
       </c>
       <c r="R126" t="n">
-        <v>6385186</v>
+        <v>6385071</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13954,9 +13952,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13971,22 +13979,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128791495</v>
+        <v>128791460</v>
       </c>
       <c r="B127" t="n">
-        <v>90936</v>
+        <v>86803</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13994,16 +14002,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1000938</v>
+        <v>3712</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14013,10 +14026,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>725745</v>
+        <v>725718</v>
       </c>
       <c r="R127" t="n">
-        <v>6385094</v>
+        <v>6385251</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14048,7 +14061,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14058,7 +14071,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14085,10 +14098,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128791448</v>
+        <v>128784670</v>
       </c>
       <c r="B128" t="n">
-        <v>91298</v>
+        <v>87035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14096,34 +14109,30 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2015</v>
+        <v>433</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>725501</v>
+        <v>725570</v>
       </c>
       <c r="R128" t="n">
-        <v>6385071</v>
+        <v>6385186</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14153,19 +14162,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14180,46 +14179,42 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128791460</v>
+        <v>128791512</v>
       </c>
       <c r="B129" t="n">
-        <v>86800</v>
+        <v>87035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14227,10 +14222,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>725718</v>
+        <v>725631</v>
       </c>
       <c r="R129" t="n">
-        <v>6385251</v>
+        <v>6385124</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14262,7 +14257,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14272,7 +14267,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14299,45 +14294,40 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128786102</v>
+        <v>128791495</v>
       </c>
       <c r="B130" t="n">
-        <v>86891</v>
+        <v>90939</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248956</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Gulsträngad fagerspindling</t>
-        </is>
+        <v>1000938</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>725513</v>
+        <v>725745</v>
       </c>
       <c r="R130" t="n">
-        <v>6385159</v>
+        <v>6385094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,9 +14357,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,12 +14384,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -14399,7 +14399,7 @@
         <v>128791455</v>
       </c>
       <c r="B131" t="n">
-        <v>87169</v>
+        <v>87172</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>128815450</v>
       </c>
       <c r="B132" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>128791501</v>
       </c>
       <c r="B133" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>128786095</v>
       </c>
       <c r="B134" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>128791510</v>
       </c>
       <c r="B135" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>128815373</v>
       </c>
       <c r="B136" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 30236-2025 artfynd.xlsx
+++ b/artfynd/A 30236-2025 artfynd.xlsx
@@ -7014,7 +7014,7 @@
         <v>128786101</v>
       </c>
       <c r="B59" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128791453</v>
+        <v>128791517</v>
       </c>
       <c r="B60" t="n">
-        <v>91301</v>
+        <v>86828</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,21 +7119,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>725494</v>
+        <v>725712</v>
       </c>
       <c r="R60" t="n">
-        <v>6385080</v>
+        <v>6385261</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7197,7 +7197,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7216,10 +7215,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128786091</v>
+        <v>128791453</v>
       </c>
       <c r="B61" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7247,14 +7246,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>725507</v>
+        <v>725494</v>
       </c>
       <c r="R61" t="n">
-        <v>6385159</v>
+        <v>6385080</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7284,39 +7283,50 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128784654</v>
+        <v>128786091</v>
       </c>
       <c r="B62" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7344,14 +7354,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>725494</v>
+        <v>725507</v>
       </c>
       <c r="R62" t="n">
-        <v>6385035</v>
+        <v>6385159</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7398,22 +7408,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128791517</v>
+        <v>128784654</v>
       </c>
       <c r="B63" t="n">
-        <v>86825</v>
+        <v>91304</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7421,34 +7431,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>725712</v>
+        <v>725494</v>
       </c>
       <c r="R63" t="n">
-        <v>6385261</v>
+        <v>6385035</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7478,19 +7488,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7505,12 +7505,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
         <v>128784663</v>
       </c>
       <c r="B64" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
         <v>128791459</v>
       </c>
       <c r="B65" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>128791475</v>
       </c>
       <c r="B66" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>128791478</v>
       </c>
       <c r="B67" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128791463</v>
+        <v>128791449</v>
       </c>
       <c r="B68" t="n">
-        <v>86978</v>
+        <v>91304</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>725426</v>
+        <v>725457</v>
       </c>
       <c r="R68" t="n">
-        <v>6385160</v>
+        <v>6385042</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8027,7 +8027,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8046,32 +8045,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791449</v>
+        <v>128791463</v>
       </c>
       <c r="B69" t="n">
-        <v>91301</v>
+        <v>86981</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8081,10 +8080,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>725457</v>
+        <v>725426</v>
       </c>
       <c r="R69" t="n">
-        <v>6385042</v>
+        <v>6385160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,6 +8134,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>128786092</v>
       </c>
       <c r="B70" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128784653</v>
       </c>
       <c r="B71" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
         <v>128791503</v>
       </c>
       <c r="B72" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>128784660</v>
       </c>
       <c r="B73" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8551,7 +8551,7 @@
         <v>128791476</v>
       </c>
       <c r="B74" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>128784664</v>
       </c>
       <c r="B75" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8747,37 +8747,41 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791506</v>
+        <v>128791465</v>
       </c>
       <c r="B76" t="n">
-        <v>87035</v>
+        <v>86981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8785,10 +8789,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>725546</v>
+        <v>725458</v>
       </c>
       <c r="R76" t="n">
-        <v>6385296</v>
+        <v>6385186</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8820,7 +8824,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8830,7 +8834,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8839,6 +8843,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8857,32 +8862,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791488</v>
+        <v>128791481</v>
       </c>
       <c r="B77" t="n">
-        <v>87000</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>725580</v>
+        <v>725669</v>
       </c>
       <c r="R77" t="n">
-        <v>6385121</v>
+        <v>6385183</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8927,7 +8932,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8937,7 +8942,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8946,6 +8951,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8964,34 +8970,30 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791465</v>
+        <v>128791506</v>
       </c>
       <c r="B78" t="n">
-        <v>86978</v>
+        <v>87038</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8999,10 +9001,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>725458</v>
+        <v>725546</v>
       </c>
       <c r="R78" t="n">
-        <v>6385186</v>
+        <v>6385296</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9034,7 +9036,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9044,7 +9046,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9053,7 +9055,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9072,32 +9073,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128791481</v>
+        <v>128791488</v>
       </c>
       <c r="B79" t="n">
-        <v>86978</v>
+        <v>87003</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9108,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>725669</v>
+        <v>725580</v>
       </c>
       <c r="R79" t="n">
-        <v>6385183</v>
+        <v>6385121</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9142,7 +9143,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9152,7 +9153,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,7 +9162,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>128791458</v>
       </c>
       <c r="B80" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>128791466</v>
       </c>
       <c r="B81" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>128791474</v>
       </c>
       <c r="B82" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128791482</v>
       </c>
       <c r="B83" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>128786097</v>
       </c>
       <c r="B84" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>128786098</v>
       </c>
       <c r="B85" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>128791489</v>
       </c>
       <c r="B86" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>128791452</v>
       </c>
       <c r="B87" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>128791502</v>
       </c>
       <c r="B88" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10123,45 +10123,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791469</v>
+        <v>128784675</v>
       </c>
       <c r="B89" t="n">
-        <v>86978</v>
+        <v>86868</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>725461</v>
+        <v>725536</v>
       </c>
       <c r="R89" t="n">
-        <v>6385028</v>
+        <v>6385137</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,72 +10191,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128784662</v>
+        <v>128784669</v>
       </c>
       <c r="B90" t="n">
-        <v>86978</v>
+        <v>87003</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10266,10 +10255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>725771</v>
+        <v>725759</v>
       </c>
       <c r="R90" t="n">
-        <v>6385166</v>
+        <v>6385120</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10310,7 +10299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10322,17 +10310,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128784659</v>
+        <v>128791469</v>
       </c>
       <c r="B91" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10360,14 +10348,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>725626</v>
+        <v>725461</v>
       </c>
       <c r="R91" t="n">
-        <v>6385141</v>
+        <v>6385028</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10397,9 +10385,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10415,44 +10413,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128784675</v>
+        <v>128784662</v>
       </c>
       <c r="B92" t="n">
-        <v>86865</v>
+        <v>86981</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10462,10 +10460,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>725536</v>
+        <v>725771</v>
       </c>
       <c r="R92" t="n">
-        <v>6385137</v>
+        <v>6385166</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10506,6 +10504,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10517,39 +10516,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128784669</v>
+        <v>128784659</v>
       </c>
       <c r="B93" t="n">
-        <v>87000</v>
+        <v>86981</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10559,10 +10558,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>725759</v>
+        <v>725626</v>
       </c>
       <c r="R93" t="n">
-        <v>6385120</v>
+        <v>6385141</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10603,6 +10602,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10624,7 +10624,7 @@
         <v>128791498</v>
       </c>
       <c r="B94" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128786089</v>
       </c>
       <c r="B95" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>128791477</v>
       </c>
       <c r="B96" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>128791504</v>
       </c>
       <c r="B97" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>128791514</v>
       </c>
       <c r="B98" t="n">
-        <v>86865</v>
+        <v>86868</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11141,32 +11141,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128784661</v>
+        <v>128784657</v>
       </c>
       <c r="B99" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11176,10 +11176,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>725740</v>
+        <v>725724</v>
       </c>
       <c r="R99" t="n">
-        <v>6385127</v>
+        <v>6385171</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11220,7 +11220,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11232,39 +11231,39 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128791473</v>
+        <v>128791516</v>
       </c>
       <c r="B100" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11274,10 +11273,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>725405</v>
+        <v>725744</v>
       </c>
       <c r="R100" t="n">
-        <v>6385117</v>
+        <v>6385244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11309,7 +11308,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11319,7 +11318,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11328,7 +11327,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11347,10 +11345,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128784657</v>
+        <v>128791505</v>
       </c>
       <c r="B101" t="n">
-        <v>86825</v>
+        <v>87038</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11358,34 +11356,30 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>725724</v>
+        <v>725506</v>
       </c>
       <c r="R101" t="n">
-        <v>6385171</v>
+        <v>6385254</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11415,9 +11409,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11432,57 +11436,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128791516</v>
+        <v>128784661</v>
       </c>
       <c r="B102" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>725744</v>
+        <v>725740</v>
       </c>
       <c r="R102" t="n">
-        <v>6385244</v>
+        <v>6385127</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11512,69 +11516,64 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128791505</v>
+        <v>128791473</v>
       </c>
       <c r="B103" t="n">
-        <v>87035</v>
+        <v>86981</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11582,10 +11581,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>725506</v>
+        <v>725405</v>
       </c>
       <c r="R103" t="n">
-        <v>6385254</v>
+        <v>6385117</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11616,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11626,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11636,6 +11635,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128786100</v>
+        <v>128784652</v>
       </c>
       <c r="B104" t="n">
-        <v>90961</v>
+        <v>92815</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,34 +11665,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4190</v>
+        <v>4363</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kantjordstjärna</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Geastrum striatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nors, Gtl</t>
+          <t>Storhagen, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>725528</v>
+        <v>725629</v>
       </c>
       <c r="R104" t="n">
-        <v>6385185</v>
+        <v>6385285</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11733,64 +11733,59 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128784652</v>
+        <v>128791499</v>
       </c>
       <c r="B105" t="n">
-        <v>92812</v>
+        <v>87038</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4363</v>
+        <v>433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storhagen, Gtl</t>
+          <t>Gothem Hangre, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>725629</v>
+        <v>725431</v>
       </c>
       <c r="R105" t="n">
-        <v>6385285</v>
+        <v>6385191</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11820,9 +11815,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11837,22 +11842,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128791499</v>
+        <v>128786099</v>
       </c>
       <c r="B106" t="n">
-        <v>87035</v>
+        <v>91061</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11860,30 +11865,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>433</v>
+        <v>5747</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gothem Hangre, Gtl</t>
+          <t>Nors, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>725431</v>
+        <v>725542</v>
       </c>
       <c r="R106" t="n">
-        <v>6385191</v>
+        <v>6385225</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11913,19 +11922,9 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,44 +11939,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128786099</v>
+        <v>128786100</v>
       </c>
       <c r="B107" t="n">
-        <v>91058</v>
+        <v>90964</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5747</v>
+        <v>4190</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kantjordstjärna</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum striatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11987,10 +11986,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>725542</v>
+        <v>725528</v>
       </c>
       <c r="R107" t="n">
-        <v>6385225</v>
+        <v>6385185</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12031,6 +12030,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>128784666</v>
       </c>
       <c r="B108" t="n">
-        <v>107571</v>
+        <v>107574</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
         <v>128791479</v>
       </c>
       <c r="B109" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>128786096</v>
       </c>
       <c r="B110" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>128791468</v>
       </c>
       <c r="B111" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12460,32 +12460,32 @@
     </row>
